--- a/tabular/reference/herv_sublineage_data.xlsx
+++ b/tabular/reference/herv_sublineage_data.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C24C156-F07E-B645-A2F4-C48A75F7E4E6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D532016-7CAC-6B4A-89F9-868901BFD1CD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2320" yWindow="500" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1680" yWindow="520" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sublineage" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="229">
   <si>
     <t>sequenceID</t>
   </si>
@@ -635,6 +636,78 @@
   </si>
   <si>
     <t>Standardised lineage name</t>
+  </si>
+  <si>
+    <t>HERV-Fc1</t>
+  </si>
+  <si>
+    <t>ERV-1.HF.Fc.1</t>
+  </si>
+  <si>
+    <t>lineage</t>
+  </si>
+  <si>
+    <t>AncRecon</t>
+  </si>
+  <si>
+    <t>HERV-Fc2</t>
+  </si>
+  <si>
+    <t>ERV-1.HF.Fc.2</t>
+  </si>
+  <si>
+    <t>human endogenous retrovirus F(c) 2</t>
+  </si>
+  <si>
+    <t>human endogenous retrovirus F(c) 1</t>
+  </si>
+  <si>
+    <t>HERV-T1</t>
+  </si>
+  <si>
+    <t>ERV-1.Gamma.T1</t>
+  </si>
+  <si>
+    <t>human endogenous retrovirus T1</t>
+  </si>
+  <si>
+    <t>HERV-T2</t>
+  </si>
+  <si>
+    <t>ERV-1.Gamma.T2</t>
+  </si>
+  <si>
+    <t>human endogenous retrovirus T2</t>
+  </si>
+  <si>
+    <t>HERVT1</t>
+  </si>
+  <si>
+    <t>HERVT2</t>
+  </si>
+  <si>
+    <t>HERV-T3</t>
+  </si>
+  <si>
+    <t>ERV-1.Gamma.T3</t>
+  </si>
+  <si>
+    <t>human endogenous retrovirus T3</t>
+  </si>
+  <si>
+    <t>HERVT3</t>
+  </si>
+  <si>
+    <t>HERVT</t>
+  </si>
+  <si>
+    <t>RRHERV-I</t>
+  </si>
+  <si>
+    <t>Retinoic acid-responsive human endogenous retrovirus I</t>
+  </si>
+  <si>
+    <t>ERV-1.Gamma.I</t>
   </si>
 </sst>
 </file>
@@ -1526,13 +1599,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB9083D8-DE01-F14E-ACB5-AF33867092C5}">
-  <dimension ref="A1:U57"/>
+  <dimension ref="A1:U58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
     <col min="2" max="2" width="27.5" customWidth="1"/>
     <col min="3" max="3" width="18.5" customWidth="1"/>
-    <col min="4" max="4" width="21" customWidth="1"/>
+    <col min="4" max="4" width="50.1640625" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="11" max="11" width="21" customWidth="1"/>
   </cols>
@@ -4832,6 +4905,67 @@
         <v>3</v>
       </c>
     </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A58" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H58" s="2">
+        <v>9464</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="O58" s="2">
+        <v>7</v>
+      </c>
+      <c r="P58" s="2"/>
+      <c r="Q58" s="2"/>
+      <c r="R58" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="S58" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="T58" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="U58" s="2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T57">
     <sortCondition ref="I2:I57"/>
@@ -4839,7 +4973,67 @@
     <sortCondition ref="L2:L57"/>
     <sortCondition ref="C2:C57"/>
   </sortState>
-  <conditionalFormatting sqref="U58:U1048576 U1:U48">
+  <conditionalFormatting sqref="U63:U1048576 U1:U48">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U49:U52">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U53:U54">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U55">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U56">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U57">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -4851,55 +5045,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U49:U52">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U53:U54">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U55">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U56">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U57">
+  <conditionalFormatting sqref="U58">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -4913,4 +5059,426 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF64240C-8748-834A-9B04-2536247ED9D0}">
+  <dimension ref="A1:U6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="O4" s="2">
+        <v>7</v>
+      </c>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="U4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="O5" s="2">
+        <v>7</v>
+      </c>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="U5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="O6" s="2">
+        <v>7</v>
+      </c>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="U6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="U2">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U4">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U3">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U5">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U6">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U1">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/tabular/reference/herv_sublineage_data.xlsx
+++ b/tabular/reference/herv_sublineage_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D532016-7CAC-6B4A-89F9-868901BFD1CD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05097530-0173-0D4A-A691-99FA59B25F84}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="520" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="233">
   <si>
     <t>sequenceID</t>
   </si>
@@ -708,6 +708,18 @@
   </si>
   <si>
     <t>ERV-1.Gamma.I</t>
+  </si>
+  <si>
+    <t>Iotaretrovirus</t>
+  </si>
+  <si>
+    <t>HERV-ADP</t>
+  </si>
+  <si>
+    <t>human endogenous retrovirus ADP</t>
+  </si>
+  <si>
+    <t>ERV-1.Iota.ADP</t>
   </si>
 </sst>
 </file>
@@ -1599,7 +1611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB9083D8-DE01-F14E-ACB5-AF33867092C5}">
-  <dimension ref="A1:U58"/>
+  <dimension ref="A1:U59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -1793,28 +1805,28 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>45</v>
+        <v>226</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>172</v>
+        <v>228</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>108</v>
+        <v>226</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>227</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>45</v>
+        <v>226</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H4" s="2">
-        <v>4936</v>
+        <v>9464</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>24</v>
@@ -1823,55 +1835,59 @@
         <v>5</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>225</v>
+      </c>
       <c r="M4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O4" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="O4" s="2">
+        <v>7</v>
+      </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
       <c r="R4" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="U4" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>173</v>
+        <v>232</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>109</v>
+        <v>230</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>231</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>143</v>
+        <v>207</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H5" s="2">
-        <v>9084</v>
+        <v>7590</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>24</v>
@@ -1880,53 +1896,57 @@
         <v>5</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>44</v>
+        <v>229</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O5" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="O5" s="2">
+        <v>1</v>
+      </c>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U5" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E6" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="F6" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H6" s="2">
-        <v>8439</v>
+        <v>4936</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>24</v>
@@ -1939,14 +1959,12 @@
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O6" s="2">
-        <v>1</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="O6" s="2"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2" t="s">
@@ -1964,28 +1982,28 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>143</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H7" s="2">
-        <v>7613</v>
+        <v>9084</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>24</v>
@@ -1994,7 +2012,7 @@
         <v>5</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="2" t="s">
@@ -2007,7 +2025,7 @@
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>13</v>
@@ -2016,33 +2034,31 @@
         <v>13</v>
       </c>
       <c r="U7" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>147</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H8" s="2">
-        <v>1786</v>
+        <v>8439</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>24</v>
@@ -2051,16 +2067,18 @@
         <v>5</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O8" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="O8" s="2">
+        <v>1</v>
+      </c>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="2" t="s">
@@ -2078,28 +2096,28 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>143</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H9" s="2">
-        <v>9161</v>
+        <v>7613</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>24</v>
@@ -2112,14 +2130,12 @@
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O9" s="2">
-        <v>1</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="O9" s="2"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="2" t="s">
@@ -2132,31 +2148,33 @@
         <v>13</v>
       </c>
       <c r="U9" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" s="2"/>
+        <v>53</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="F10" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H10" s="2">
-        <v>8120</v>
+        <v>1786</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>24</v>
@@ -2192,28 +2210,28 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H11" s="2">
-        <v>4060</v>
+        <v>9161</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>24</v>
@@ -2226,16 +2244,18 @@
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O11" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="O11" s="2">
+        <v>1</v>
+      </c>
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
       <c r="R11" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>13</v>
@@ -2244,33 +2264,31 @@
         <v>13</v>
       </c>
       <c r="U11" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>147</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H12" s="2">
-        <v>4798</v>
+        <v>8120</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>24</v>
@@ -2306,28 +2324,28 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>124</v>
+        <v>56</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H13" s="2">
-        <v>6639</v>
+        <v>4060</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>24</v>
@@ -2363,28 +2381,28 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>125</v>
+        <v>57</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>147</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="2">
-        <v>933</v>
+        <v>4798</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>24</v>
@@ -2420,28 +2438,28 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H15" s="2">
-        <v>4936</v>
+        <v>6639</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>24</v>
@@ -2477,28 +2495,28 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>147</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H16" s="2">
-        <v>5356</v>
+        <v>933</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>24</v>
@@ -2534,28 +2552,28 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>185</v>
+        <v>60</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>183</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>147</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H17" s="2">
-        <v>6387</v>
+        <v>4936</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>24</v>
@@ -2591,28 +2609,28 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>186</v>
+        <v>61</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>147</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H18" s="2">
-        <v>6758</v>
+        <v>5356</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>24</v>
@@ -2648,28 +2666,28 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H19" s="2">
-        <v>5217</v>
+        <v>6387</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>24</v>
@@ -2705,28 +2723,28 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H20" s="2">
-        <v>4871</v>
+        <v>6758</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>24</v>
@@ -2751,7 +2769,7 @@
         <v>46</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T20" s="2" t="s">
         <v>13</v>
@@ -2762,28 +2780,28 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H21" s="2">
-        <v>7048</v>
+        <v>5217</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>24</v>
@@ -2819,28 +2837,28 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>190</v>
+        <v>65</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>188</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>143</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H22" s="2">
-        <v>4102</v>
+        <v>4871</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>24</v>
@@ -2862,7 +2880,7 @@
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="S22" s="2" t="s">
         <v>12</v>
@@ -2871,33 +2889,33 @@
         <v>13</v>
       </c>
       <c r="U22" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>191</v>
+        <v>66</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>189</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>147</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H23" s="2">
-        <v>4981</v>
+        <v>7048</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>24</v>
@@ -2906,11 +2924,9 @@
         <v>5</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>69</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="L23" s="1"/>
       <c r="M23" s="2" t="s">
         <v>6</v>
       </c>
@@ -2921,7 +2937,7 @@
       <c r="P23" s="2"/>
       <c r="Q23" s="2"/>
       <c r="R23" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="S23" s="2" t="s">
         <v>13</v>
@@ -2930,33 +2946,33 @@
         <v>13</v>
       </c>
       <c r="U23" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>116</v>
+        <v>67</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>143</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H24" s="2">
-        <v>6996</v>
+        <v>4102</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>24</v>
@@ -2965,11 +2981,9 @@
         <v>5</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>71</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="L24" s="1"/>
       <c r="M24" s="2" t="s">
         <v>6</v>
       </c>
@@ -2983,7 +2997,7 @@
         <v>12</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T24" s="2" t="s">
         <v>13</v>
@@ -2994,28 +3008,28 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H25" s="2">
-        <v>11027</v>
+        <v>4981</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>24</v>
@@ -3027,7 +3041,7 @@
         <v>68</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>6</v>
@@ -3039,7 +3053,7 @@
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
       <c r="R25" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="S25" s="2" t="s">
         <v>13</v>
@@ -3048,33 +3062,33 @@
         <v>13</v>
       </c>
       <c r="U25" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>116</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H26" s="2">
-        <v>8987</v>
+        <v>6996</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>24</v>
@@ -3098,7 +3112,7 @@
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
       <c r="R26" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="S26" s="2" t="s">
         <v>13</v>
@@ -3107,33 +3121,33 @@
         <v>13</v>
       </c>
       <c r="U26" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H27" s="2">
-        <v>7418</v>
+        <v>11027</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>24</v>
@@ -3157,7 +3171,7 @@
       <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
       <c r="R27" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="S27" s="2" t="s">
         <v>13</v>
@@ -3166,33 +3180,33 @@
         <v>13</v>
       </c>
       <c r="U27" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H28" s="2">
-        <v>5586</v>
+        <v>8987</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>24</v>
@@ -3203,7 +3217,9 @@
       <c r="K28" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="L28" s="1"/>
+      <c r="L28" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="M28" s="2" t="s">
         <v>6</v>
       </c>
@@ -3228,28 +3244,28 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H29" s="2">
-        <v>6918</v>
+        <v>7418</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>24</v>
@@ -3260,7 +3276,9 @@
       <c r="K29" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="L29" s="1"/>
+      <c r="L29" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="M29" s="2" t="s">
         <v>6</v>
       </c>
@@ -3271,7 +3289,7 @@
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
       <c r="R29" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="S29" s="2" t="s">
         <v>13</v>
@@ -3280,33 +3298,33 @@
         <v>13</v>
       </c>
       <c r="U29" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>198</v>
+        <v>70</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H30" s="2">
-        <v>3944</v>
+        <v>5586</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>24</v>
@@ -3342,26 +3360,28 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>199</v>
+        <v>72</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E31" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>145</v>
+      </c>
       <c r="F31" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H31" s="2">
-        <v>7133</v>
+        <v>6918</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>24</v>
@@ -3397,28 +3417,28 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>147</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H32" s="2">
-        <v>4285</v>
+        <v>3944</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>24</v>
@@ -3454,28 +3474,26 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>147</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H33" s="2">
-        <v>4880</v>
+        <v>7133</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>24</v>
@@ -3511,28 +3529,28 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>147</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H34" s="2">
-        <v>2880</v>
+        <v>4285</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>24</v>
@@ -3554,42 +3572,42 @@
       <c r="P34" s="2"/>
       <c r="Q34" s="2"/>
       <c r="R34" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T34" s="2" t="s">
         <v>13</v>
       </c>
       <c r="U34" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>203</v>
+        <v>81</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>201</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>147</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H35" s="2">
-        <v>8665</v>
+        <v>4880</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>24</v>
@@ -3611,7 +3629,7 @@
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
       <c r="R35" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="S35" s="2" t="s">
         <v>13</v>
@@ -3620,46 +3638,44 @@
         <v>13</v>
       </c>
       <c r="U35" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>150</v>
+        <v>82</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>202</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>100</v>
+        <v>147</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H36" s="2">
-        <v>7048</v>
+        <v>2880</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>5</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="L36" s="1"/>
       <c r="M36" s="2" t="s">
         <v>6</v>
       </c>
@@ -3673,61 +3689,57 @@
         <v>12</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U36" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>151</v>
+        <v>203</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>100</v>
+        <v>147</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H37" s="2">
-        <v>6364</v>
+        <v>8665</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>5</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="L37" s="1"/>
       <c r="M37" s="2" t="s">
         <v>6</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O37" s="2">
-        <v>7</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2" t="s">
@@ -3737,21 +3749,21 @@
         <v>13</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U37" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>106</v>
@@ -3766,7 +3778,7 @@
         <v>3</v>
       </c>
       <c r="H38" s="2">
-        <v>9472</v>
+        <v>7048</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>4</v>
@@ -3784,18 +3796,16 @@
         <v>6</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O38" s="2">
-        <v>47</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" s="2"/>
       <c r="Q38" s="2"/>
       <c r="R38" s="2" t="s">
         <v>12</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>12</v>
@@ -3806,13 +3816,13 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>106</v>
@@ -3827,7 +3837,7 @@
         <v>3</v>
       </c>
       <c r="H39" s="2">
-        <v>7045</v>
+        <v>6364</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>4</v>
@@ -3845,9 +3855,11 @@
         <v>6</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="O39" s="2">
+        <v>7</v>
+      </c>
       <c r="P39" s="2"/>
       <c r="Q39" s="2"/>
       <c r="R39" s="2" t="s">
@@ -3865,13 +3877,13 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>106</v>
@@ -3886,7 +3898,7 @@
         <v>3</v>
       </c>
       <c r="H40" s="2">
-        <v>10243</v>
+        <v>9472</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>4</v>
@@ -3907,7 +3919,7 @@
         <v>7</v>
       </c>
       <c r="O40" s="2">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
@@ -3915,7 +3927,7 @@
         <v>12</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T40" s="2" t="s">
         <v>12</v>
@@ -3926,13 +3938,13 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>106</v>
@@ -3947,7 +3959,7 @@
         <v>3</v>
       </c>
       <c r="H41" s="2">
-        <v>8355</v>
+        <v>7045</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>4</v>
@@ -3965,11 +3977,9 @@
         <v>6</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O41" s="2">
-        <v>25</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" s="2"/>
       <c r="Q41" s="2"/>
       <c r="R41" s="2" t="s">
@@ -3987,13 +3997,13 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>106</v>
@@ -4008,7 +4018,7 @@
         <v>3</v>
       </c>
       <c r="H42" s="2">
-        <v>7274</v>
+        <v>10243</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>4</v>
@@ -4029,7 +4039,7 @@
         <v>7</v>
       </c>
       <c r="O42" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P42" s="2"/>
       <c r="Q42" s="2"/>
@@ -4037,7 +4047,7 @@
         <v>12</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T42" s="2" t="s">
         <v>12</v>
@@ -4048,13 +4058,13 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>106</v>
@@ -4069,7 +4079,7 @@
         <v>3</v>
       </c>
       <c r="H43" s="2">
-        <v>8214</v>
+        <v>8355</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>4</v>
@@ -4090,7 +4100,7 @@
         <v>7</v>
       </c>
       <c r="O43" s="2">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="P43" s="2"/>
       <c r="Q43" s="2"/>
@@ -4109,46 +4119,50 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F44" s="2" t="s">
-        <v>30</v>
+      <c r="F44" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H44" s="2">
-        <v>6070</v>
+        <v>7274</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>5</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L44" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="M44" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="O44" s="2">
+        <v>10</v>
+      </c>
       <c r="P44" s="2"/>
       <c r="Q44" s="2"/>
       <c r="R44" s="2" t="s">
@@ -4158,54 +4172,58 @@
         <v>13</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U44" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>31</v>
+        <v>143</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H45" s="2">
-        <v>5667</v>
+        <v>8214</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>5</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L45" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="M45" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="O45" s="2">
+        <v>104</v>
+      </c>
       <c r="P45" s="2"/>
       <c r="Q45" s="2"/>
       <c r="R45" s="2" t="s">
@@ -4215,36 +4233,36 @@
         <v>13</v>
       </c>
       <c r="T45" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U45" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>104</v>
+        <v>30</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>143</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H46" s="2">
-        <v>5714</v>
+        <v>6070</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>28</v>
@@ -4280,22 +4298,22 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>103</v>
+        <v>31</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>3</v>
@@ -4337,28 +4355,28 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>117</v>
+        <v>32</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H48" s="2">
-        <v>4996</v>
+        <v>5714</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>28</v>
@@ -4394,28 +4412,28 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>118</v>
+        <v>33</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>103</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H49" s="2">
-        <v>3556</v>
+        <v>5667</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>28</v>
@@ -4437,7 +4455,7 @@
       <c r="P49" s="2"/>
       <c r="Q49" s="2"/>
       <c r="R49" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>13</v>
@@ -4446,33 +4464,33 @@
         <v>13</v>
       </c>
       <c r="U49" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H50" s="2">
-        <v>5343</v>
+        <v>4996</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>28</v>
@@ -4494,7 +4512,7 @@
       <c r="P50" s="2"/>
       <c r="Q50" s="2"/>
       <c r="R50" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="S50" s="2" t="s">
         <v>13</v>
@@ -4503,33 +4521,33 @@
         <v>13</v>
       </c>
       <c r="U50" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H51" s="2">
-        <v>5530</v>
+        <v>3556</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>28</v>
@@ -4551,7 +4569,7 @@
       <c r="P51" s="2"/>
       <c r="Q51" s="2"/>
       <c r="R51" s="2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="S51" s="2" t="s">
         <v>13</v>
@@ -4565,28 +4583,28 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H52" s="2">
-        <v>3329</v>
+        <v>5343</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>28</v>
@@ -4622,28 +4640,28 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H53" s="2">
-        <v>3037</v>
+        <v>5530</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>28</v>
@@ -4665,7 +4683,7 @@
       <c r="P53" s="2"/>
       <c r="Q53" s="2"/>
       <c r="R53" s="2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="S53" s="2" t="s">
         <v>13</v>
@@ -4679,28 +4697,28 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H54" s="2">
-        <v>5685</v>
+        <v>3329</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>28</v>
@@ -4722,7 +4740,7 @@
       <c r="P54" s="2"/>
       <c r="Q54" s="2"/>
       <c r="R54" s="2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="S54" s="2" t="s">
         <v>13</v>
@@ -4736,28 +4754,28 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>147</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H55" s="2">
-        <v>5023</v>
+        <v>3037</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>28</v>
@@ -4779,7 +4797,7 @@
       <c r="P55" s="2"/>
       <c r="Q55" s="2"/>
       <c r="R55" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="S55" s="2" t="s">
         <v>13</v>
@@ -4788,33 +4806,33 @@
         <v>13</v>
       </c>
       <c r="U55" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>143</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H56" s="2">
-        <v>6189</v>
+        <v>5685</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>28</v>
@@ -4850,28 +4868,28 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H57" s="2">
-        <v>5246</v>
+        <v>5023</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>28</v>
@@ -4880,7 +4898,7 @@
         <v>5</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="L57" s="1"/>
       <c r="M57" s="2" t="s">
@@ -4907,73 +4925,138 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
-        <v>226</v>
+        <v>43</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>228</v>
+        <v>169</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>226</v>
+        <v>43</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>227</v>
+        <v>140</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>143</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>226</v>
+        <v>43</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H58" s="2">
-        <v>9464</v>
+        <v>6189</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>5</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L58" s="1" t="s">
-        <v>225</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="L58" s="1"/>
       <c r="M58" s="2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O58" s="2">
-        <v>7</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" s="2"/>
       <c r="Q58" s="2"/>
       <c r="R58" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S58" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T58" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="U58" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A59" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="2">
+        <v>5246</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L59" s="1"/>
+      <c r="M59" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" s="2"/>
+      <c r="Q59" s="2"/>
+      <c r="R59" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="S58" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="T58" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U58" s="2">
-        <v>2</v>
+      <c r="S59" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T59" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="U59" s="2">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T57">
-    <sortCondition ref="I2:I57"/>
-    <sortCondition ref="K2:K57"/>
-    <sortCondition ref="L2:L57"/>
-    <sortCondition ref="C2:C57"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U59">
+    <sortCondition ref="I2:I59"/>
+    <sortCondition ref="K2:K59"/>
+    <sortCondition ref="L2:L59"/>
+    <sortCondition ref="C2:C59"/>
   </sortState>
   <conditionalFormatting sqref="U63:U1048576 U1:U48">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U49:U52">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -4985,7 +5068,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U49:U52">
+  <conditionalFormatting sqref="U53:U54">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -4997,7 +5080,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U53:U54">
+  <conditionalFormatting sqref="U55">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -5009,7 +5092,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U55">
+  <conditionalFormatting sqref="U56">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -5021,7 +5104,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U56">
+  <conditionalFormatting sqref="U57">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -5033,8 +5116,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U57">
-    <cfRule type="colorScale" priority="6">
+  <conditionalFormatting sqref="U58">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5045,7 +5128,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U58">
+  <conditionalFormatting sqref="U59">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/tabular/reference/herv_sublineage_data.xlsx
+++ b/tabular/reference/herv_sublineage_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05097530-0173-0D4A-A691-99FA59B25F84}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC672C2F-4121-4A43-9EB4-B2645F6BFAAB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="520" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="232">
   <si>
     <t>sequenceID</t>
   </si>
@@ -395,57 +395,6 @@
     <t>human endogenous retrovirus L74</t>
   </si>
   <si>
-    <t>mammalian endogenous retrovirus 101</t>
-  </si>
-  <si>
-    <t>mammalian endogenous retrovirus 21</t>
-  </si>
-  <si>
-    <t>mammalian endogenous retrovirus 31</t>
-  </si>
-  <si>
-    <t>mammalian endogenous retrovirus 34B</t>
-  </si>
-  <si>
-    <t>mammalian endogenous retrovirus 4</t>
-  </si>
-  <si>
-    <t>mammalian endogenous retrovirus 4B</t>
-  </si>
-  <si>
-    <t>mammalian endogenous retrovirus 61</t>
-  </si>
-  <si>
-    <t>mammalian endogenous retrovirus 65</t>
-  </si>
-  <si>
-    <t>mammalian endogenous retrovirus 89</t>
-  </si>
-  <si>
-    <t>mammalian endogenous retrovirus 41</t>
-  </si>
-  <si>
-    <t>mammalian endogenous retrovirus 57</t>
-  </si>
-  <si>
-    <t>mammalian endogenous retrovirus 83A</t>
-  </si>
-  <si>
-    <t>mammalian endogenous retrovirus 83B</t>
-  </si>
-  <si>
-    <t>mammalian endogenous retrovirus 84</t>
-  </si>
-  <si>
-    <t>mammalian endogenous retrovirus 52A</t>
-  </si>
-  <si>
-    <t>mammalian endogenous retrovirus 70</t>
-  </si>
-  <si>
-    <t>mammalian endogenous retrovirus 76</t>
-  </si>
-  <si>
     <t>curation_tier</t>
   </si>
   <si>
@@ -455,15 +404,9 @@
     <t>sublineage</t>
   </si>
   <si>
-    <t>sublineage?</t>
-  </si>
-  <si>
     <t>lineage?</t>
   </si>
   <si>
-    <t>dup (HERV-P)?</t>
-  </si>
-  <si>
     <t>fragsub</t>
   </si>
   <si>
@@ -602,15 +545,6 @@
     <t>ERV-1.Zeta.W9.G25</t>
   </si>
   <si>
-    <t>ERV-1.Zeta.W9.huersP1</t>
-  </si>
-  <si>
-    <t>ERV-1.Zeta.W9.huersP2</t>
-  </si>
-  <si>
-    <t>ERV-1.Zeta.W9.huersP3b</t>
-  </si>
-  <si>
     <t>ERV-1.Zeta.19</t>
   </si>
   <si>
@@ -720,6 +654,69 @@
   </si>
   <si>
     <t>ERV-1.Iota.ADP</t>
+  </si>
+  <si>
+    <t>medium reiteration frequency repeat 101</t>
+  </si>
+  <si>
+    <t>medium reiteration frequency repeat 21</t>
+  </si>
+  <si>
+    <t>medium reiteration frequency repeat 31</t>
+  </si>
+  <si>
+    <t>medium reiteration frequency repeat 34B</t>
+  </si>
+  <si>
+    <t>medium reiteration frequency repeat 4</t>
+  </si>
+  <si>
+    <t>medium reiteration frequency repeat 4B</t>
+  </si>
+  <si>
+    <t>medium reiteration frequency repeat 61</t>
+  </si>
+  <si>
+    <t>medium reiteration frequency repeat 65</t>
+  </si>
+  <si>
+    <t>medium reiteration frequency repeat 89</t>
+  </si>
+  <si>
+    <t>medium reiteration frequency repeat 52A</t>
+  </si>
+  <si>
+    <t>medium reiteration frequency repeat 41</t>
+  </si>
+  <si>
+    <t>medium reiteration frequency repeat 57</t>
+  </si>
+  <si>
+    <t>medium reiteration frequency repeat 83A</t>
+  </si>
+  <si>
+    <t>medium reiteration frequency repeat 83B</t>
+  </si>
+  <si>
+    <t>medium reiteration frequency repeat 84</t>
+  </si>
+  <si>
+    <t>medium reiteration frequency repeat 70</t>
+  </si>
+  <si>
+    <t>medium reiteration frequency repeat 76</t>
+  </si>
+  <si>
+    <t>sublineage? (HERV-P)</t>
+  </si>
+  <si>
+    <t>ERV-1.Zeta.huersP1</t>
+  </si>
+  <si>
+    <t>ERV-1.Zeta.P.huersP3b</t>
+  </si>
+  <si>
+    <t>ERV-1.Zeta.P.huersP2</t>
   </si>
 </sst>
 </file>
@@ -1618,7 +1615,7 @@
     <col min="2" max="2" width="27.5" customWidth="1"/>
     <col min="3" max="3" width="18.5" customWidth="1"/>
     <col min="4" max="4" width="50.1640625" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.6640625" customWidth="1"/>
     <col min="11" max="11" width="21" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1627,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>84</v>
@@ -1636,7 +1633,7 @@
         <v>85</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>98</v>
@@ -1684,7 +1681,7 @@
         <v>97</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">
@@ -1692,7 +1689,7 @@
         <v>99</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>99</v>
@@ -1701,7 +1698,7 @@
         <v>99</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>105</v>
@@ -1749,7 +1746,7 @@
         <v>26</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>26</v>
@@ -1758,7 +1755,7 @@
         <v>107</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>105</v>
@@ -1805,22 +1802,22 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>3</v>
@@ -1838,7 +1835,7 @@
         <v>25</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>6</v>
@@ -1866,22 +1863,22 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>3</v>
@@ -1896,7 +1893,7 @@
         <v>5</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="2" t="s">
@@ -1928,7 +1925,7 @@
         <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>45</v>
@@ -1937,7 +1934,7 @@
         <v>108</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>45</v>
@@ -1985,7 +1982,7 @@
         <v>47</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>47</v>
@@ -1994,7 +1991,7 @@
         <v>109</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>47</v>
@@ -2042,7 +2039,7 @@
         <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>48</v>
@@ -2099,7 +2096,7 @@
         <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>52</v>
@@ -2108,7 +2105,7 @@
         <v>111</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>52</v>
@@ -2156,7 +2153,7 @@
         <v>53</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>53</v>
@@ -2165,7 +2162,7 @@
         <v>112</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>53</v>
@@ -2213,7 +2210,7 @@
         <v>54</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>54</v>
@@ -2222,7 +2219,7 @@
         <v>113</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>54</v>
@@ -2272,7 +2269,7 @@
         <v>55</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>55</v>
@@ -2327,7 +2324,7 @@
         <v>56</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>56</v>
@@ -2336,7 +2333,7 @@
         <v>56</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>56</v>
@@ -2384,7 +2381,7 @@
         <v>57</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>57</v>
@@ -2393,7 +2390,7 @@
         <v>57</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>57</v>
@@ -2441,16 +2438,16 @@
         <v>58</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>58</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>124</v>
+        <v>211</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>58</v>
@@ -2498,16 +2495,16 @@
         <v>59</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>125</v>
+        <v>212</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>59</v>
@@ -2555,16 +2552,16 @@
         <v>60</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>126</v>
+        <v>213</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>60</v>
@@ -2612,16 +2609,16 @@
         <v>61</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>61</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>127</v>
+        <v>214</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>61</v>
@@ -2669,16 +2666,16 @@
         <v>62</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>62</v>
@@ -2726,16 +2723,16 @@
         <v>63</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>63</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>129</v>
+        <v>216</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>63</v>
@@ -2783,16 +2780,16 @@
         <v>64</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>130</v>
+        <v>217</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>64</v>
@@ -2840,16 +2837,16 @@
         <v>65</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>131</v>
+        <v>218</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>65</v>
@@ -2897,16 +2894,16 @@
         <v>66</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>66</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>132</v>
+        <v>219</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>66</v>
@@ -2954,7 +2951,7 @@
         <v>67</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>67</v>
@@ -2963,7 +2960,7 @@
         <v>67</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>67</v>
@@ -3011,16 +3008,16 @@
         <v>78</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>78</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>138</v>
+        <v>220</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>78</v>
@@ -3070,7 +3067,7 @@
         <v>73</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>73</v>
@@ -3079,7 +3076,7 @@
         <v>116</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>73</v>
@@ -3129,7 +3126,7 @@
         <v>74</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>74</v>
@@ -3138,7 +3135,7 @@
         <v>74</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>74</v>
@@ -3188,7 +3185,7 @@
         <v>75</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>75</v>
@@ -3197,7 +3194,7 @@
         <v>75</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>144</v>
+        <v>228</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>75</v>
@@ -3247,7 +3244,7 @@
         <v>76</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>76</v>
@@ -3256,7 +3253,7 @@
         <v>76</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>146</v>
+        <v>228</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>76</v>
@@ -3306,7 +3303,7 @@
         <v>70</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>70</v>
@@ -3315,7 +3312,7 @@
         <v>114</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>70</v>
@@ -3363,7 +3360,7 @@
         <v>72</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>72</v>
@@ -3372,7 +3369,7 @@
         <v>115</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>72</v>
@@ -3420,16 +3417,16 @@
         <v>77</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>133</v>
+        <v>221</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>77</v>
@@ -3477,15 +3474,17 @@
         <v>79</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E33" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="F33" s="2" t="s">
         <v>79</v>
       </c>
@@ -3532,16 +3531,16 @@
         <v>80</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>135</v>
+        <v>223</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>80</v>
@@ -3589,16 +3588,16 @@
         <v>81</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>81</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>136</v>
+        <v>224</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>81</v>
@@ -3646,16 +3645,16 @@
         <v>82</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>137</v>
+        <v>225</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>82</v>
@@ -3703,7 +3702,7 @@
         <v>83</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>83</v>
@@ -3712,7 +3711,7 @@
         <v>83</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>83</v>
@@ -3760,7 +3759,7 @@
         <v>8</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>8</v>
@@ -3769,7 +3768,7 @@
         <v>106</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>100</v>
@@ -3819,7 +3818,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>14</v>
@@ -3828,7 +3827,7 @@
         <v>106</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>100</v>
@@ -3880,7 +3879,7 @@
         <v>15</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>15</v>
@@ -3889,7 +3888,7 @@
         <v>106</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>100</v>
@@ -3941,7 +3940,7 @@
         <v>17</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>17</v>
@@ -3950,7 +3949,7 @@
         <v>106</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>100</v>
@@ -4000,7 +3999,7 @@
         <v>18</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>18</v>
@@ -4009,7 +4008,7 @@
         <v>106</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>100</v>
@@ -4061,7 +4060,7 @@
         <v>19</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>19</v>
@@ -4070,7 +4069,7 @@
         <v>106</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>100</v>
@@ -4122,7 +4121,7 @@
         <v>20</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>20</v>
@@ -4131,7 +4130,7 @@
         <v>106</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>100</v>
@@ -4183,7 +4182,7 @@
         <v>21</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>21</v>
@@ -4192,7 +4191,7 @@
         <v>106</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>100</v>
@@ -4244,7 +4243,7 @@
         <v>30</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>30</v>
@@ -4253,7 +4252,7 @@
         <v>30</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>30</v>
@@ -4301,7 +4300,7 @@
         <v>31</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>31</v>
@@ -4310,7 +4309,7 @@
         <v>101</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>31</v>
@@ -4358,7 +4357,7 @@
         <v>32</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>32</v>
@@ -4367,7 +4366,7 @@
         <v>104</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>32</v>
@@ -4415,7 +4414,7 @@
         <v>33</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>33</v>
@@ -4424,7 +4423,7 @@
         <v>103</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>33</v>
@@ -4472,7 +4471,7 @@
         <v>34</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>34</v>
@@ -4481,7 +4480,7 @@
         <v>117</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>34</v>
@@ -4529,7 +4528,7 @@
         <v>35</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>35</v>
@@ -4538,7 +4537,7 @@
         <v>118</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>35</v>
@@ -4586,7 +4585,7 @@
         <v>36</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>36</v>
@@ -4595,7 +4594,7 @@
         <v>119</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>36</v>
@@ -4643,7 +4642,7 @@
         <v>38</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>38</v>
@@ -4652,7 +4651,7 @@
         <v>120</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>38</v>
@@ -4700,7 +4699,7 @@
         <v>39</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>39</v>
@@ -4709,7 +4708,7 @@
         <v>121</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>39</v>
@@ -4757,7 +4756,7 @@
         <v>40</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>40</v>
@@ -4766,7 +4765,7 @@
         <v>122</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>40</v>
@@ -4814,7 +4813,7 @@
         <v>41</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>41</v>
@@ -4823,7 +4822,7 @@
         <v>123</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>41</v>
@@ -4871,16 +4870,16 @@
         <v>42</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>139</v>
+        <v>226</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>42</v>
@@ -4928,16 +4927,16 @@
         <v>43</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>140</v>
+        <v>227</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>43</v>
@@ -4985,7 +4984,7 @@
         <v>50</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -4994,7 +4993,7 @@
         <v>102</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>50</v>
@@ -5154,7 +5153,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>84</v>
@@ -5163,7 +5162,7 @@
         <v>85</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>98</v>
@@ -5211,27 +5210,27 @@
         <v>97</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>3</v>
@@ -5265,22 +5264,22 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>3</v>
@@ -5314,22 +5313,22 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>3</v>
@@ -5345,10 +5344,10 @@
         <v>25</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>7</v>
@@ -5373,22 +5372,22 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>3</v>
@@ -5404,10 +5403,10 @@
         <v>25</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>7</v>
@@ -5432,22 +5431,22 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>3</v>
@@ -5463,10 +5462,10 @@
         <v>25</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>7</v>

--- a/tabular/reference/herv_sublineage_data.xlsx
+++ b/tabular/reference/herv_sublineage_data.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A22FB3-E77A-A14B-A2C4-2A998CC7099D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D205A717-8EE7-B945-AB62-E252EA7B2FF3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1680" yWindow="520" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1680" yWindow="520" windowWidth="27120" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sublineage" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="255">
   <si>
     <t>sequenceID</t>
   </si>
@@ -761,6 +762,30 @@
   </si>
   <si>
     <t>retinoic acid-responsive human endogenous retrovirus I</t>
+  </si>
+  <si>
+    <t>HERV-K-HML6-1a</t>
+  </si>
+  <si>
+    <t>HERV-K-HML6-1b</t>
+  </si>
+  <si>
+    <t>ERV-2.Beta.K6</t>
+  </si>
+  <si>
+    <t>HERV-K-HML6</t>
+  </si>
+  <si>
+    <t>endogenous archeobetaretrovirus K Catarrhini type 6</t>
+  </si>
+  <si>
+    <t>lineage</t>
+  </si>
+  <si>
+    <t>Archaeobetaretrovirus kappacatarrhini6</t>
+  </si>
+  <si>
+    <t>Archaeobeta</t>
   </si>
 </sst>
 </file>
@@ -6412,4 +6437,273 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E84FD6B7-DAC0-EF4A-B6E8-A6FD2C634E5A}">
+  <dimension ref="A1:Z3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2">
+        <v>8214</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T2" s="2">
+        <v>20</v>
+      </c>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2">
+        <v>31167914</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2">
+        <v>8214</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T3" s="2">
+        <v>20</v>
+      </c>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2">
+        <v>31167914</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="Z2">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z1">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/tabular/reference/herv_sublineage_data.xlsx
+++ b/tabular/reference/herv_sublineage_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D205A717-8EE7-B945-AB62-E252EA7B2FF3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF22DFF-BEF6-1E4D-B5EB-62CA9800B731}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1680" yWindow="520" windowWidth="27120" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1680" yWindow="1120" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sublineage" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="256">
   <si>
     <t>sequenceID</t>
   </si>
@@ -779,13 +779,16 @@
     <t>endogenous archeobetaretrovirus K Catarrhini type 6</t>
   </si>
   <si>
-    <t>lineage</t>
-  </si>
-  <si>
-    <t>Archaeobetaretrovirus kappacatarrhini6</t>
-  </si>
-  <si>
     <t>Archaeobeta</t>
+  </si>
+  <si>
+    <t>lineage_id</t>
+  </si>
+  <si>
+    <t>ERV-2.Beta.K6.1a</t>
+  </si>
+  <si>
+    <t>ERV-2.Beta.K6.1b</t>
   </si>
 </sst>
 </file>
@@ -1687,7 +1690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB9083D8-DE01-F14E-ACB5-AF33867092C5}">
-  <dimension ref="A1:Z62"/>
+  <dimension ref="A1:Z57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -1710,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>169</v>
+        <v>253</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>82</v>
@@ -5125,19 +5128,19 @@
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>177</v>
+        <v>8</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>178</v>
+        <v>124</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>179</v>
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>245</v>
@@ -5154,41 +5157,43 @@
       <c r="J48" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K48" s="2" t="s">
-        <v>177</v>
+      <c r="K48" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="2"/>
+      <c r="M48" s="2">
+        <v>7048</v>
+      </c>
       <c r="N48" s="8" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="Q48" s="1" t="s">
-        <v>183</v>
+        <v>10</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>172</v>
+        <v>6</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T48" s="2"/>
       <c r="U48" s="2"/>
       <c r="V48" s="2">
-        <v>28397686</v>
+        <v>7692084</v>
       </c>
       <c r="W48" s="2" t="s">
         <v>12</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y48" s="2" t="s">
         <v>12</v>
@@ -5199,19 +5204,19 @@
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>180</v>
+        <v>14</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>181</v>
+        <v>125</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>182</v>
+        <v>14</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>245</v>
@@ -5228,41 +5233,45 @@
       <c r="J49" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K49" s="2" t="s">
-        <v>180</v>
+      <c r="K49" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="2"/>
+      <c r="M49" s="2">
+        <v>6364</v>
+      </c>
       <c r="N49" s="8" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="Q49" s="1" t="s">
-        <v>184</v>
+        <v>10</v>
       </c>
       <c r="R49" s="2" t="s">
-        <v>172</v>
+        <v>6</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="T49" s="2"/>
+      <c r="T49" s="2">
+        <v>7</v>
+      </c>
       <c r="U49" s="2"/>
       <c r="V49" s="2">
-        <v>28397686</v>
+        <v>19540319</v>
       </c>
       <c r="W49" s="2" t="s">
         <v>12</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y49" s="2" t="s">
         <v>12</v>
@@ -5273,19 +5282,19 @@
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>185</v>
+        <v>15</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>186</v>
+        <v>126</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>187</v>
+        <v>15</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>245</v>
@@ -5302,41 +5311,45 @@
       <c r="J50" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K50" s="2" t="s">
-        <v>185</v>
+      <c r="K50" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M50" s="2"/>
+      <c r="M50" s="2">
+        <v>9472</v>
+      </c>
       <c r="N50" s="8" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>188</v>
+        <v>10</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>172</v>
+        <v>6</v>
       </c>
       <c r="S50" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="T50" s="2"/>
+      <c r="T50" s="2">
+        <v>47</v>
+      </c>
       <c r="U50" s="2"/>
       <c r="V50" s="2">
-        <v>28397686</v>
+        <v>7692084</v>
       </c>
       <c r="W50" s="2" t="s">
         <v>12</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Y50" s="2" t="s">
         <v>12</v>
@@ -5347,19 +5360,19 @@
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>170</v>
+        <v>17</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>176</v>
+        <v>17</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>245</v>
@@ -5376,35 +5389,37 @@
       <c r="J51" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K51" s="2" t="s">
-        <v>170</v>
+      <c r="K51" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M51" s="2"/>
+      <c r="M51" s="2">
+        <v>7045</v>
+      </c>
       <c r="N51" s="8" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="Q51" s="1" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="T51" s="2"/>
       <c r="U51" s="2"/>
       <c r="V51" s="2">
-        <v>26952212</v>
+        <v>7692084</v>
       </c>
       <c r="W51" s="2" t="s">
         <v>12</v>
@@ -5413,27 +5428,27 @@
         <v>13</v>
       </c>
       <c r="Y51" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z51" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>173</v>
+        <v>18</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>174</v>
+        <v>128</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>175</v>
+        <v>18</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>245</v>
@@ -5450,58 +5465,62 @@
       <c r="J52" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K52" s="2" t="s">
-        <v>173</v>
+      <c r="K52" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="2"/>
+      <c r="M52" s="2">
+        <v>10243</v>
+      </c>
       <c r="N52" s="8" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="R52" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T52" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="T52" s="2">
+        <v>7</v>
+      </c>
       <c r="U52" s="2"/>
       <c r="V52" s="2">
-        <v>26952212</v>
+        <v>7692084</v>
       </c>
       <c r="W52" s="2" t="s">
         <v>12</v>
       </c>
       <c r="X52" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y52" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z52" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>104</v>
@@ -5531,7 +5550,7 @@
         <v>3</v>
       </c>
       <c r="M53" s="2">
-        <v>7048</v>
+        <v>8355</v>
       </c>
       <c r="N53" s="8" t="s">
         <v>4</v>
@@ -5549,12 +5568,14 @@
         <v>6</v>
       </c>
       <c r="S53" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="T53" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="T53" s="2">
+        <v>25</v>
+      </c>
       <c r="U53" s="2"/>
       <c r="V53" s="2">
-        <v>7692084</v>
+        <v>9934709</v>
       </c>
       <c r="W53" s="2" t="s">
         <v>12</v>
@@ -5571,13 +5592,13 @@
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>104</v>
@@ -5607,7 +5628,7 @@
         <v>3</v>
       </c>
       <c r="M54" s="2">
-        <v>6364</v>
+        <v>7274</v>
       </c>
       <c r="N54" s="8" t="s">
         <v>4</v>
@@ -5628,11 +5649,11 @@
         <v>7</v>
       </c>
       <c r="T54" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U54" s="2"/>
       <c r="V54" s="2">
-        <v>19540319</v>
+        <v>9934709</v>
       </c>
       <c r="W54" s="2" t="s">
         <v>12</v>
@@ -5649,13 +5670,13 @@
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>104</v>
@@ -5685,7 +5706,7 @@
         <v>3</v>
       </c>
       <c r="M55" s="2">
-        <v>9472</v>
+        <v>8214</v>
       </c>
       <c r="N55" s="8" t="s">
         <v>4</v>
@@ -5706,17 +5727,17 @@
         <v>7</v>
       </c>
       <c r="T55" s="2">
-        <v>47</v>
+        <v>104</v>
       </c>
       <c r="U55" s="2"/>
       <c r="V55" s="2">
-        <v>7692084</v>
+        <v>19540319</v>
       </c>
       <c r="W55" s="2" t="s">
         <v>12</v>
       </c>
       <c r="X55" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Y55" s="2" t="s">
         <v>12</v>
@@ -5727,19 +5748,19 @@
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>245</v>
@@ -5748,34 +5769,34 @@
         <v>121</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M56" s="2">
-        <v>7045</v>
+        <v>6896</v>
       </c>
       <c r="N56" s="8" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="Q56" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="R56" s="2" t="s">
         <v>6</v>
@@ -5785,9 +5806,7 @@
       </c>
       <c r="T56" s="2"/>
       <c r="U56" s="2"/>
-      <c r="V56" s="2">
-        <v>7692084</v>
-      </c>
+      <c r="V56" s="2"/>
       <c r="W56" s="2" t="s">
         <v>12</v>
       </c>
@@ -5795,27 +5814,27 @@
         <v>13</v>
       </c>
       <c r="Y56" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z56" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>245</v>
@@ -5824,450 +5843,64 @@
         <v>121</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>13</v>
+        <v>219</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>98</v>
+        <v>16</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M57" s="2">
-        <v>10243</v>
+        <v>5685</v>
       </c>
       <c r="N57" s="8" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q57" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="Q57" s="1"/>
       <c r="R57" s="2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="T57" s="2">
-        <v>7</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="T57" s="2"/>
       <c r="U57" s="2"/>
-      <c r="V57" s="2">
-        <v>7692084</v>
-      </c>
+      <c r="V57" s="2"/>
       <c r="W57" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="X57" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y57" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z57" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A58" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J58" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="L58" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="2">
-        <v>8355</v>
-      </c>
-      <c r="N58" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="O58" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="P58" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q58" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="R58" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="S58" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="T58" s="2">
-        <v>25</v>
-      </c>
-      <c r="U58" s="2"/>
-      <c r="V58" s="2">
-        <v>9934709</v>
-      </c>
-      <c r="W58" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="X58" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y58" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z58" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A59" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J59" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="L59" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="2">
-        <v>7274</v>
-      </c>
-      <c r="N59" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="O59" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="P59" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q59" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="R59" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="S59" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="T59" s="2">
-        <v>10</v>
-      </c>
-      <c r="U59" s="2"/>
-      <c r="V59" s="2">
-        <v>9934709</v>
-      </c>
-      <c r="W59" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="X59" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y59" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z59" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A60" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J60" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="L60" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="2">
-        <v>8214</v>
-      </c>
-      <c r="N60" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="O60" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="P60" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q60" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="R60" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="S60" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="T60" s="2">
-        <v>104</v>
-      </c>
-      <c r="U60" s="2"/>
-      <c r="V60" s="2">
-        <v>19540319</v>
-      </c>
-      <c r="W60" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="X60" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y60" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z60" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A61" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J61" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="L61" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M61" s="2">
-        <v>6896</v>
-      </c>
-      <c r="N61" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="O61" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="P61" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q61" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="R61" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="S61" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="T61" s="2"/>
-      <c r="U61" s="2"/>
-      <c r="V61" s="2"/>
-      <c r="W61" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="X61" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y61" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z61" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A62" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="J62" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K62" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L62" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="2">
-        <v>5685</v>
-      </c>
-      <c r="N62" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="O62" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="P62" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q62" s="1"/>
-      <c r="R62" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="S62" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="T62" s="2"/>
-      <c r="U62" s="2"/>
-      <c r="V62" s="2"/>
-      <c r="W62" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="X62" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y62" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z62" s="2">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z62">
-    <sortCondition ref="G2:G62"/>
-    <sortCondition ref="H2:H62"/>
-    <sortCondition ref="N2:N62"/>
-    <sortCondition ref="P2:P62"/>
-    <sortCondition ref="Q2:Q62"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z57">
+    <sortCondition ref="G2:G57"/>
+    <sortCondition ref="H2:H57"/>
+    <sortCondition ref="N2:N57"/>
+    <sortCondition ref="P2:P57"/>
+    <sortCondition ref="Q2:Q57"/>
   </sortState>
-  <conditionalFormatting sqref="Z63:Z1048576 Z1:Z45">
+  <conditionalFormatting sqref="Z58:Z1048576 Z1:Z45">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
@@ -6279,7 +5912,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z46:Z49">
+  <conditionalFormatting sqref="Z46:Z47">
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
@@ -6291,8 +5924,92 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z50:Z51">
-    <cfRule type="colorScale" priority="18">
+  <conditionalFormatting sqref="Z48">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z49">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z50">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z51">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z54">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z55">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z56">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z57">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6304,7 +6021,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z52">
-    <cfRule type="colorScale" priority="17">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6316,114 +6033,6 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z53">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z54">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z55">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z56">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z59">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z60">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z61">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z62">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z57">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z58">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6441,10 +6050,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E84FD6B7-DAC0-EF4A-B6E8-A6FD2C634E5A}">
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.1640625" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="4" max="4" width="40.5" customWidth="1"/>
+    <col min="5" max="5" width="21.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.2">
@@ -6532,7 +6144,7 @@
         <v>247</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>250</v>
@@ -6541,13 +6153,13 @@
         <v>251</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>3</v>
+        <v>121</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
@@ -6569,7 +6181,7 @@
         <v>9</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>6</v>
@@ -6602,7 +6214,7 @@
         <v>248</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>250</v>
@@ -6611,13 +6223,13 @@
         <v>251</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>3</v>
+        <v>121</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
@@ -6639,7 +6251,7 @@
         <v>9</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>6</v>
@@ -6667,8 +6279,426 @@
         <v>1</v>
       </c>
     </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="2"/>
+      <c r="N4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2">
+        <v>28397686</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" s="2"/>
+      <c r="N5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2">
+        <v>28397686</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M6" s="2"/>
+      <c r="N6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2">
+        <v>28397686</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2"/>
+      <c r="N7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2">
+        <v>26952212</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="2"/>
+      <c r="N8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2">
+        <v>26952212</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="Z2">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z1">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z4:Z5">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z6:Z7">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -6680,20 +6710,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z3">
+  <conditionalFormatting sqref="Z8">
     <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z1">
-    <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/tabular/reference/herv_sublineage_data.xlsx
+++ b/tabular/reference/herv_sublineage_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF22DFF-BEF6-1E4D-B5EB-62CA9800B731}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF0074D-C184-EF44-BC5D-A72E70D339C5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="1120" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -389,9 +389,6 @@
     <t>sublineage</t>
   </si>
   <si>
-    <t>ERV-1.Gamma.E1</t>
-  </si>
-  <si>
     <t>ERV-1.Gamma.HARLEQUIN</t>
   </si>
   <si>
@@ -593,9 +590,6 @@
     <t>RRHERV-I</t>
   </si>
   <si>
-    <t>ERV-1.Gamma.I</t>
-  </si>
-  <si>
     <t>Iotaretrovirus</t>
   </si>
   <si>
@@ -789,6 +783,12 @@
   </si>
   <si>
     <t>ERV-2.Beta.K6.1b</t>
+  </si>
+  <si>
+    <t>ERV-1.Gamma.R.1</t>
+  </si>
+  <si>
+    <t>ERV-1.Gamma.E.RR</t>
   </si>
 </sst>
 </file>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>82</v>
@@ -1722,22 +1722,22 @@
         <v>83</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>96</v>
@@ -1790,28 +1790,28 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>194</v>
-      </c>
       <c r="C2" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="G2" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>13</v>
@@ -1820,7 +1820,7 @@
         <v>13</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>3</v>
@@ -1835,7 +1835,7 @@
         <v>5</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Q2" s="1"/>
       <c r="R2" s="2" t="s">
@@ -1869,7 +1869,7 @@
         <v>74</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>74</v>
@@ -1878,16 +1878,16 @@
         <v>74</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>13</v>
@@ -1945,7 +1945,7 @@
         <v>31</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>31</v>
@@ -1954,22 +1954,22 @@
         <v>99</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>31</v>
@@ -2017,7 +2017,7 @@
         <v>32</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>32</v>
@@ -2026,16 +2026,16 @@
         <v>102</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>13</v>
@@ -2089,7 +2089,7 @@
         <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>33</v>
@@ -2098,16 +2098,16 @@
         <v>101</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>13</v>
@@ -2161,7 +2161,7 @@
         <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>49</v>
@@ -2170,22 +2170,22 @@
         <v>100</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>49</v>
@@ -2233,7 +2233,7 @@
         <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>122</v>
+        <v>254</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>26</v>
@@ -2242,16 +2242,16 @@
         <v>105</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>13</v>
@@ -2304,28 +2304,28 @@
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>190</v>
+        <v>255</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>13</v>
@@ -2383,7 +2383,7 @@
         <v>45</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>45</v>
@@ -2392,16 +2392,16 @@
         <v>106</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>16</v>
@@ -2455,7 +2455,7 @@
         <v>47</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>47</v>
@@ -2464,19 +2464,19 @@
         <v>107</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>16</v>
@@ -2527,7 +2527,7 @@
         <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>51</v>
@@ -2536,16 +2536,16 @@
         <v>108</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>13</v>
@@ -2599,7 +2599,7 @@
         <v>52</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>52</v>
@@ -2608,16 +2608,16 @@
         <v>109</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>16</v>
@@ -2671,7 +2671,7 @@
         <v>65</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>65</v>
@@ -2680,16 +2680,16 @@
         <v>65</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>16</v>
@@ -2743,25 +2743,25 @@
         <v>76</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>13</v>
@@ -2817,7 +2817,7 @@
         <v>71</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>71</v>
@@ -2826,19 +2826,19 @@
         <v>112</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>16</v>
@@ -2891,7 +2891,7 @@
         <v>73</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>73</v>
@@ -2900,19 +2900,19 @@
         <v>73</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -2967,7 +2967,7 @@
         <v>68</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>68</v>
@@ -2976,16 +2976,16 @@
         <v>110</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>16</v>
@@ -3039,7 +3039,7 @@
         <v>70</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>70</v>
@@ -3048,16 +3048,16 @@
         <v>111</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>16</v>
@@ -3111,7 +3111,7 @@
         <v>30</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>30</v>
@@ -3120,16 +3120,16 @@
         <v>30</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>13</v>
@@ -3183,7 +3183,7 @@
         <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>34</v>
@@ -3192,16 +3192,16 @@
         <v>113</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>13</v>
@@ -3255,7 +3255,7 @@
         <v>35</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>35</v>
@@ -3264,19 +3264,19 @@
         <v>114</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>16</v>
@@ -3327,7 +3327,7 @@
         <v>36</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>36</v>
@@ -3336,19 +3336,19 @@
         <v>115</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>16</v>
@@ -3399,7 +3399,7 @@
         <v>38</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>38</v>
@@ -3408,19 +3408,19 @@
         <v>116</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>16</v>
@@ -3471,7 +3471,7 @@
         <v>39</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>39</v>
@@ -3480,19 +3480,19 @@
         <v>117</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>16</v>
@@ -3543,7 +3543,7 @@
         <v>40</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>40</v>
@@ -3552,19 +3552,19 @@
         <v>118</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>16</v>
@@ -3615,7 +3615,7 @@
         <v>72</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>72</v>
@@ -3624,16 +3624,16 @@
         <v>72</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>16</v>
@@ -3691,7 +3691,7 @@
         <v>81</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>81</v>
@@ -3700,16 +3700,16 @@
         <v>81</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>13</v>
@@ -3763,7 +3763,7 @@
         <v>53</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>53</v>
@@ -3772,16 +3772,16 @@
         <v>53</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F29" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="H29" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>16</v>
@@ -3835,7 +3835,7 @@
         <v>54</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>54</v>
@@ -3844,16 +3844,16 @@
         <v>54</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F30" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="H30" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>16</v>
@@ -3907,7 +3907,7 @@
         <v>55</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>55</v>
@@ -3916,16 +3916,16 @@
         <v>55</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F31" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="H31" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>16</v>
@@ -3979,25 +3979,25 @@
         <v>56</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F32" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G32" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="H32" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>16</v>
@@ -4051,25 +4051,25 @@
         <v>57</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F33" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G33" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="H33" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>16</v>
@@ -4123,25 +4123,25 @@
         <v>58</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>58</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F34" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="H34" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>16</v>
@@ -4195,25 +4195,25 @@
         <v>59</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F35" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G35" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="H35" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>16</v>
@@ -4267,25 +4267,25 @@
         <v>60</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F36" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G36" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="H36" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>16</v>
@@ -4339,25 +4339,25 @@
         <v>61</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>61</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F37" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G37" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="H37" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>16</v>
@@ -4411,25 +4411,25 @@
         <v>62</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F38" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="H38" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>16</v>
@@ -4483,25 +4483,25 @@
         <v>63</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>63</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F39" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G39" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="H39" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>16</v>
@@ -4555,25 +4555,25 @@
         <v>64</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F40" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G40" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="H40" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>16</v>
@@ -4627,25 +4627,25 @@
         <v>75</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F41" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G41" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G41" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="H41" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>16</v>
@@ -4699,25 +4699,25 @@
         <v>77</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F42" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G42" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="H42" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>16</v>
@@ -4771,25 +4771,25 @@
         <v>78</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>78</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F43" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G43" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G43" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="H43" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>16</v>
@@ -4843,25 +4843,25 @@
         <v>79</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F44" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G44" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="H44" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>16</v>
@@ -4915,25 +4915,25 @@
         <v>80</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F45" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G45" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="H45" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>16</v>
@@ -4987,28 +4987,28 @@
         <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F46" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G46" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="H46" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>16</v>
@@ -5059,28 +5059,28 @@
         <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F47" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G47" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="H47" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>16</v>
@@ -5131,7 +5131,7 @@
         <v>8</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>8</v>
@@ -5140,16 +5140,16 @@
         <v>104</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>121</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>13</v>
@@ -5207,7 +5207,7 @@
         <v>14</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>14</v>
@@ -5216,16 +5216,16 @@
         <v>104</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>121</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>13</v>
@@ -5285,7 +5285,7 @@
         <v>15</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>15</v>
@@ -5294,16 +5294,16 @@
         <v>104</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>121</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>13</v>
@@ -5363,7 +5363,7 @@
         <v>17</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>17</v>
@@ -5372,16 +5372,16 @@
         <v>104</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>121</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>13</v>
@@ -5439,7 +5439,7 @@
         <v>18</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>18</v>
@@ -5448,16 +5448,16 @@
         <v>104</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>121</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>13</v>
@@ -5517,7 +5517,7 @@
         <v>19</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>19</v>
@@ -5526,16 +5526,16 @@
         <v>104</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>121</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>13</v>
@@ -5595,7 +5595,7 @@
         <v>20</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>20</v>
@@ -5604,16 +5604,16 @@
         <v>104</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>121</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>13</v>
@@ -5673,7 +5673,7 @@
         <v>21</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>21</v>
@@ -5682,16 +5682,16 @@
         <v>104</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>121</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>13</v>
@@ -5751,7 +5751,7 @@
         <v>97</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>97</v>
@@ -5760,16 +5760,16 @@
         <v>97</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>121</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>13</v>
@@ -5825,7 +5825,7 @@
         <v>41</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>41</v>
@@ -5834,19 +5834,19 @@
         <v>119</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>121</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>16</v>
@@ -6064,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>82</v>
@@ -6073,22 +6073,22 @@
         <v>83</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>96</v>
@@ -6141,22 +6141,22 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>121</v>
@@ -6181,7 +6181,7 @@
         <v>9</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>6</v>
@@ -6211,22 +6211,22 @@
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>250</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>121</v>
@@ -6251,7 +6251,7 @@
         <v>9</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>6</v>
@@ -6281,28 +6281,28 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>179</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>121</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>13</v>
@@ -6311,7 +6311,7 @@
         <v>13</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>3</v>
@@ -6327,10 +6327,10 @@
         <v>25</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>7</v>
@@ -6355,28 +6355,28 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>121</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>13</v>
@@ -6385,7 +6385,7 @@
         <v>13</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>3</v>
@@ -6401,10 +6401,10 @@
         <v>25</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="S5" s="2" t="s">
         <v>7</v>
@@ -6429,28 +6429,28 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>187</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>121</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>13</v>
@@ -6459,7 +6459,7 @@
         <v>13</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>3</v>
@@ -6475,10 +6475,10 @@
         <v>25</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="S6" s="2" t="s">
         <v>7</v>
@@ -6503,28 +6503,28 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>171</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>121</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>13</v>
@@ -6533,7 +6533,7 @@
         <v>13</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
@@ -6577,28 +6577,28 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>121</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>13</v>
@@ -6607,7 +6607,7 @@
         <v>13</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>3</v>

--- a/tabular/reference/herv_sublineage_data.xlsx
+++ b/tabular/reference/herv_sublineage_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF0074D-C184-EF44-BC5D-A72E70D339C5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E279405E-8A35-5046-8E3E-DB8AA22A23B9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="1120" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="263">
   <si>
     <t>sequenceID</t>
   </si>
@@ -335,9 +335,6 @@
     <t>Gammaretrovirus etacatarrhini</t>
   </si>
   <si>
-    <t>endogenous betaretrovirus K Catarrhini</t>
-  </si>
-  <si>
     <t>human endogenous retrovirus 1</t>
   </si>
   <si>
@@ -789,6 +786,30 @@
   </si>
   <si>
     <t>ERV-1.Gamma.E.RR</t>
+  </si>
+  <si>
+    <t>endogenous betaretrovirus K Catarrhini HML1</t>
+  </si>
+  <si>
+    <t>endogenous betaretrovirus K Catarrhini HML10</t>
+  </si>
+  <si>
+    <t>endogenous betaretrovirus K Catarrhini HML2</t>
+  </si>
+  <si>
+    <t>endogenous betaretrovirus K Catarrhini HML3</t>
+  </si>
+  <si>
+    <t>endogenous betaretrovirus K Catarrhini HML4</t>
+  </si>
+  <si>
+    <t>endogenous betaretrovirus K Catarrhini HML8</t>
+  </si>
+  <si>
+    <t>endogenous betaretrovirus K Catarrhini HML7</t>
+  </si>
+  <si>
+    <t>endogenous betaretrovirus K Catarrhini HML9</t>
   </si>
 </sst>
 </file>
@@ -1713,7 +1734,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>82</v>
@@ -1722,22 +1743,22 @@
         <v>83</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>214</v>
-      </c>
       <c r="I1" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>221</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>96</v>
@@ -1785,33 +1806,33 @@
         <v>95</v>
       </c>
       <c r="Z1" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>191</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>13</v>
@@ -1820,7 +1841,7 @@
         <v>13</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>3</v>
@@ -1835,7 +1856,7 @@
         <v>5</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q2" s="1"/>
       <c r="R2" s="2" t="s">
@@ -1869,7 +1890,7 @@
         <v>74</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>74</v>
@@ -1878,16 +1899,16 @@
         <v>74</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="H3" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>13</v>
@@ -1945,7 +1966,7 @@
         <v>31</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>31</v>
@@ -1954,22 +1975,22 @@
         <v>99</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>31</v>
@@ -2017,7 +2038,7 @@
         <v>32</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>32</v>
@@ -2026,16 +2047,16 @@
         <v>102</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>13</v>
@@ -2089,7 +2110,7 @@
         <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>33</v>
@@ -2098,16 +2119,16 @@
         <v>101</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>13</v>
@@ -2161,7 +2182,7 @@
         <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>49</v>
@@ -2170,22 +2191,22 @@
         <v>100</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H7" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>217</v>
-      </c>
       <c r="J7" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>49</v>
@@ -2233,25 +2254,25 @@
         <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>13</v>
@@ -2304,28 +2325,28 @@
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="H9" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>13</v>
@@ -2383,25 +2404,25 @@
         <v>45</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>16</v>
@@ -2455,28 +2476,28 @@
         <v>47</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>47</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="H11" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>16</v>
@@ -2527,25 +2548,25 @@
         <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="H12" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>13</v>
@@ -2599,25 +2620,25 @@
         <v>52</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>16</v>
@@ -2671,7 +2692,7 @@
         <v>65</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>65</v>
@@ -2680,16 +2701,16 @@
         <v>65</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F14" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="H14" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>16</v>
@@ -2743,25 +2764,25 @@
         <v>76</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F15" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="H15" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>13</v>
@@ -2817,28 +2838,28 @@
         <v>71</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F16" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="H16" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>16</v>
@@ -2891,7 +2912,7 @@
         <v>73</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>73</v>
@@ -2900,19 +2921,19 @@
         <v>73</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F17" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="H17" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -2967,25 +2988,25 @@
         <v>68</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F18" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="H18" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>16</v>
@@ -3039,25 +3060,25 @@
         <v>70</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F19" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="H19" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>16</v>
@@ -3111,7 +3132,7 @@
         <v>30</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>30</v>
@@ -3120,16 +3141,16 @@
         <v>30</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F20" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="H20" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>13</v>
@@ -3183,25 +3204,25 @@
         <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F21" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="H21" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>13</v>
@@ -3255,28 +3276,28 @@
         <v>35</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F22" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="H22" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>16</v>
@@ -3327,28 +3348,28 @@
         <v>36</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F23" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="H23" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>16</v>
@@ -3399,28 +3420,28 @@
         <v>38</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F24" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="H24" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>16</v>
@@ -3471,28 +3492,28 @@
         <v>39</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F25" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="H25" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>16</v>
@@ -3543,28 +3564,28 @@
         <v>40</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F26" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="H26" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>16</v>
@@ -3615,7 +3636,7 @@
         <v>72</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>72</v>
@@ -3624,16 +3645,16 @@
         <v>72</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>16</v>
@@ -3691,7 +3712,7 @@
         <v>81</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>81</v>
@@ -3700,16 +3721,16 @@
         <v>81</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>13</v>
@@ -3763,7 +3784,7 @@
         <v>53</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>53</v>
@@ -3772,16 +3793,16 @@
         <v>53</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>16</v>
@@ -3835,7 +3856,7 @@
         <v>54</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>54</v>
@@ -3844,16 +3865,16 @@
         <v>54</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>16</v>
@@ -3907,7 +3928,7 @@
         <v>55</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>55</v>
@@ -3916,16 +3937,16 @@
         <v>55</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>16</v>
@@ -3979,25 +4000,25 @@
         <v>56</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>16</v>
@@ -4051,25 +4072,25 @@
         <v>57</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>16</v>
@@ -4123,25 +4144,25 @@
         <v>58</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>58</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>16</v>
@@ -4195,25 +4216,25 @@
         <v>59</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>16</v>
@@ -4267,25 +4288,25 @@
         <v>60</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>16</v>
@@ -4339,25 +4360,25 @@
         <v>61</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>61</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>16</v>
@@ -4411,25 +4432,25 @@
         <v>62</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>16</v>
@@ -4483,25 +4504,25 @@
         <v>63</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>63</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>16</v>
@@ -4555,25 +4576,25 @@
         <v>64</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>16</v>
@@ -4627,25 +4648,25 @@
         <v>75</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>16</v>
@@ -4699,25 +4720,25 @@
         <v>77</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>16</v>
@@ -4771,25 +4792,25 @@
         <v>78</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>78</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>16</v>
@@ -4843,25 +4864,25 @@
         <v>79</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>16</v>
@@ -4915,25 +4936,25 @@
         <v>80</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>16</v>
@@ -4987,28 +5008,28 @@
         <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H46" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I46" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>16</v>
@@ -5059,28 +5080,28 @@
         <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H47" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I47" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>16</v>
@@ -5131,25 +5152,25 @@
         <v>8</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>104</v>
+        <v>255</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>13</v>
@@ -5207,25 +5228,25 @@
         <v>14</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>104</v>
+        <v>256</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>13</v>
@@ -5285,25 +5306,25 @@
         <v>15</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>104</v>
+        <v>257</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>13</v>
@@ -5363,25 +5384,25 @@
         <v>17</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>104</v>
+        <v>258</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>13</v>
@@ -5439,25 +5460,25 @@
         <v>18</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>104</v>
+        <v>259</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>13</v>
@@ -5517,25 +5538,25 @@
         <v>19</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>104</v>
+        <v>261</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>13</v>
@@ -5595,25 +5616,25 @@
         <v>20</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>104</v>
+        <v>260</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>13</v>
@@ -5673,25 +5694,25 @@
         <v>21</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>104</v>
+        <v>262</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>13</v>
@@ -5751,7 +5772,7 @@
         <v>97</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>97</v>
@@ -5760,16 +5781,16 @@
         <v>97</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>13</v>
@@ -5825,28 +5846,28 @@
         <v>41</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>41</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H57" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I57" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>16</v>
@@ -6064,7 +6085,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>82</v>
@@ -6073,22 +6094,22 @@
         <v>83</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>214</v>
-      </c>
       <c r="I1" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>221</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>96</v>
@@ -6136,30 +6157,30 @@
         <v>95</v>
       </c>
       <c r="Z1" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
@@ -6181,7 +6202,7 @@
         <v>9</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>6</v>
@@ -6211,25 +6232,25 @@
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>247</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
@@ -6251,7 +6272,7 @@
         <v>9</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>6</v>
@@ -6281,28 +6302,28 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>13</v>
@@ -6311,7 +6332,7 @@
         <v>13</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>3</v>
@@ -6327,10 +6348,10 @@
         <v>25</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>7</v>
@@ -6355,28 +6376,28 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>13</v>
@@ -6385,7 +6406,7 @@
         <v>13</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>3</v>
@@ -6401,10 +6422,10 @@
         <v>25</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="S5" s="2" t="s">
         <v>7</v>
@@ -6429,28 +6450,28 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>13</v>
@@ -6459,7 +6480,7 @@
         <v>13</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>3</v>
@@ -6475,10 +6496,10 @@
         <v>25</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="S6" s="2" t="s">
         <v>7</v>
@@ -6503,28 +6524,28 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>13</v>
@@ -6533,7 +6554,7 @@
         <v>13</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
@@ -6577,28 +6598,28 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>13</v>
@@ -6607,7 +6628,7 @@
         <v>13</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>3</v>

--- a/tabular/reference/herv_sublineage_data.xlsx
+++ b/tabular/reference/herv_sublineage_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E279405E-8A35-5046-8E3E-DB8AA22A23B9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D718F7D-E69C-FA47-B064-EA56DCC2955D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1680" yWindow="1120" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1680" yWindow="1560" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sublineage" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="255">
   <si>
     <t>sequenceID</t>
   </si>
@@ -584,21 +584,6 @@
     <t>HERVT3</t>
   </si>
   <si>
-    <t>RRHERV-I</t>
-  </si>
-  <si>
-    <t>Iotaretrovirus</t>
-  </si>
-  <si>
-    <t>HERV-ADP</t>
-  </si>
-  <si>
-    <t>human endogenous retrovirus ADP</t>
-  </si>
-  <si>
-    <t>ERV-1.Iota.ADP</t>
-  </si>
-  <si>
     <t>medium reiteration frequency repeat 101</t>
   </si>
   <si>
@@ -743,18 +728,12 @@
     <t>ERV-1.Zeta.W9</t>
   </si>
   <si>
-    <t>ERV-1.Iota</t>
-  </si>
-  <si>
     <t>relationship</t>
   </si>
   <si>
     <t>sublineage_of</t>
   </si>
   <si>
-    <t>retinoic acid-responsive human endogenous retrovirus I</t>
-  </si>
-  <si>
     <t>HERV-K-HML6-1a</t>
   </si>
   <si>
@@ -783,9 +762,6 @@
   </si>
   <si>
     <t>ERV-1.Gamma.R.1</t>
-  </si>
-  <si>
-    <t>ERV-1.Gamma.E.RR</t>
   </si>
   <si>
     <t>endogenous betaretrovirus K Catarrhini HML1</t>
@@ -1711,7 +1687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB9083D8-DE01-F14E-ACB5-AF33867092C5}">
-  <dimension ref="A1:Z57"/>
+  <dimension ref="A1:Z55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -1734,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>82</v>
@@ -1743,22 +1719,22 @@
         <v>83</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>96</v>
@@ -1811,28 +1787,28 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>189</v>
+        <v>74</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>189</v>
+        <v>74</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>190</v>
+        <v>74</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>13</v>
@@ -1841,13 +1817,13 @@
         <v>13</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>189</v>
+        <v>74</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M2" s="2">
-        <v>7590</v>
+        <v>7418</v>
       </c>
       <c r="N2" s="8" t="s">
         <v>24</v>
@@ -1856,30 +1832,30 @@
         <v>5</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q2" s="1"/>
+        <v>66</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="R2" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="T2" s="2">
-        <v>1</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="T2" s="2"/>
       <c r="U2" s="2"/>
-      <c r="V2" s="2">
-        <v>7904581</v>
+      <c r="V2" s="10">
+        <v>2825129</v>
       </c>
       <c r="W2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z2" s="2">
         <v>2</v>
@@ -1887,67 +1863,63 @@
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>214</v>
-      </c>
       <c r="I3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>13</v>
+        <v>211</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M3" s="2">
-        <v>7418</v>
+        <v>5667</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>69</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="Q3" s="1"/>
       <c r="R3" s="2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
-      <c r="V3" s="10">
-        <v>2825129</v>
-      </c>
+      <c r="V3" s="2"/>
       <c r="W3" s="2" t="s">
         <v>12</v>
       </c>
@@ -1963,43 +1935,43 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>99</v>
+        <v>32</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>102</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>130</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>216</v>
+        <v>16</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M4" s="2">
-        <v>5667</v>
+        <v>5714</v>
       </c>
       <c r="N4" s="8" t="s">
         <v>28</v>
@@ -2035,28 +2007,28 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>130</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>217</v>
+        <v>236</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>13</v>
@@ -2065,13 +2037,13 @@
         <v>16</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M5" s="2">
-        <v>5714</v>
+        <v>5667</v>
       </c>
       <c r="N5" s="8" t="s">
         <v>28</v>
@@ -2107,43 +2079,43 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>101</v>
+        <v>49</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>130</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>217</v>
+        <v>236</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>212</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>13</v>
+        <v>211</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>16</v>
+        <v>211</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M6" s="2">
-        <v>5667</v>
+        <v>5246</v>
       </c>
       <c r="N6" s="8" t="s">
         <v>28</v>
@@ -2152,7 +2124,7 @@
         <v>5</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="Q6" s="1"/>
       <c r="R6" s="2" t="s">
@@ -2174,61 +2146,63 @@
         <v>13</v>
       </c>
       <c r="Z6" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>142</v>
+        <v>246</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>130</v>
+        <v>232</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>49</v>
+        <v>16</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M7" s="2">
-        <v>5246</v>
+        <v>9611</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q7" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="R7" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>11</v>
@@ -2246,48 +2220,48 @@
         <v>13</v>
       </c>
       <c r="Z7" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>253</v>
+        <v>144</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>104</v>
+        <v>45</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>103</v>
+      <c r="K8" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M8" s="2">
-        <v>9611</v>
+        <v>4936</v>
       </c>
       <c r="N8" s="8" t="s">
         <v>24</v>
@@ -2296,11 +2270,9 @@
         <v>5</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>27</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="Q8" s="1"/>
       <c r="R8" s="2" t="s">
         <v>6</v>
       </c>
@@ -2311,7 +2283,7 @@
       <c r="U8" s="2"/>
       <c r="V8" s="2"/>
       <c r="W8" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="X8" s="2" t="s">
         <v>13</v>
@@ -2320,48 +2292,48 @@
         <v>13</v>
       </c>
       <c r="Z8" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>187</v>
+        <v>47</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>254</v>
+        <v>145</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>243</v>
+        <v>47</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>13</v>
+        <v>211</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>103</v>
+        <v>16</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M9" s="2">
-        <v>9464</v>
+        <v>9084</v>
       </c>
       <c r="N9" s="8" t="s">
         <v>24</v>
@@ -2370,74 +2342,70 @@
         <v>5</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>27</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="Q9" s="1"/>
       <c r="R9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="T9" s="2">
-        <v>7</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="T9" s="2"/>
       <c r="U9" s="2"/>
       <c r="V9" s="2"/>
       <c r="W9" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y9" s="2" t="s">
         <v>13</v>
       </c>
       <c r="Z9" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M10" s="2">
-        <v>4936</v>
+        <v>7613</v>
       </c>
       <c r="N10" s="8" t="s">
         <v>24</v>
@@ -2446,7 +2414,7 @@
         <v>5</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="Q10" s="1"/>
       <c r="R10" s="2" t="s">
@@ -2459,7 +2427,7 @@
       <c r="U10" s="2"/>
       <c r="V10" s="2"/>
       <c r="W10" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="X10" s="2" t="s">
         <v>13</v>
@@ -2468,48 +2436,48 @@
         <v>13</v>
       </c>
       <c r="Z10" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>216</v>
+        <v>16</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M11" s="2">
-        <v>9084</v>
+        <v>1786</v>
       </c>
       <c r="N11" s="8" t="s">
         <v>24</v>
@@ -2518,7 +2486,7 @@
         <v>5</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="Q11" s="1"/>
       <c r="R11" s="2" t="s">
@@ -2545,43 +2513,43 @@
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>107</v>
+        <v>65</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M12" s="2">
-        <v>7613</v>
+        <v>4102</v>
       </c>
       <c r="N12" s="8" t="s">
         <v>24</v>
@@ -2606,7 +2574,7 @@
         <v>12</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y12" s="2" t="s">
         <v>13</v>
@@ -2617,43 +2585,43 @@
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>108</v>
+        <v>76</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>196</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M13" s="2">
-        <v>1786</v>
+        <v>4981</v>
       </c>
       <c r="N13" s="8" t="s">
         <v>24</v>
@@ -2662,9 +2630,11 @@
         <v>5</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q13" s="1"/>
+        <v>66</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="R13" s="2" t="s">
         <v>6</v>
       </c>
@@ -2675,7 +2645,7 @@
       <c r="U13" s="2"/>
       <c r="V13" s="2"/>
       <c r="W13" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="X13" s="2" t="s">
         <v>13</v>
@@ -2684,48 +2654,48 @@
         <v>13</v>
       </c>
       <c r="Z13" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>16</v>
+        <v>211</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M14" s="2">
-        <v>4102</v>
+        <v>6996</v>
       </c>
       <c r="N14" s="8" t="s">
         <v>24</v>
@@ -2734,9 +2704,11 @@
         <v>5</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q14" s="1"/>
+        <v>66</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="R14" s="2" t="s">
         <v>6</v>
       </c>
@@ -2750,7 +2722,7 @@
         <v>12</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y14" s="2" t="s">
         <v>13</v>
@@ -2761,43 +2733,43 @@
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>157</v>
+        <v>206</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>201</v>
+        <v>73</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>13</v>
+        <v>211</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M15" s="2">
-        <v>4981</v>
+        <v>8987</v>
       </c>
       <c r="N15" s="8" t="s">
         <v>24</v>
@@ -2809,7 +2781,7 @@
         <v>66</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="R15" s="2" t="s">
         <v>6</v>
@@ -2819,9 +2791,11 @@
       </c>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
-      <c r="V15" s="2"/>
+      <c r="V15" s="10">
+        <v>2825129</v>
+      </c>
       <c r="W15" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="X15" s="2" t="s">
         <v>13</v>
@@ -2830,48 +2804,48 @@
         <v>13</v>
       </c>
       <c r="Z15" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>111</v>
+        <v>68</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>216</v>
+        <v>16</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M16" s="2">
-        <v>6996</v>
+        <v>5586</v>
       </c>
       <c r="N16" s="8" t="s">
         <v>24</v>
@@ -2882,9 +2856,7 @@
       <c r="P16" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="Q16" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="Q16" s="1"/>
       <c r="R16" s="2" t="s">
         <v>6</v>
       </c>
@@ -2895,7 +2867,7 @@
       <c r="U16" s="2"/>
       <c r="V16" s="2"/>
       <c r="W16" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="X16" s="2" t="s">
         <v>13</v>
@@ -2904,48 +2876,48 @@
         <v>13</v>
       </c>
       <c r="Z16" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>216</v>
-      </c>
       <c r="G17" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>216</v>
+        <v>16</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M17" s="2">
-        <v>8987</v>
+        <v>6918</v>
       </c>
       <c r="N17" s="8" t="s">
         <v>24</v>
@@ -2956,9 +2928,7 @@
       <c r="P17" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="Q17" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="Q17" s="1"/>
       <c r="R17" s="2" t="s">
         <v>6</v>
       </c>
@@ -2967,9 +2937,7 @@
       </c>
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
-      <c r="V17" s="10">
-        <v>2825129</v>
-      </c>
+      <c r="V17" s="2"/>
       <c r="W17" s="2" t="s">
         <v>46</v>
       </c>
@@ -2983,58 +2951,58 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:26" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>109</v>
+        <v>30</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M18" s="2">
-        <v>5586</v>
+        <v>6070</v>
       </c>
       <c r="N18" s="8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="Q18" s="1"/>
       <c r="R18" s="2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="S18" s="2" t="s">
         <v>11</v>
@@ -3043,7 +3011,7 @@
       <c r="U18" s="2"/>
       <c r="V18" s="2"/>
       <c r="W18" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="X18" s="2" t="s">
         <v>13</v>
@@ -3052,61 +3020,61 @@
         <v>13</v>
       </c>
       <c r="Z18" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M19" s="2">
-        <v>6918</v>
+        <v>4996</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="Q19" s="1"/>
       <c r="R19" s="2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="S19" s="2" t="s">
         <v>11</v>
@@ -3115,7 +3083,7 @@
       <c r="U19" s="2"/>
       <c r="V19" s="2"/>
       <c r="W19" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="X19" s="2" t="s">
         <v>13</v>
@@ -3124,48 +3092,48 @@
         <v>13</v>
       </c>
       <c r="Z19" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:26" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>13</v>
+        <v>211</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M20" s="2">
-        <v>6070</v>
+        <v>3556</v>
       </c>
       <c r="N20" s="8" t="s">
         <v>28</v>
@@ -3187,7 +3155,7 @@
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
       <c r="W20" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="X20" s="2" t="s">
         <v>13</v>
@@ -3196,48 +3164,48 @@
         <v>13</v>
       </c>
       <c r="Z20" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>212</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>13</v>
+        <v>211</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M21" s="2">
-        <v>4996</v>
+        <v>5343</v>
       </c>
       <c r="N21" s="8" t="s">
         <v>28</v>
@@ -3259,7 +3227,7 @@
       <c r="U21" s="2"/>
       <c r="V21" s="2"/>
       <c r="W21" s="2" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="X21" s="2" t="s">
         <v>13</v>
@@ -3268,48 +3236,48 @@
         <v>13</v>
       </c>
       <c r="Z21" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>212</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M22" s="2">
-        <v>3556</v>
+        <v>5530</v>
       </c>
       <c r="N22" s="8" t="s">
         <v>28</v>
@@ -3331,7 +3299,7 @@
       <c r="U22" s="2"/>
       <c r="V22" s="2"/>
       <c r="W22" s="2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="X22" s="2" t="s">
         <v>13</v>
@@ -3345,43 +3313,43 @@
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M23" s="2">
-        <v>5343</v>
+        <v>3329</v>
       </c>
       <c r="N23" s="8" t="s">
         <v>28</v>
@@ -3417,43 +3385,43 @@
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M24" s="2">
-        <v>5530</v>
+        <v>3037</v>
       </c>
       <c r="N24" s="8" t="s">
         <v>28</v>
@@ -3475,7 +3443,7 @@
       <c r="U24" s="2"/>
       <c r="V24" s="2"/>
       <c r="W24" s="2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="X24" s="2" t="s">
         <v>13</v>
@@ -3489,65 +3457,69 @@
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>136</v>
+        <v>204</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>217</v>
+        <v>236</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>212</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>216</v>
+        <v>16</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M25" s="2">
-        <v>3329</v>
+        <v>11027</v>
       </c>
       <c r="N25" s="8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q25" s="1"/>
+        <v>66</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="R25" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="S25" s="2" t="s">
         <v>11</v>
       </c>
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
-      <c r="V25" s="2"/>
+      <c r="V25" s="2">
+        <v>2825129</v>
+      </c>
       <c r="W25" s="2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="X25" s="2" t="s">
         <v>13</v>
@@ -3561,56 +3533,56 @@
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>217</v>
+        <v>236</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>213</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M26" s="2">
-        <v>3037</v>
+        <v>8665</v>
       </c>
       <c r="N26" s="8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="Q26" s="1"/>
       <c r="R26" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="S26" s="2" t="s">
         <v>11</v>
@@ -3619,7 +3591,7 @@
       <c r="U26" s="2"/>
       <c r="V26" s="2"/>
       <c r="W26" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="X26" s="2" t="s">
         <v>13</v>
@@ -3628,48 +3600,48 @@
         <v>13</v>
       </c>
       <c r="Z26" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>209</v>
+        <v>148</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M27" s="2">
-        <v>11027</v>
+        <v>8120</v>
       </c>
       <c r="N27" s="8" t="s">
         <v>24</v>
@@ -3678,11 +3650,9 @@
         <v>5</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>69</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q27" s="1"/>
       <c r="R27" s="2" t="s">
         <v>6</v>
       </c>
@@ -3691,9 +3661,7 @@
       </c>
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
-      <c r="V27" s="2">
-        <v>2825129</v>
-      </c>
+      <c r="V27" s="2"/>
       <c r="W27" s="2" t="s">
         <v>46</v>
       </c>
@@ -3709,43 +3677,43 @@
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M28" s="2">
-        <v>8665</v>
+        <v>4060</v>
       </c>
       <c r="N28" s="8" t="s">
         <v>24</v>
@@ -3754,7 +3722,7 @@
         <v>5</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="Q28" s="1"/>
       <c r="R28" s="2" t="s">
@@ -3767,7 +3735,7 @@
       <c r="U28" s="2"/>
       <c r="V28" s="2"/>
       <c r="W28" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="X28" s="2" t="s">
         <v>13</v>
@@ -3776,33 +3744,33 @@
         <v>13</v>
       </c>
       <c r="Z28" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>16</v>
@@ -3811,13 +3779,13 @@
         <v>16</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M29" s="2">
-        <v>8120</v>
+        <v>4798</v>
       </c>
       <c r="N29" s="8" t="s">
         <v>24</v>
@@ -3853,28 +3821,28 @@
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>16</v>
@@ -3883,13 +3851,13 @@
         <v>16</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M30" s="2">
-        <v>4060</v>
+        <v>6639</v>
       </c>
       <c r="N30" s="8" t="s">
         <v>24</v>
@@ -3925,28 +3893,28 @@
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>150</v>
+        <v>221</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>55</v>
+        <v>188</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>16</v>
@@ -3955,13 +3923,13 @@
         <v>16</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M31" s="2">
-        <v>4798</v>
+        <v>933</v>
       </c>
       <c r="N31" s="8" t="s">
         <v>24</v>
@@ -3997,28 +3965,28 @@
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>16</v>
@@ -4027,13 +3995,13 @@
         <v>16</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M32" s="2">
-        <v>6639</v>
+        <v>4936</v>
       </c>
       <c r="N32" s="8" t="s">
         <v>24</v>
@@ -4069,28 +4037,28 @@
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>16</v>
@@ -4099,13 +4067,13 @@
         <v>16</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M33" s="2">
-        <v>933</v>
+        <v>5356</v>
       </c>
       <c r="N33" s="8" t="s">
         <v>24</v>
@@ -4141,28 +4109,28 @@
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>225</v>
+        <v>60</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>152</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>16</v>
@@ -4171,13 +4139,13 @@
         <v>16</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M34" s="2">
-        <v>4936</v>
+        <v>6387</v>
       </c>
       <c r="N34" s="8" t="s">
         <v>24</v>
@@ -4213,28 +4181,28 @@
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>224</v>
+        <v>61</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>153</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>16</v>
@@ -4243,13 +4211,13 @@
         <v>16</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M35" s="2">
-        <v>5356</v>
+        <v>6758</v>
       </c>
       <c r="N35" s="8" t="s">
         <v>24</v>
@@ -4285,28 +4253,28 @@
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>16</v>
@@ -4315,13 +4283,13 @@
         <v>16</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M36" s="2">
-        <v>6387</v>
+        <v>5217</v>
       </c>
       <c r="N36" s="8" t="s">
         <v>24</v>
@@ -4357,28 +4325,28 @@
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>153</v>
+        <v>218</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>16</v>
@@ -4387,13 +4355,13 @@
         <v>16</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M37" s="2">
-        <v>6758</v>
+        <v>4871</v>
       </c>
       <c r="N37" s="8" t="s">
         <v>24</v>
@@ -4418,7 +4386,7 @@
         <v>46</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y37" s="2" t="s">
         <v>13</v>
@@ -4429,28 +4397,28 @@
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>16</v>
@@ -4459,13 +4427,13 @@
         <v>16</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M38" s="2">
-        <v>5217</v>
+        <v>7048</v>
       </c>
       <c r="N38" s="8" t="s">
         <v>24</v>
@@ -4501,28 +4469,28 @@
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>16</v>
@@ -4531,13 +4499,13 @@
         <v>16</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M39" s="2">
-        <v>4871</v>
+        <v>3944</v>
       </c>
       <c r="N39" s="8" t="s">
         <v>24</v>
@@ -4546,7 +4514,7 @@
         <v>5</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="Q39" s="1"/>
       <c r="R39" s="2" t="s">
@@ -4562,7 +4530,7 @@
         <v>46</v>
       </c>
       <c r="X39" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y39" s="2" t="s">
         <v>13</v>
@@ -4573,28 +4541,28 @@
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>16</v>
@@ -4603,13 +4571,13 @@
         <v>16</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M40" s="2">
-        <v>7048</v>
+        <v>7133</v>
       </c>
       <c r="N40" s="8" t="s">
         <v>24</v>
@@ -4618,7 +4586,7 @@
         <v>5</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="Q40" s="1"/>
       <c r="R40" s="2" t="s">
@@ -4645,28 +4613,28 @@
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>16</v>
@@ -4675,13 +4643,13 @@
         <v>16</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M41" s="2">
-        <v>3944</v>
+        <v>4285</v>
       </c>
       <c r="N41" s="8" t="s">
         <v>24</v>
@@ -4717,28 +4685,28 @@
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>16</v>
@@ -4747,13 +4715,13 @@
         <v>16</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M42" s="2">
-        <v>7133</v>
+        <v>4880</v>
       </c>
       <c r="N42" s="8" t="s">
         <v>24</v>
@@ -4789,28 +4757,28 @@
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>16</v>
@@ -4819,13 +4787,13 @@
         <v>16</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M43" s="2">
-        <v>4285</v>
+        <v>2880</v>
       </c>
       <c r="N43" s="8" t="s">
         <v>24</v>
@@ -4847,70 +4815,70 @@
       <c r="U43" s="2"/>
       <c r="V43" s="2"/>
       <c r="W43" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y43" s="2" t="s">
         <v>13</v>
       </c>
       <c r="Z43" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>164</v>
+        <v>42</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>16</v>
+        <v>211</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M44" s="2">
-        <v>4880</v>
+        <v>5023</v>
       </c>
       <c r="N44" s="8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="Q44" s="1"/>
       <c r="R44" s="2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="S44" s="2" t="s">
         <v>11</v>
@@ -4919,7 +4887,7 @@
       <c r="U44" s="2"/>
       <c r="V44" s="2"/>
       <c r="W44" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="X44" s="2" t="s">
         <v>13</v>
@@ -4928,61 +4896,61 @@
         <v>13</v>
       </c>
       <c r="Z44" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>165</v>
+        <v>43</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>16</v>
+        <v>211</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M45" s="2">
-        <v>2880</v>
+        <v>6189</v>
       </c>
       <c r="N45" s="8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="Q45" s="1"/>
       <c r="R45" s="2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="S45" s="2" t="s">
         <v>11</v>
@@ -4991,77 +4959,81 @@
       <c r="U45" s="2"/>
       <c r="V45" s="2"/>
       <c r="W45" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="X45" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y45" s="2" t="s">
         <v>13</v>
       </c>
       <c r="Z45" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>207</v>
+        <v>247</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>218</v>
+        <v>120</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>42</v>
+        <v>13</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M46" s="2">
-        <v>5023</v>
+        <v>7048</v>
       </c>
       <c r="N46" s="8" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q46" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="Q46" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="R46" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="S46" s="2" t="s">
         <v>11</v>
       </c>
       <c r="T46" s="2"/>
       <c r="U46" s="2"/>
-      <c r="V46" s="2"/>
+      <c r="V46" s="2">
+        <v>7692084</v>
+      </c>
       <c r="W46" s="2" t="s">
         <v>12</v>
       </c>
@@ -5069,108 +5041,114 @@
         <v>13</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z46" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>208</v>
+        <v>248</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>218</v>
+        <v>120</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K47" s="2" t="s">
-        <v>43</v>
+        <v>13</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M47" s="2">
-        <v>6189</v>
+        <v>6364</v>
       </c>
       <c r="N47" s="8" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q47" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="Q47" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="R47" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="T47" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="T47" s="2">
+        <v>7</v>
+      </c>
       <c r="U47" s="2"/>
-      <c r="V47" s="2"/>
+      <c r="V47" s="2">
+        <v>19540319</v>
+      </c>
       <c r="W47" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="X47" s="2" t="s">
         <v>13</v>
       </c>
       <c r="Y47" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z47" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>13</v>
@@ -5185,7 +5163,7 @@
         <v>3</v>
       </c>
       <c r="M48" s="2">
-        <v>7048</v>
+        <v>9472</v>
       </c>
       <c r="N48" s="8" t="s">
         <v>4</v>
@@ -5203,9 +5181,11 @@
         <v>6</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="T48" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="T48" s="2">
+        <v>47</v>
+      </c>
       <c r="U48" s="2"/>
       <c r="V48" s="2">
         <v>7692084</v>
@@ -5214,7 +5194,7 @@
         <v>12</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Y48" s="2" t="s">
         <v>12</v>
@@ -5225,28 +5205,28 @@
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>13</v>
@@ -5261,7 +5241,7 @@
         <v>3</v>
       </c>
       <c r="M49" s="2">
-        <v>6364</v>
+        <v>7045</v>
       </c>
       <c r="N49" s="8" t="s">
         <v>4</v>
@@ -5279,14 +5259,12 @@
         <v>6</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="T49" s="2">
-        <v>7</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="T49" s="2"/>
       <c r="U49" s="2"/>
       <c r="V49" s="2">
-        <v>19540319</v>
+        <v>7692084</v>
       </c>
       <c r="W49" s="2" t="s">
         <v>12</v>
@@ -5303,28 +5281,28 @@
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>13</v>
@@ -5339,7 +5317,7 @@
         <v>3</v>
       </c>
       <c r="M50" s="2">
-        <v>9472</v>
+        <v>10243</v>
       </c>
       <c r="N50" s="8" t="s">
         <v>4</v>
@@ -5360,7 +5338,7 @@
         <v>7</v>
       </c>
       <c r="T50" s="2">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="U50" s="2"/>
       <c r="V50" s="2">
@@ -5370,7 +5348,7 @@
         <v>12</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Y50" s="2" t="s">
         <v>12</v>
@@ -5381,28 +5359,28 @@
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>13</v>
@@ -5417,7 +5395,7 @@
         <v>3</v>
       </c>
       <c r="M51" s="2">
-        <v>7045</v>
+        <v>8355</v>
       </c>
       <c r="N51" s="8" t="s">
         <v>4</v>
@@ -5435,12 +5413,14 @@
         <v>6</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="T51" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="T51" s="2">
+        <v>25</v>
+      </c>
       <c r="U51" s="2"/>
       <c r="V51" s="2">
-        <v>7692084</v>
+        <v>9934709</v>
       </c>
       <c r="W51" s="2" t="s">
         <v>12</v>
@@ -5457,28 +5437,28 @@
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>13</v>
@@ -5493,7 +5473,7 @@
         <v>3</v>
       </c>
       <c r="M52" s="2">
-        <v>10243</v>
+        <v>7274</v>
       </c>
       <c r="N52" s="8" t="s">
         <v>4</v>
@@ -5514,17 +5494,17 @@
         <v>7</v>
       </c>
       <c r="T52" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U52" s="2"/>
       <c r="V52" s="2">
-        <v>7692084</v>
+        <v>9934709</v>
       </c>
       <c r="W52" s="2" t="s">
         <v>12</v>
       </c>
       <c r="X52" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y52" s="2" t="s">
         <v>12</v>
@@ -5535,28 +5515,28 @@
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>13</v>
@@ -5571,7 +5551,7 @@
         <v>3</v>
       </c>
       <c r="M53" s="2">
-        <v>8355</v>
+        <v>8214</v>
       </c>
       <c r="N53" s="8" t="s">
         <v>4</v>
@@ -5592,11 +5572,11 @@
         <v>7</v>
       </c>
       <c r="T53" s="2">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="U53" s="2"/>
       <c r="V53" s="2">
-        <v>9934709</v>
+        <v>19540319</v>
       </c>
       <c r="W53" s="2" t="s">
         <v>12</v>
@@ -5613,69 +5593,65 @@
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>260</v>
+        <v>97</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M54" s="2">
-        <v>7274</v>
+        <v>6896</v>
       </c>
       <c r="N54" s="8" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="Q54" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="R54" s="2" t="s">
         <v>6</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="T54" s="2">
-        <v>10</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="T54" s="2"/>
       <c r="U54" s="2"/>
-      <c r="V54" s="2">
-        <v>9934709</v>
-      </c>
+      <c r="V54" s="2"/>
       <c r="W54" s="2" t="s">
         <v>12</v>
       </c>
@@ -5683,245 +5659,93 @@
         <v>13</v>
       </c>
       <c r="Y54" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z54" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>262</v>
+        <v>118</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>13</v>
+        <v>211</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>98</v>
+        <v>16</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M55" s="2">
-        <v>8214</v>
+        <v>5685</v>
       </c>
       <c r="N55" s="8" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="O55" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q55" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="Q55" s="1"/>
       <c r="R55" s="2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="T55" s="2">
-        <v>104</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="T55" s="2"/>
       <c r="U55" s="2"/>
-      <c r="V55" s="2">
-        <v>19540319</v>
-      </c>
+      <c r="V55" s="2"/>
       <c r="W55" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="X55" s="2" t="s">
         <v>13</v>
       </c>
       <c r="Y55" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z55" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A56" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J56" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="L56" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M56" s="2">
-        <v>6896</v>
-      </c>
-      <c r="N56" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="O56" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="P56" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q56" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="R56" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="S56" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="T56" s="2"/>
-      <c r="U56" s="2"/>
-      <c r="V56" s="2"/>
-      <c r="W56" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="X56" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y56" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z56" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A57" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="J57" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K57" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L57" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="2">
-        <v>5685</v>
-      </c>
-      <c r="N57" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="O57" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="P57" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q57" s="1"/>
-      <c r="R57" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="S57" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="T57" s="2"/>
-      <c r="U57" s="2"/>
-      <c r="V57" s="2"/>
-      <c r="W57" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="X57" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y57" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z57" s="2">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z57">
-    <sortCondition ref="G2:G57"/>
-    <sortCondition ref="H2:H57"/>
-    <sortCondition ref="N2:N57"/>
-    <sortCondition ref="P2:P57"/>
-    <sortCondition ref="Q2:Q57"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z55">
+    <sortCondition ref="G2:G55"/>
+    <sortCondition ref="H2:H55"/>
+    <sortCondition ref="N2:N55"/>
+    <sortCondition ref="P2:P55"/>
+    <sortCondition ref="Q2:Q55"/>
   </sortState>
-  <conditionalFormatting sqref="Z58:Z1048576 Z1:Z45">
+  <conditionalFormatting sqref="Z56:Z1048576 Z1:Z43">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
@@ -5933,7 +5757,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z46:Z47">
+  <conditionalFormatting sqref="Z44:Z45">
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
@@ -5945,7 +5769,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z48">
+  <conditionalFormatting sqref="Z46">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -5957,7 +5781,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z49">
+  <conditionalFormatting sqref="Z47">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -5969,7 +5793,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z50">
+  <conditionalFormatting sqref="Z48">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -5981,7 +5805,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z51">
+  <conditionalFormatting sqref="Z49">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -5993,7 +5817,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z54">
+  <conditionalFormatting sqref="Z52">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -6005,7 +5829,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z55">
+  <conditionalFormatting sqref="Z53">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -6017,7 +5841,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z56">
+  <conditionalFormatting sqref="Z54">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -6029,7 +5853,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z57">
+  <conditionalFormatting sqref="Z55">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -6041,7 +5865,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z52">
+  <conditionalFormatting sqref="Z50">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -6053,7 +5877,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z53">
+  <conditionalFormatting sqref="Z51">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6094,22 +5918,22 @@
         <v>83</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>96</v>
@@ -6162,22 +5986,22 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>251</v>
-      </c>
       <c r="C2" s="2" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>120</v>
@@ -6202,7 +6026,7 @@
         <v>9</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>6</v>
@@ -6232,22 +6056,22 @@
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>252</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>120</v>
@@ -6272,7 +6096,7 @@
         <v>9</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>6</v>
@@ -6314,16 +6138,16 @@
         <v>177</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>13</v>
@@ -6388,16 +6212,16 @@
         <v>180</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>13</v>
@@ -6462,16 +6286,16 @@
         <v>185</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>13</v>
@@ -6536,16 +6360,16 @@
         <v>174</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>13</v>
@@ -6610,16 +6434,16 @@
         <v>173</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>13</v>

--- a/tabular/reference/herv_sublineage_data.xlsx
+++ b/tabular/reference/herv_sublineage_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D718F7D-E69C-FA47-B064-EA56DCC2955D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE4E8FB6-FE7F-574B-A678-E029BA11FF8F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="1560" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/tabular/reference/herv_sublineage_data.xlsx
+++ b/tabular/reference/herv_sublineage_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE4E8FB6-FE7F-574B-A678-E029BA11FF8F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083BCD05-093D-3B41-A9FD-B1D83CC285A1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="1560" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/tabular/reference/herv_sublineage_data.xlsx
+++ b/tabular/reference/herv_sublineage_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083BCD05-093D-3B41-A9FD-B1D83CC285A1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564939A7-EA4D-0741-8E7C-CBAC06996E2F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1680" yWindow="1560" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="920" yWindow="500" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sublineage" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="253">
   <si>
     <t>sequenceID</t>
   </si>
@@ -266,9 +266,6 @@
     <t>MER-84</t>
   </si>
   <si>
-    <t>PRIMA-41</t>
-  </si>
-  <si>
     <t>name</t>
   </si>
   <si>
@@ -519,9 +516,6 @@
   </si>
   <si>
     <t>ERV-1.Zeta.MER84</t>
-  </si>
-  <si>
-    <t>ERV-1.Zeta.prima41</t>
   </si>
   <si>
     <t>Standardised lineage name</t>
@@ -1687,7 +1681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB9083D8-DE01-F14E-ACB5-AF33867092C5}">
-  <dimension ref="A1:Z55"/>
+  <dimension ref="A1:Z54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -1710,34 +1704,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="E1" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>1</v>
@@ -1746,43 +1740,43 @@
         <v>2</v>
       </c>
       <c r="N1" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="Y1" s="4" t="s">
-        <v>95</v>
-      </c>
       <c r="Z1" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
@@ -1790,7 +1784,7 @@
         <v>74</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>74</v>
@@ -1799,16 +1793,16 @@
         <v>74</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>13</v>
@@ -1866,31 +1860,31 @@
         <v>31</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>31</v>
@@ -1938,25 +1932,25 @@
         <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>13</v>
@@ -2010,25 +2004,25 @@
         <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>13</v>
@@ -2082,31 +2076,31 @@
         <v>49</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>49</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>49</v>
@@ -2154,25 +2148,25 @@
         <v>26</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>13</v>
@@ -2181,7 +2175,7 @@
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
@@ -2228,25 +2222,25 @@
         <v>45</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>16</v>
@@ -2300,28 +2294,28 @@
         <v>47</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>47</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>16</v>
@@ -2372,25 +2366,25 @@
         <v>51</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>13</v>
@@ -2444,25 +2438,25 @@
         <v>52</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>16</v>
@@ -2516,7 +2510,7 @@
         <v>65</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>65</v>
@@ -2525,16 +2519,16 @@
         <v>65</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>16</v>
@@ -2588,25 +2582,25 @@
         <v>76</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>13</v>
@@ -2662,28 +2656,28 @@
         <v>71</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>16</v>
@@ -2736,7 +2730,7 @@
         <v>73</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>73</v>
@@ -2745,19 +2739,19 @@
         <v>73</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>13</v>
@@ -2812,25 +2806,25 @@
         <v>68</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>16</v>
@@ -2884,25 +2878,25 @@
         <v>70</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>16</v>
@@ -2956,7 +2950,7 @@
         <v>30</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>30</v>
@@ -2965,16 +2959,16 @@
         <v>30</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>13</v>
@@ -3028,25 +3022,25 @@
         <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>13</v>
@@ -3100,28 +3094,28 @@
         <v>35</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>16</v>
@@ -3172,28 +3166,28 @@
         <v>36</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>16</v>
@@ -3244,28 +3238,28 @@
         <v>38</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>16</v>
@@ -3316,28 +3310,28 @@
         <v>39</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>16</v>
@@ -3388,28 +3382,28 @@
         <v>40</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>16</v>
@@ -3460,7 +3454,7 @@
         <v>72</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>72</v>
@@ -3469,16 +3463,16 @@
         <v>72</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>16</v>
@@ -3533,43 +3527,43 @@
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>236</v>
+        <v>209</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M26" s="2">
-        <v>8665</v>
+        <v>8120</v>
       </c>
       <c r="N26" s="8" t="s">
         <v>24</v>
@@ -3578,7 +3572,7 @@
         <v>5</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="Q26" s="1"/>
       <c r="R26" s="2" t="s">
@@ -3591,7 +3585,7 @@
       <c r="U26" s="2"/>
       <c r="V26" s="2"/>
       <c r="W26" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="X26" s="2" t="s">
         <v>13</v>
@@ -3600,33 +3594,33 @@
         <v>13</v>
       </c>
       <c r="Z26" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F27" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="H27" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>16</v>
@@ -3635,13 +3629,13 @@
         <v>16</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M27" s="2">
-        <v>8120</v>
+        <v>4060</v>
       </c>
       <c r="N27" s="8" t="s">
         <v>24</v>
@@ -3677,28 +3671,28 @@
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F28" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="H28" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>16</v>
@@ -3707,13 +3701,13 @@
         <v>16</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M28" s="2">
-        <v>4060</v>
+        <v>4798</v>
       </c>
       <c r="N28" s="8" t="s">
         <v>24</v>
@@ -3749,28 +3743,28 @@
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>55</v>
+        <v>185</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F29" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="H29" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>16</v>
@@ -3779,13 +3773,13 @@
         <v>16</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M29" s="2">
-        <v>4798</v>
+        <v>6639</v>
       </c>
       <c r="N29" s="8" t="s">
         <v>24</v>
@@ -3821,28 +3815,28 @@
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>151</v>
+        <v>219</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F30" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="H30" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>16</v>
@@ -3851,13 +3845,13 @@
         <v>16</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M30" s="2">
-        <v>6639</v>
+        <v>933</v>
       </c>
       <c r="N30" s="8" t="s">
         <v>24</v>
@@ -3893,28 +3887,28 @@
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F31" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="H31" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>16</v>
@@ -3923,13 +3917,13 @@
         <v>16</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M31" s="2">
-        <v>933</v>
+        <v>4936</v>
       </c>
       <c r="N31" s="8" t="s">
         <v>24</v>
@@ -3965,28 +3959,28 @@
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F32" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G32" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="H32" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>16</v>
@@ -3995,13 +3989,13 @@
         <v>16</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M32" s="2">
-        <v>4936</v>
+        <v>5356</v>
       </c>
       <c r="N32" s="8" t="s">
         <v>24</v>
@@ -4037,28 +4031,28 @@
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>219</v>
+        <v>60</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F33" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G33" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="H33" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>16</v>
@@ -4067,13 +4061,13 @@
         <v>16</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M33" s="2">
-        <v>5356</v>
+        <v>6387</v>
       </c>
       <c r="N33" s="8" t="s">
         <v>24</v>
@@ -4109,28 +4103,28 @@
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>152</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F34" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="H34" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>16</v>
@@ -4139,13 +4133,13 @@
         <v>16</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M34" s="2">
-        <v>6387</v>
+        <v>6758</v>
       </c>
       <c r="N34" s="8" t="s">
         <v>24</v>
@@ -4181,28 +4175,28 @@
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>153</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F35" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G35" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="H35" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>16</v>
@@ -4211,13 +4205,13 @@
         <v>16</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M35" s="2">
-        <v>6758</v>
+        <v>5217</v>
       </c>
       <c r="N35" s="8" t="s">
         <v>24</v>
@@ -4253,28 +4247,28 @@
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>154</v>
+        <v>216</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F36" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G36" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="H36" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>16</v>
@@ -4283,13 +4277,13 @@
         <v>16</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M36" s="2">
-        <v>5217</v>
+        <v>4871</v>
       </c>
       <c r="N36" s="8" t="s">
         <v>24</v>
@@ -4314,7 +4308,7 @@
         <v>46</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y36" s="2" t="s">
         <v>13</v>
@@ -4325,28 +4319,28 @@
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>218</v>
+        <v>154</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F37" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G37" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="H37" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>16</v>
@@ -4355,13 +4349,13 @@
         <v>16</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M37" s="2">
-        <v>4871</v>
+        <v>7048</v>
       </c>
       <c r="N37" s="8" t="s">
         <v>24</v>
@@ -4386,7 +4380,7 @@
         <v>46</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y37" s="2" t="s">
         <v>13</v>
@@ -4397,28 +4391,28 @@
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>195</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F38" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="H38" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>16</v>
@@ -4427,13 +4421,13 @@
         <v>16</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M38" s="2">
-        <v>7048</v>
+        <v>3944</v>
       </c>
       <c r="N38" s="8" t="s">
         <v>24</v>
@@ -4442,7 +4436,7 @@
         <v>5</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="Q38" s="1"/>
       <c r="R38" s="2" t="s">
@@ -4469,28 +4463,28 @@
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>161</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F39" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G39" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="H39" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>16</v>
@@ -4499,13 +4493,13 @@
         <v>16</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M39" s="2">
-        <v>3944</v>
+        <v>7133</v>
       </c>
       <c r="N39" s="8" t="s">
         <v>24</v>
@@ -4541,28 +4535,28 @@
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>162</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F40" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G40" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="H40" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>16</v>
@@ -4571,13 +4565,13 @@
         <v>16</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M40" s="2">
-        <v>7133</v>
+        <v>4285</v>
       </c>
       <c r="N40" s="8" t="s">
         <v>24</v>
@@ -4613,28 +4607,28 @@
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>163</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F41" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G41" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G41" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="H41" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>16</v>
@@ -4643,13 +4637,13 @@
         <v>16</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M41" s="2">
-        <v>4285</v>
+        <v>4880</v>
       </c>
       <c r="N41" s="8" t="s">
         <v>24</v>
@@ -4685,28 +4679,28 @@
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>164</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F42" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G42" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="H42" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>16</v>
@@ -4715,13 +4709,13 @@
         <v>16</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M42" s="2">
-        <v>4880</v>
+        <v>2880</v>
       </c>
       <c r="N42" s="8" t="s">
         <v>24</v>
@@ -4743,70 +4737,70 @@
       <c r="U42" s="2"/>
       <c r="V42" s="2"/>
       <c r="W42" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="X42" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y42" s="2" t="s">
         <v>13</v>
       </c>
       <c r="Z42" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>165</v>
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F43" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G43" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G43" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="H43" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>16</v>
+        <v>209</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M43" s="2">
-        <v>2880</v>
+        <v>5023</v>
       </c>
       <c r="N43" s="8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="Q43" s="1"/>
       <c r="R43" s="2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="S43" s="2" t="s">
         <v>11</v>
@@ -4818,7 +4812,7 @@
         <v>12</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y43" s="2" t="s">
         <v>13</v>
@@ -4829,43 +4823,43 @@
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>140</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F44" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G44" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="H44" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M44" s="2">
-        <v>5023</v>
+        <v>6189</v>
       </c>
       <c r="N44" s="8" t="s">
         <v>28</v>
@@ -4887,7 +4881,7 @@
       <c r="U44" s="2"/>
       <c r="V44" s="2"/>
       <c r="W44" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="X44" s="2" t="s">
         <v>13</v>
@@ -4896,105 +4890,109 @@
         <v>13</v>
       </c>
       <c r="Z44" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>203</v>
+        <v>245</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>213</v>
+        <v>119</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>211</v>
+        <v>13</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K45" s="2" t="s">
-        <v>43</v>
+        <v>13</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M45" s="2">
-        <v>6189</v>
+        <v>7048</v>
       </c>
       <c r="N45" s="8" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q45" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="Q45" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="R45" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="S45" s="2" t="s">
         <v>11</v>
       </c>
       <c r="T45" s="2"/>
       <c r="U45" s="2"/>
-      <c r="V45" s="2"/>
+      <c r="V45" s="2">
+        <v>7692084</v>
+      </c>
       <c r="W45" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="X45" s="2" t="s">
         <v>13</v>
       </c>
       <c r="Y45" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z45" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>13</v>
@@ -5003,13 +5001,13 @@
         <v>13</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M46" s="2">
-        <v>7048</v>
+        <v>6364</v>
       </c>
       <c r="N46" s="8" t="s">
         <v>4</v>
@@ -5027,12 +5025,14 @@
         <v>6</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="T46" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="T46" s="2">
+        <v>7</v>
+      </c>
       <c r="U46" s="2"/>
       <c r="V46" s="2">
-        <v>7692084</v>
+        <v>19540319</v>
       </c>
       <c r="W46" s="2" t="s">
         <v>12</v>
@@ -5049,28 +5049,28 @@
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>13</v>
@@ -5079,13 +5079,13 @@
         <v>13</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M47" s="2">
-        <v>6364</v>
+        <v>9472</v>
       </c>
       <c r="N47" s="8" t="s">
         <v>4</v>
@@ -5106,17 +5106,17 @@
         <v>7</v>
       </c>
       <c r="T47" s="2">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="U47" s="2"/>
       <c r="V47" s="2">
-        <v>19540319</v>
+        <v>7692084</v>
       </c>
       <c r="W47" s="2" t="s">
         <v>12</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Y47" s="2" t="s">
         <v>12</v>
@@ -5127,28 +5127,28 @@
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>13</v>
@@ -5157,13 +5157,13 @@
         <v>13</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M48" s="2">
-        <v>9472</v>
+        <v>7045</v>
       </c>
       <c r="N48" s="8" t="s">
         <v>4</v>
@@ -5181,11 +5181,9 @@
         <v>6</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="T48" s="2">
-        <v>47</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="T48" s="2"/>
       <c r="U48" s="2"/>
       <c r="V48" s="2">
         <v>7692084</v>
@@ -5194,7 +5192,7 @@
         <v>12</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Y48" s="2" t="s">
         <v>12</v>
@@ -5205,28 +5203,28 @@
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>125</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>13</v>
@@ -5235,13 +5233,13 @@
         <v>13</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M49" s="2">
-        <v>7045</v>
+        <v>10243</v>
       </c>
       <c r="N49" s="8" t="s">
         <v>4</v>
@@ -5259,9 +5257,11 @@
         <v>6</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="T49" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="T49" s="2">
+        <v>7</v>
+      </c>
       <c r="U49" s="2"/>
       <c r="V49" s="2">
         <v>7692084</v>
@@ -5270,7 +5270,7 @@
         <v>12</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y49" s="2" t="s">
         <v>12</v>
@@ -5281,28 +5281,28 @@
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>251</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>13</v>
@@ -5311,13 +5311,13 @@
         <v>13</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M50" s="2">
-        <v>10243</v>
+        <v>8355</v>
       </c>
       <c r="N50" s="8" t="s">
         <v>4</v>
@@ -5338,17 +5338,17 @@
         <v>7</v>
       </c>
       <c r="T50" s="2">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="U50" s="2"/>
       <c r="V50" s="2">
-        <v>7692084</v>
+        <v>9934709</v>
       </c>
       <c r="W50" s="2" t="s">
         <v>12</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y50" s="2" t="s">
         <v>12</v>
@@ -5359,28 +5359,28 @@
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>13</v>
@@ -5389,13 +5389,13 @@
         <v>13</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M51" s="2">
-        <v>8355</v>
+        <v>7274</v>
       </c>
       <c r="N51" s="8" t="s">
         <v>4</v>
@@ -5416,7 +5416,7 @@
         <v>7</v>
       </c>
       <c r="T51" s="2">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="U51" s="2"/>
       <c r="V51" s="2">
@@ -5437,28 +5437,28 @@
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>252</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>13</v>
@@ -5467,13 +5467,13 @@
         <v>13</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M52" s="2">
-        <v>7274</v>
+        <v>8214</v>
       </c>
       <c r="N52" s="8" t="s">
         <v>4</v>
@@ -5494,11 +5494,11 @@
         <v>7</v>
       </c>
       <c r="T52" s="2">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="U52" s="2"/>
       <c r="V52" s="2">
-        <v>9934709</v>
+        <v>19540319</v>
       </c>
       <c r="W52" s="2" t="s">
         <v>12</v>
@@ -5515,69 +5515,65 @@
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>254</v>
+        <v>96</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M53" s="2">
-        <v>8214</v>
+        <v>6896</v>
       </c>
       <c r="N53" s="8" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="O53" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="Q53" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="R53" s="2" t="s">
         <v>6</v>
       </c>
       <c r="S53" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="T53" s="2">
-        <v>104</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="T53" s="2"/>
       <c r="U53" s="2"/>
-      <c r="V53" s="2">
-        <v>19540319</v>
-      </c>
+      <c r="V53" s="2"/>
       <c r="W53" s="2" t="s">
         <v>12</v>
       </c>
@@ -5585,66 +5581,64 @@
         <v>13</v>
       </c>
       <c r="Y53" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z53" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>13</v>
+        <v>209</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K54" s="1" t="s">
-        <v>103</v>
+      <c r="K54" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M54" s="2">
-        <v>6896</v>
+        <v>5685</v>
       </c>
       <c r="N54" s="8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q54" s="1" t="s">
-        <v>27</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="Q54" s="1"/>
       <c r="R54" s="2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="S54" s="2" t="s">
         <v>11</v>
@@ -5653,7 +5647,7 @@
       <c r="U54" s="2"/>
       <c r="V54" s="2"/>
       <c r="W54" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="X54" s="2" t="s">
         <v>13</v>
@@ -5662,90 +5656,18 @@
         <v>13</v>
       </c>
       <c r="Z54" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A55" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="J55" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K55" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L55" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M55" s="2">
-        <v>5685</v>
-      </c>
-      <c r="N55" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="O55" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="P55" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q55" s="1"/>
-      <c r="R55" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="S55" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="T55" s="2"/>
-      <c r="U55" s="2"/>
-      <c r="V55" s="2"/>
-      <c r="W55" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="X55" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y55" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z55" s="2">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z55">
-    <sortCondition ref="G2:G55"/>
-    <sortCondition ref="H2:H55"/>
-    <sortCondition ref="N2:N55"/>
-    <sortCondition ref="P2:P55"/>
-    <sortCondition ref="Q2:Q55"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z54">
+    <sortCondition ref="G2:G54"/>
+    <sortCondition ref="H2:H54"/>
+    <sortCondition ref="N2:N54"/>
+    <sortCondition ref="P2:P54"/>
+    <sortCondition ref="Q2:Q54"/>
   </sortState>
-  <conditionalFormatting sqref="Z56:Z1048576 Z1:Z43">
+  <conditionalFormatting sqref="Z55:Z1048576 Z1:Z42">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
@@ -5757,7 +5679,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z44:Z45">
+  <conditionalFormatting sqref="Z43:Z44">
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
@@ -5769,7 +5691,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z46">
+  <conditionalFormatting sqref="Z45">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -5781,7 +5703,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z47">
+  <conditionalFormatting sqref="Z46">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -5793,7 +5715,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z48">
+  <conditionalFormatting sqref="Z47">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -5805,7 +5727,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z49">
+  <conditionalFormatting sqref="Z48">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -5817,7 +5739,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z52">
+  <conditionalFormatting sqref="Z51">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -5829,7 +5751,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z53">
+  <conditionalFormatting sqref="Z52">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -5841,7 +5763,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z54">
+  <conditionalFormatting sqref="Z53">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -5853,7 +5775,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z55">
+  <conditionalFormatting sqref="Z54">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -5865,7 +5787,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z50">
+  <conditionalFormatting sqref="Z49">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -5877,7 +5799,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z51">
+  <conditionalFormatting sqref="Z50">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -5909,34 +5831,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="E1" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>1</v>
@@ -5945,66 +5867,66 @@
         <v>2</v>
       </c>
       <c r="N1" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="Y1" s="4" t="s">
-        <v>95</v>
-      </c>
       <c r="Z1" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>239</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
@@ -6026,7 +5948,7 @@
         <v>9</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>6</v>
@@ -6056,25 +5978,25 @@
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>240</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
@@ -6096,7 +6018,7 @@
         <v>9</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>6</v>
@@ -6126,28 +6048,28 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>13</v>
@@ -6156,7 +6078,7 @@
         <v>13</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>3</v>
@@ -6172,10 +6094,10 @@
         <v>25</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>7</v>
@@ -6200,28 +6122,28 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>180</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>13</v>
@@ -6230,7 +6152,7 @@
         <v>13</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>3</v>
@@ -6246,10 +6168,10 @@
         <v>25</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="S5" s="2" t="s">
         <v>7</v>
@@ -6274,28 +6196,28 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>13</v>
@@ -6304,7 +6226,7 @@
         <v>13</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>3</v>
@@ -6320,10 +6242,10 @@
         <v>25</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="S6" s="2" t="s">
         <v>7</v>
@@ -6348,28 +6270,28 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>13</v>
@@ -6378,7 +6300,7 @@
         <v>13</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
@@ -6422,28 +6344,28 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>13</v>
@@ -6452,7 +6374,7 @@
         <v>13</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>3</v>

--- a/tabular/reference/herv_sublineage_data.xlsx
+++ b/tabular/reference/herv_sublineage_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564939A7-EA4D-0741-8E7C-CBAC06996E2F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A3065FE-18BA-6744-B734-EE18C6AFD8C1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="920" yWindow="500" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="940" yWindow="500" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sublineage" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="260">
   <si>
     <t>sequenceID</t>
   </si>
@@ -780,6 +780,27 @@
   </si>
   <si>
     <t>endogenous betaretrovirus K Catarrhini HML9</t>
+  </si>
+  <si>
+    <t>HERV-Pb</t>
+  </si>
+  <si>
+    <t>HERV-V</t>
+  </si>
+  <si>
+    <t>ERV-1.Unclassified.V</t>
+  </si>
+  <si>
+    <t>ERV-1.Unclassified.Pb</t>
+  </si>
+  <si>
+    <t>Unclassified</t>
+  </si>
+  <si>
+    <t>human endogenous retrovirus Pb</t>
+  </si>
+  <si>
+    <t>human endogenous retrovirus V</t>
   </si>
 </sst>
 </file>
@@ -1681,7 +1702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB9083D8-DE01-F14E-ACB5-AF33867092C5}">
-  <dimension ref="A1:Z54"/>
+  <dimension ref="A1:Z57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -1693,7 +1714,7 @@
     <col min="7" max="7" width="19.6640625" customWidth="1"/>
     <col min="8" max="8" width="13.6640625" customWidth="1"/>
     <col min="9" max="9" width="14.5" customWidth="1"/>
-    <col min="10" max="10" width="12.5" customWidth="1"/>
+    <col min="10" max="10" width="25" customWidth="1"/>
     <col min="11" max="11" width="19" customWidth="1"/>
     <col min="14" max="14" width="10.83203125" style="9"/>
     <col min="16" max="16" width="21" customWidth="1"/>
@@ -5658,6 +5679,145 @@
       <c r="Z54" s="2">
         <v>4</v>
       </c>
+    </row>
+    <row r="55" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A55" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N55" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="O55" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q55" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R55" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S55" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W55" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="X55" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y55" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A56" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B56" t="s">
+        <v>255</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E56" t="s">
+        <v>255</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N56" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="O56" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q56" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="R56" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S56" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W56" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="X56" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y56" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="C57" s="2"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z54">

--- a/tabular/reference/herv_sublineage_data.xlsx
+++ b/tabular/reference/herv_sublineage_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{401FF91E-4A55-0A47-9E23-FF85DBE75D7B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17BA465D-F397-F743-8226-FFFEDD8020A0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="940" yWindow="500" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3460" yWindow="620" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sublineage" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="232">
   <si>
     <t>sequenceID</t>
   </si>
@@ -47,15 +47,9 @@
     <t>majority_consensus</t>
   </si>
   <si>
-    <t>HERV-K-HML1</t>
-  </si>
-  <si>
     <t>Betaretrovirus</t>
   </si>
   <si>
-    <t>Kappa</t>
-  </si>
-  <si>
     <t>REPBASE</t>
   </si>
   <si>
@@ -65,30 +59,9 @@
     <t>no</t>
   </si>
   <si>
-    <t>HERV-K-HML10</t>
-  </si>
-  <si>
-    <t>HERV-K-HML2</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
-    <t>HERV-K-HML3</t>
-  </si>
-  <si>
-    <t>HERV-K-HML4</t>
-  </si>
-  <si>
-    <t>HERV-K-HML7</t>
-  </si>
-  <si>
-    <t>HERV-K-HML8</t>
-  </si>
-  <si>
-    <t>HERV-K-HML9</t>
-  </si>
-  <si>
     <t>Reference</t>
   </si>
   <si>
@@ -311,9 +284,6 @@
     <t>HARLEQUIN</t>
   </si>
   <si>
-    <t>Betaretrovirus kappacatarrhini</t>
-  </si>
-  <si>
     <t>endogenous retrovirus L</t>
   </si>
   <si>
@@ -383,30 +353,6 @@
     <t>ERV-1.Gamma.HARLEQUIN</t>
   </si>
   <si>
-    <t>ERV-2.Beta.K.HML1</t>
-  </si>
-  <si>
-    <t>ERV-2.Beta.K.HML10</t>
-  </si>
-  <si>
-    <t>ERV-2.Beta.K.HML2</t>
-  </si>
-  <si>
-    <t>ERV-2.Beta.K.HML3</t>
-  </si>
-  <si>
-    <t>ERV-2.Beta.K.HML4</t>
-  </si>
-  <si>
-    <t>ERV-2.Beta.K.HML7</t>
-  </si>
-  <si>
-    <t>ERV-2.Beta.K.HML8</t>
-  </si>
-  <si>
-    <t>ERV-2.Beta.K.HML9</t>
-  </si>
-  <si>
     <t>ERV-3.Lambda.L</t>
   </si>
   <si>
@@ -686,18 +632,12 @@
     <t>ERV-1.HF.Fc</t>
   </si>
   <si>
-    <t>ERV-2.Beta.K</t>
-  </si>
-  <si>
     <t>ERV-2.Gamma.E</t>
   </si>
   <si>
     <t>ERV-3.Lamba.L</t>
   </si>
   <si>
-    <t>ERV-3.Lamba</t>
-  </si>
-  <si>
     <t>ERV-1.Zeta</t>
   </si>
   <si>
@@ -755,30 +695,6 @@
     <t>ERV-1.Gamma.R.1</t>
   </si>
   <si>
-    <t>endogenous betaretrovirus K Catarrhini HML1</t>
-  </si>
-  <si>
-    <t>endogenous betaretrovirus K Catarrhini HML10</t>
-  </si>
-  <si>
-    <t>endogenous betaretrovirus K Catarrhini HML2</t>
-  </si>
-  <si>
-    <t>endogenous betaretrovirus K Catarrhini HML3</t>
-  </si>
-  <si>
-    <t>endogenous betaretrovirus K Catarrhini HML4</t>
-  </si>
-  <si>
-    <t>endogenous betaretrovirus K Catarrhini HML8</t>
-  </si>
-  <si>
-    <t>endogenous betaretrovirus K Catarrhini HML7</t>
-  </si>
-  <si>
-    <t>endogenous betaretrovirus K Catarrhini HML9</t>
-  </si>
-  <si>
     <t>HERV-Pb</t>
   </si>
   <si>
@@ -795,12 +711,6 @@
   </si>
   <si>
     <t>human endogenous retrovirus V</t>
-  </si>
-  <si>
-    <t>entity_level</t>
-  </si>
-  <si>
-    <t>test</t>
   </si>
   <si>
     <t>no pol</t>
@@ -813,7 +723,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -959,23 +869,6 @@
       <i/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1352,7 +1245,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
@@ -1369,14 +1262,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1732,7 +1623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB9083D8-DE01-F14E-ACB5-AF33867092C5}">
-  <dimension ref="A1:AA57"/>
+  <dimension ref="A1:Z48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -1750,39 +1641,39 @@
     <col min="16" max="16" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>1</v>
@@ -1791,534 +1682,511 @@
         <v>2</v>
       </c>
       <c r="N1" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="W1" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="Q1" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="R1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="S1" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="U1" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="V1" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="W1" s="4" t="s">
+      <c r="B2" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="X1" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>73</v>
-      </c>
       <c r="L2" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M2" s="10">
-        <v>7418</v>
+        <v>6896</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O2" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P2" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q2" s="12" t="s">
-        <v>68</v>
+        <v>16</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="R2" s="10" t="s">
         <v>6</v>
       </c>
       <c r="S2" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T2" s="10"/>
       <c r="U2" s="10"/>
-      <c r="V2" s="13">
-        <v>2825129</v>
-      </c>
+      <c r="V2" s="10"/>
       <c r="W2" s="10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X2" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y2" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z2" s="10">
         <v>2</v>
       </c>
-      <c r="AA2" s="10" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>128</v>
+        <v>17</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>128</v>
+        <v>209</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>31</v>
+        <v>12</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="L3" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M3" s="10">
-        <v>5667</v>
+        <v>9611</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="O3" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P3" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q3" s="12"/>
+        <v>16</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="R3" s="10" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="S3" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T3" s="10"/>
       <c r="U3" s="10"/>
       <c r="V3" s="10"/>
       <c r="W3" s="10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X3" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y3" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z3" s="10">
         <v>2</v>
       </c>
-      <c r="AA3" s="10" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>137</v>
+        <v>41</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>100</v>
+        <v>41</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>128</v>
+        <v>196</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="L4" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M4" s="10">
-        <v>5714</v>
+        <v>7613</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="O4" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q4" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="Q4" s="1"/>
       <c r="R4" s="10" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="S4" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T4" s="10"/>
       <c r="U4" s="10"/>
       <c r="V4" s="10"/>
       <c r="W4" s="10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X4" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y4" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z4" s="10">
-        <v>2</v>
-      </c>
-      <c r="AA4" s="10" t="s">
-        <v>259</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>129</v>
+        <v>42</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>99</v>
+        <v>42</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>128</v>
+        <v>196</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>209</v>
+        <v>190</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>191</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L5" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M5" s="10">
-        <v>5667</v>
+        <v>1786</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="O5" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q5" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="Q5" s="1"/>
       <c r="R5" s="10" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="S5" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T5" s="10"/>
       <c r="U5" s="10"/>
       <c r="V5" s="10"/>
       <c r="W5" s="10" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="X5" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y5" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z5" s="10">
-        <v>2</v>
-      </c>
-      <c r="AA5" s="10" t="s">
-        <v>259</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>140</v>
+        <v>225</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>231</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>48</v>
+        <v>225</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>128</v>
+        <v>229</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>231</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>209</v>
+        <v>108</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>208</v>
+        <v>12</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>208</v>
+        <v>11</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>48</v>
+        <v>225</v>
       </c>
       <c r="L6" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="M6" s="10">
-        <v>5246</v>
+      <c r="M6" s="13">
+        <v>2482</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="O6" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P6" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q6" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="Q6" s="10"/>
       <c r="R6" s="10" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="S6" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10"/>
-      <c r="V6" s="10"/>
+        <v>3</v>
+      </c>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="13"/>
       <c r="W6" s="10" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="X6" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y6" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z6" s="10">
-        <v>3</v>
-      </c>
-      <c r="AA6" s="10" t="s">
-        <v>259</v>
+        <v>10</v>
+      </c>
+      <c r="Z6" s="13">
+        <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>243</v>
+        <v>43</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>128</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>101</v>
+        <v>12</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="L7" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M7" s="10">
-        <v>9611</v>
+        <v>8120</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O7" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P7" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q7" s="12" t="s">
-        <v>27</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="Q7" s="1"/>
       <c r="R7" s="10" t="s">
         <v>6</v>
       </c>
       <c r="S7" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T7" s="10"/>
       <c r="U7" s="10"/>
       <c r="V7" s="10"/>
       <c r="W7" s="10" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="X7" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y7" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z7" s="10">
-        <v>2</v>
-      </c>
-      <c r="AA7" s="10" t="s">
-        <v>259</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>142</v>
+      <c r="B8" s="12" t="s">
+        <v>129</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="14" t="s">
-        <v>103</v>
+      <c r="D8" s="10" t="s">
+        <v>44</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K8" s="10" t="s">
         <v>44</v>
@@ -2327,1284 +2195,1229 @@
         <v>3</v>
       </c>
       <c r="M8" s="10">
-        <v>4936</v>
+        <v>4060</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O8" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P8" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q8" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="Q8" s="1"/>
       <c r="R8" s="10" t="s">
         <v>6</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T8" s="10"/>
       <c r="U8" s="10"/>
       <c r="V8" s="10"/>
       <c r="W8" s="10" t="s">
-        <v>260</v>
+        <v>36</v>
       </c>
       <c r="X8" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z8" s="10">
         <v>4</v>
       </c>
-      <c r="AA8" s="10" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>143</v>
+        <v>45</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>104</v>
+        <v>45</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>208</v>
+        <v>12</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L9" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M9" s="10">
-        <v>9084</v>
+        <v>4798</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O9" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P9" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q9" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="Q9" s="1"/>
       <c r="R9" s="10" t="s">
         <v>6</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T9" s="10"/>
       <c r="U9" s="10"/>
       <c r="V9" s="10"/>
       <c r="W9" s="10" t="s">
-        <v>260</v>
+        <v>36</v>
       </c>
       <c r="X9" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z9" s="10">
         <v>4</v>
       </c>
-      <c r="AA9" s="10" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>144</v>
+        <v>46</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>105</v>
+        <v>46</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>166</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L10" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M10" s="10">
-        <v>7613</v>
+        <v>6639</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O10" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P10" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q10" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="Q10" s="1"/>
       <c r="R10" s="10" t="s">
         <v>6</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T10" s="10"/>
       <c r="U10" s="10"/>
       <c r="V10" s="10"/>
       <c r="W10" s="10" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="X10" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z10" s="10">
-        <v>3</v>
-      </c>
-      <c r="AA10" s="10" t="s">
-        <v>259</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>145</v>
+        <v>47</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>200</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>106</v>
+        <v>47</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>167</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="L11" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M11" s="10">
-        <v>1786</v>
+        <v>933</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O11" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q11" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="Q11" s="1"/>
       <c r="R11" s="10" t="s">
         <v>6</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T11" s="10"/>
       <c r="U11" s="10"/>
       <c r="V11" s="10"/>
       <c r="W11" s="10" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="X11" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y11" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z11" s="10">
         <v>4</v>
       </c>
-      <c r="AA11" s="10" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>154</v>
+        <v>48</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>199</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>64</v>
+        <v>168</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="L12" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M12" s="10">
-        <v>4102</v>
+        <v>4936</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O12" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P12" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q12" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="Q12" s="1"/>
       <c r="R12" s="10" t="s">
         <v>6</v>
       </c>
       <c r="S12" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T12" s="10"/>
       <c r="U12" s="10"/>
       <c r="V12" s="10"/>
       <c r="W12" s="10" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="X12" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z12" s="10">
-        <v>3</v>
-      </c>
-      <c r="AA12" s="10" t="s">
-        <v>259</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>155</v>
+        <v>49</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>198</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="L13" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M13" s="10">
-        <v>4981</v>
+        <v>5356</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O13" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q13" s="12" t="s">
-        <v>66</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="Q13" s="1"/>
       <c r="R13" s="10" t="s">
         <v>6</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T13" s="10"/>
       <c r="U13" s="10"/>
       <c r="V13" s="10"/>
       <c r="W13" s="10" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="X13" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y13" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z13" s="10">
-        <v>3</v>
-      </c>
-      <c r="AA13" s="10" t="s">
-        <v>259</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>156</v>
+        <v>50</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>132</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>109</v>
+        <v>50</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>170</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>208</v>
+        <v>12</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="L14" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M14" s="10">
-        <v>6996</v>
+        <v>6387</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O14" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P14" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q14" s="12" t="s">
-        <v>68</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="Q14" s="1"/>
       <c r="R14" s="10" t="s">
         <v>6</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T14" s="10"/>
       <c r="U14" s="10"/>
       <c r="V14" s="10"/>
       <c r="W14" s="10" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="X14" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y14" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z14" s="10">
-        <v>3</v>
-      </c>
-      <c r="AA14" s="10" t="s">
-        <v>259</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>203</v>
+        <v>51</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>133</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>208</v>
+        <v>12</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="L15" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M15" s="10">
-        <v>8987</v>
+        <v>6758</v>
       </c>
       <c r="N15" s="11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O15" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q15" s="12" t="s">
-        <v>68</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="Q15" s="1"/>
       <c r="R15" s="10" t="s">
         <v>6</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T15" s="10"/>
       <c r="U15" s="10"/>
-      <c r="V15" s="13">
-        <v>2825129</v>
-      </c>
+      <c r="V15" s="10"/>
       <c r="W15" s="10" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="X15" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z15" s="10">
         <v>4</v>
       </c>
-      <c r="AA15" s="10" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>157</v>
+        <v>52</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>134</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>107</v>
+        <v>172</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="L16" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M16" s="10">
-        <v>5586</v>
+        <v>5217</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O16" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P16" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q16" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="Q16" s="1"/>
       <c r="R16" s="10" t="s">
         <v>6</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T16" s="10"/>
       <c r="U16" s="10"/>
       <c r="V16" s="10"/>
       <c r="W16" s="10" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="X16" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y16" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z16" s="10">
         <v>4</v>
       </c>
-      <c r="AA16" s="10" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>158</v>
+        <v>53</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>197</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>108</v>
+        <v>173</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="L17" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M17" s="10">
-        <v>6918</v>
+        <v>4871</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O17" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q17" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="Q17" s="1"/>
       <c r="R17" s="10" t="s">
         <v>6</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T17" s="10"/>
       <c r="U17" s="10"/>
       <c r="V17" s="10"/>
       <c r="W17" s="10" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="X17" s="10" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y17" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z17" s="10">
         <v>4</v>
       </c>
-      <c r="AA17" s="10" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="18" spans="1:27" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>141</v>
+        <v>54</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>135</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>30</v>
+        <v>174</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="L18" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M18" s="10">
-        <v>6070</v>
+        <v>7048</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="O18" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P18" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q18" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="Q18" s="1"/>
       <c r="R18" s="10" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T18" s="10"/>
       <c r="U18" s="10"/>
       <c r="V18" s="10"/>
       <c r="W18" s="10" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="X18" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y18" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z18" s="10">
-        <v>2</v>
-      </c>
-      <c r="AA18" s="10" t="s">
-        <v>259</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>130</v>
+        <v>55</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>136</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>209</v>
+        <v>190</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>191</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="L19" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M19" s="10">
-        <v>4996</v>
+        <v>4102</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="O19" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q19" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="Q19" s="1"/>
       <c r="R19" s="10" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T19" s="10"/>
       <c r="U19" s="10"/>
       <c r="V19" s="10"/>
       <c r="W19" s="10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X19" s="10" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y19" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z19" s="10">
-        <v>2</v>
-      </c>
-      <c r="AA19" s="10" t="s">
-        <v>259</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>131</v>
+        <v>224</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>226</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>35</v>
+        <v>224</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>111</v>
+        <v>228</v>
       </c>
       <c r="E20" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="K20" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="F20" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="K20" s="10" t="s">
-        <v>35</v>
-      </c>
       <c r="L20" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="10">
-        <v>3556</v>
-      </c>
+      <c r="M20" s="13"/>
       <c r="N20" s="11" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="O20" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P20" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q20" s="12"/>
+        <v>227</v>
+      </c>
+      <c r="Q20" s="10" t="s">
+        <v>227</v>
+      </c>
       <c r="R20" s="10" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="T20" s="10"/>
-      <c r="U20" s="10"/>
-      <c r="V20" s="10"/>
+        <v>3</v>
+      </c>
+      <c r="T20" s="13"/>
+      <c r="U20" s="13"/>
+      <c r="V20" s="13"/>
       <c r="W20" s="10" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="X20" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z20" s="10">
-        <v>4</v>
-      </c>
-      <c r="AA20" s="10" t="s">
-        <v>259</v>
+        <v>10</v>
+      </c>
+      <c r="Z20" s="13">
+        <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>132</v>
+        <v>35</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>112</v>
+        <v>35</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>208</v>
+        <v>12</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L21" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M21" s="10">
-        <v>5343</v>
+        <v>4936</v>
       </c>
       <c r="N21" s="11" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="O21" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q21" s="12"/>
+        <v>227</v>
+      </c>
+      <c r="Q21" s="1"/>
       <c r="R21" s="10" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T21" s="10"/>
       <c r="U21" s="10"/>
       <c r="V21" s="10"/>
       <c r="W21" s="10" t="s">
-        <v>37</v>
+        <v>230</v>
       </c>
       <c r="X21" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y21" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z21" s="10">
         <v>4</v>
       </c>
-      <c r="AA21" s="10" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>133</v>
+        <v>37</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>113</v>
+        <v>37</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L22" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M22" s="10">
-        <v>5530</v>
+        <v>9084</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="O22" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P22" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q22" s="12"/>
+        <v>227</v>
+      </c>
+      <c r="Q22" s="1"/>
       <c r="R22" s="10" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="S22" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T22" s="10"/>
       <c r="U22" s="10"/>
       <c r="V22" s="10"/>
       <c r="W22" s="10" t="s">
-        <v>37</v>
+        <v>230</v>
       </c>
       <c r="X22" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y22" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z22" s="10">
         <v>4</v>
       </c>
-      <c r="AA22" s="10" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>134</v>
+        <v>66</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>137</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>114</v>
+        <v>175</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>209</v>
+        <v>190</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>191</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>208</v>
+        <v>11</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="L23" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M23" s="10">
-        <v>3329</v>
+        <v>4981</v>
       </c>
       <c r="N23" s="11" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q23" s="12"/>
+        <v>56</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="R23" s="10" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="S23" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T23" s="10"/>
       <c r="U23" s="10"/>
       <c r="V23" s="10"/>
       <c r="W23" s="10" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="X23" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y23" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z23" s="10">
-        <v>4</v>
-      </c>
-      <c r="AA23" s="10" t="s">
-        <v>259</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>135</v>
+        <v>61</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>138</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>115</v>
+        <v>61</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>209</v>
+        <v>190</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>191</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="L24" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M24" s="10">
-        <v>3037</v>
+        <v>6996</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="O24" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P24" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q24" s="12"/>
+        <v>56</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="R24" s="10" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="S24" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T24" s="10"/>
       <c r="U24" s="10"/>
       <c r="V24" s="10"/>
       <c r="W24" s="10" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="X24" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y24" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z24" s="10">
-        <v>4</v>
-      </c>
-      <c r="AA24" s="10" t="s">
-        <v>259</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>201</v>
+        <v>62</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>183</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="L25" s="10" t="s">
         <v>3</v>
@@ -3613,22 +3426,22 @@
         <v>11027</v>
       </c>
       <c r="N25" s="11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q25" s="12" t="s">
-        <v>68</v>
+        <v>56</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="R25" s="10" t="s">
         <v>6</v>
       </c>
       <c r="S25" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T25" s="10"/>
       <c r="U25" s="10"/>
@@ -3636,2407 +3449,1691 @@
         <v>2825129</v>
       </c>
       <c r="W25" s="10" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="X25" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y25" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z25" s="10">
         <v>4</v>
       </c>
-      <c r="AA25" s="10" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>146</v>
+        <v>63</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>185</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>16</v>
+        <v>190</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="L26" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M26" s="10">
-        <v>8120</v>
+        <v>8987</v>
       </c>
       <c r="N26" s="11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O26" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P26" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q26" s="12"/>
+        <v>56</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="R26" s="10" t="s">
         <v>6</v>
       </c>
       <c r="S26" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T26" s="10"/>
       <c r="U26" s="10"/>
-      <c r="V26" s="10"/>
+      <c r="V26" s="13">
+        <v>2825129</v>
+      </c>
       <c r="W26" s="10" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="X26" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y26" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z26" s="10">
         <v>4</v>
       </c>
-      <c r="AA26" s="10" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>147</v>
+        <v>64</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>184</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="L27" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M27" s="10">
-        <v>4060</v>
+        <v>7418</v>
       </c>
       <c r="N27" s="11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q27" s="12"/>
+        <v>56</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="R27" s="10" t="s">
         <v>6</v>
       </c>
       <c r="S27" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T27" s="10"/>
       <c r="U27" s="10"/>
-      <c r="V27" s="10"/>
+      <c r="V27" s="13">
+        <v>2825129</v>
+      </c>
       <c r="W27" s="10" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="X27" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y27" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z27" s="10">
-        <v>4</v>
-      </c>
-      <c r="AA27" s="10" t="s">
-        <v>259</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>148</v>
+        <v>58</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>139</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L28" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M28" s="10">
-        <v>4798</v>
+        <v>5586</v>
       </c>
       <c r="N28" s="11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O28" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P28" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q28" s="12"/>
+        <v>56</v>
+      </c>
+      <c r="Q28" s="1"/>
       <c r="R28" s="10" t="s">
         <v>6</v>
       </c>
       <c r="S28" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T28" s="10"/>
       <c r="U28" s="10"/>
       <c r="V28" s="10"/>
       <c r="W28" s="10" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="X28" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y28" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z28" s="10">
         <v>4</v>
       </c>
-      <c r="AA28" s="10" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>149</v>
+        <v>60</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>140</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>184</v>
+        <v>98</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L29" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M29" s="10">
-        <v>6639</v>
+        <v>6918</v>
       </c>
       <c r="N29" s="11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q29" s="12"/>
+        <v>56</v>
+      </c>
+      <c r="Q29" s="1"/>
       <c r="R29" s="10" t="s">
         <v>6</v>
       </c>
       <c r="S29" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T29" s="10"/>
       <c r="U29" s="10"/>
       <c r="V29" s="10"/>
       <c r="W29" s="10" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="X29" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y29" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z29" s="10">
         <v>4</v>
       </c>
-      <c r="AA29" s="10" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>218</v>
+        <v>65</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>141</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="L30" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M30" s="10">
-        <v>933</v>
+        <v>3944</v>
       </c>
       <c r="N30" s="11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O30" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P30" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q30" s="12"/>
+        <v>56</v>
+      </c>
+      <c r="Q30" s="1"/>
       <c r="R30" s="10" t="s">
         <v>6</v>
       </c>
       <c r="S30" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T30" s="10"/>
       <c r="U30" s="10"/>
       <c r="V30" s="10"/>
       <c r="W30" s="10" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="X30" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y30" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z30" s="10">
         <v>4</v>
       </c>
-      <c r="AA30" s="10" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>217</v>
+        <v>67</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>142</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="L31" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M31" s="10">
-        <v>4936</v>
+        <v>7133</v>
       </c>
       <c r="N31" s="11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O31" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q31" s="12"/>
+        <v>56</v>
+      </c>
+      <c r="Q31" s="1"/>
       <c r="R31" s="10" t="s">
         <v>6</v>
       </c>
       <c r="S31" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T31" s="10"/>
       <c r="U31" s="10"/>
       <c r="V31" s="10"/>
       <c r="W31" s="10" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="X31" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y31" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z31" s="10">
         <v>4</v>
       </c>
-      <c r="AA31" s="10" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>216</v>
+        <v>68</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>143</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="L32" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M32" s="10">
-        <v>5356</v>
+        <v>4285</v>
       </c>
       <c r="N32" s="11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O32" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P32" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q32" s="12"/>
+        <v>56</v>
+      </c>
+      <c r="Q32" s="1"/>
       <c r="R32" s="10" t="s">
         <v>6</v>
       </c>
       <c r="S32" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T32" s="10"/>
       <c r="U32" s="10"/>
       <c r="V32" s="10"/>
       <c r="W32" s="10" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="X32" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y32" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z32" s="10">
         <v>4</v>
       </c>
-      <c r="AA32" s="10" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>150</v>
+        <v>69</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>144</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="L33" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M33" s="10">
-        <v>6387</v>
+        <v>4880</v>
       </c>
       <c r="N33" s="11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q33" s="12"/>
+        <v>56</v>
+      </c>
+      <c r="Q33" s="1"/>
       <c r="R33" s="10" t="s">
         <v>6</v>
       </c>
       <c r="S33" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T33" s="10"/>
       <c r="U33" s="10"/>
       <c r="V33" s="10"/>
       <c r="W33" s="10" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="X33" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y33" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z33" s="10">
         <v>4</v>
       </c>
-      <c r="AA33" s="10" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>151</v>
+        <v>70</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>145</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D34" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="H34" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="E34" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>207</v>
-      </c>
       <c r="I34" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="L34" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M34" s="10">
-        <v>6758</v>
+        <v>2880</v>
       </c>
       <c r="N34" s="11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O34" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P34" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q34" s="12"/>
+        <v>56</v>
+      </c>
+      <c r="Q34" s="1"/>
       <c r="R34" s="10" t="s">
         <v>6</v>
       </c>
       <c r="S34" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T34" s="10"/>
       <c r="U34" s="10"/>
       <c r="V34" s="10"/>
       <c r="W34" s="10" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="X34" s="10" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y34" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z34" s="10">
-        <v>4</v>
-      </c>
-      <c r="AA34" s="10" t="s">
-        <v>259</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>152</v>
+        <v>21</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>123</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="D35" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F35" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="E35" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>208</v>
-      </c>
       <c r="G35" s="10" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="L35" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M35" s="10">
-        <v>5217</v>
+        <v>6070</v>
       </c>
       <c r="N35" s="11" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q35" s="12"/>
+        <v>20</v>
+      </c>
+      <c r="Q35" s="1"/>
       <c r="R35" s="10" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="S35" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T35" s="10"/>
       <c r="U35" s="10"/>
       <c r="V35" s="10"/>
       <c r="W35" s="10" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="X35" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y35" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z35" s="10">
-        <v>4</v>
-      </c>
-      <c r="AA35" s="10" t="s">
-        <v>259</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>215</v>
+        <v>22</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>110</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="D36" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="G36" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="E36" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>210</v>
-      </c>
       <c r="H36" s="10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>16</v>
+        <v>190</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="L36" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M36" s="10">
-        <v>4871</v>
+        <v>5667</v>
       </c>
       <c r="N36" s="11" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="O36" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P36" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q36" s="12"/>
+        <v>20</v>
+      </c>
+      <c r="Q36" s="1"/>
       <c r="R36" s="10" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="S36" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T36" s="10"/>
       <c r="U36" s="10"/>
       <c r="V36" s="10"/>
       <c r="W36" s="10" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="X36" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y36" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z36" s="10">
-        <v>4</v>
-      </c>
-      <c r="AA36" s="10" t="s">
-        <v>259</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B37" s="15" t="s">
-        <v>153</v>
+        <v>23</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>119</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>192</v>
+        <v>23</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>226</v>
+        <v>110</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="L37" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M37" s="10">
-        <v>7048</v>
+        <v>5714</v>
       </c>
       <c r="N37" s="11" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q37" s="12"/>
+        <v>20</v>
+      </c>
+      <c r="Q37" s="1"/>
       <c r="R37" s="10" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="S37" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T37" s="10"/>
       <c r="U37" s="10"/>
       <c r="V37" s="10"/>
       <c r="W37" s="10" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="X37" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y37" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z37" s="10">
-        <v>4</v>
-      </c>
-      <c r="AA37" s="10" t="s">
-        <v>259</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A38" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>261</v>
+        <v>24</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>111</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>261</v>
+        <v>24</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>110</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="G38" s="10" t="s">
-        <v>118</v>
+        <v>213</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>191</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>253</v>
+        <v>24</v>
       </c>
       <c r="L38" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="M38" s="13">
-        <v>2482</v>
+      <c r="M38" s="10">
+        <v>5667</v>
       </c>
       <c r="N38" s="11" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="O38" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P38" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q38" s="10" t="s">
-        <v>255</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="Q38" s="1"/>
       <c r="R38" s="10" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="S38" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="T38" s="13"/>
-      <c r="U38" s="13"/>
-      <c r="V38" s="13"/>
+        <v>9</v>
+      </c>
+      <c r="T38" s="10"/>
+      <c r="U38" s="10"/>
+      <c r="V38" s="10"/>
       <c r="W38" s="10" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="X38" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y38" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z38" s="13">
-        <v>1</v>
-      </c>
-      <c r="AA38" s="10" t="s">
-        <v>259</v>
+        <v>11</v>
+      </c>
+      <c r="Z38" s="10">
+        <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>159</v>
+        <v>25</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>112</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>194</v>
+        <v>100</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>225</v>
+        <v>110</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>210</v>
+        <v>190</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>191</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="L39" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M39" s="10">
-        <v>3944</v>
+        <v>4996</v>
       </c>
       <c r="N39" s="11" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q39" s="12"/>
+        <v>20</v>
+      </c>
+      <c r="Q39" s="1"/>
       <c r="R39" s="10" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="S39" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T39" s="10"/>
       <c r="U39" s="10"/>
       <c r="V39" s="10"/>
       <c r="W39" s="10" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="X39" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y39" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z39" s="10">
-        <v>4</v>
-      </c>
-      <c r="AA39" s="10" t="s">
-        <v>259</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>160</v>
+        <v>26</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>113</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>195</v>
+        <v>101</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>225</v>
+        <v>110</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>210</v>
+        <v>190</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>191</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>16</v>
+        <v>190</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K40" s="10" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="L40" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M40" s="10">
-        <v>7133</v>
+        <v>3556</v>
       </c>
       <c r="N40" s="11" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="O40" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P40" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q40" s="12"/>
+        <v>20</v>
+      </c>
+      <c r="Q40" s="1"/>
       <c r="R40" s="10" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="S40" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T40" s="10"/>
       <c r="U40" s="10"/>
       <c r="V40" s="10"/>
       <c r="W40" s="10" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="X40" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y40" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z40" s="10">
         <v>4</v>
       </c>
-      <c r="AA40" s="10" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B41" s="15" t="s">
-        <v>161</v>
+        <v>27</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>196</v>
+        <v>102</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>225</v>
+        <v>110</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>16</v>
+        <v>190</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="L41" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M41" s="10">
-        <v>4285</v>
+        <v>5343</v>
       </c>
       <c r="N41" s="11" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q41" s="12"/>
+        <v>20</v>
+      </c>
+      <c r="Q41" s="1"/>
       <c r="R41" s="10" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="S41" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T41" s="10"/>
       <c r="U41" s="10"/>
       <c r="V41" s="10"/>
       <c r="W41" s="10" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="X41" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y41" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z41" s="10">
         <v>4</v>
       </c>
-      <c r="AA41" s="10" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A42" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>162</v>
+        <v>29</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>115</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>197</v>
+        <v>103</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>225</v>
+        <v>110</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>16</v>
+        <v>190</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K42" s="10" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="L42" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M42" s="10">
-        <v>4880</v>
+        <v>5530</v>
       </c>
       <c r="N42" s="11" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="O42" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P42" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q42" s="12"/>
+        <v>20</v>
+      </c>
+      <c r="Q42" s="1"/>
       <c r="R42" s="10" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="S42" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T42" s="10"/>
       <c r="U42" s="10"/>
       <c r="V42" s="10"/>
       <c r="W42" s="10" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="X42" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y42" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z42" s="10">
         <v>4</v>
       </c>
-      <c r="AA42" s="10" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A43" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B43" s="15" t="s">
-        <v>163</v>
+        <v>30</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>116</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>198</v>
+        <v>104</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>225</v>
+        <v>110</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>210</v>
+        <v>190</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>191</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>16</v>
+        <v>190</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K43" s="10" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="L43" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M43" s="10">
-        <v>2880</v>
+        <v>3329</v>
       </c>
       <c r="N43" s="11" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q43" s="12"/>
+        <v>20</v>
+      </c>
+      <c r="Q43" s="1"/>
       <c r="R43" s="10" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="S43" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T43" s="10"/>
       <c r="U43" s="10"/>
       <c r="V43" s="10"/>
       <c r="W43" s="10" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="X43" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y43" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z43" s="10">
-        <v>3</v>
-      </c>
-      <c r="AA43" s="10" t="s">
-        <v>259</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A44" s="9" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>199</v>
+        <v>105</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>223</v>
+        <v>110</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="G44" s="10" t="s">
-        <v>210</v>
+        <v>190</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>191</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K44" s="10" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="L44" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M44" s="10">
-        <v>5023</v>
+        <v>3037</v>
       </c>
       <c r="N44" s="11" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="O44" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P44" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q44" s="12"/>
+        <v>20</v>
+      </c>
+      <c r="Q44" s="1"/>
       <c r="R44" s="10" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="S44" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T44" s="10"/>
       <c r="U44" s="10"/>
       <c r="V44" s="10"/>
       <c r="W44" s="10" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="X44" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y44" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z44" s="10">
-        <v>3</v>
-      </c>
-      <c r="AA44" s="10" t="s">
-        <v>259</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A45" s="9" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>200</v>
+        <v>106</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>210</v>
+        <v>108</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K45" s="10" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L45" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M45" s="10">
-        <v>6189</v>
+        <v>5685</v>
       </c>
       <c r="N45" s="11" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q45" s="12"/>
+        <v>20</v>
+      </c>
+      <c r="Q45" s="1"/>
       <c r="R45" s="10" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="S45" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T45" s="10"/>
       <c r="U45" s="10"/>
       <c r="V45" s="10"/>
       <c r="W45" s="10" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="X45" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y45" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z45" s="10">
         <v>4</v>
       </c>
-      <c r="AA45" s="10" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A46" s="9" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>120</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>244</v>
+        <v>181</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>118</v>
+        <v>192</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>13</v>
+        <v>190</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="K46" s="12" t="s">
-        <v>96</v>
+        <v>12</v>
+      </c>
+      <c r="K46" s="10" t="s">
+        <v>33</v>
       </c>
       <c r="L46" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M46" s="10">
-        <v>7048</v>
+        <v>5023</v>
       </c>
       <c r="N46" s="11" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O46" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P46" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q46" s="1"/>
+      <c r="R46" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="S46" s="10" t="s">
         <v>9</v>
-      </c>
-      <c r="Q46" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="R46" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="S46" s="10" t="s">
-        <v>11</v>
       </c>
       <c r="T46" s="10"/>
       <c r="U46" s="10"/>
-      <c r="V46" s="10">
-        <v>7692084</v>
-      </c>
+      <c r="V46" s="10"/>
       <c r="W46" s="10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X46" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y46" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z46" s="10">
-        <v>1</v>
-      </c>
-      <c r="AA46" s="10" t="s">
-        <v>259</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A47" s="9" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>121</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>245</v>
+        <v>182</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>118</v>
+        <v>192</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>13</v>
+        <v>190</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="K47" s="12" t="s">
-        <v>96</v>
+        <v>12</v>
+      </c>
+      <c r="K47" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="L47" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M47" s="10">
-        <v>6364</v>
+        <v>6189</v>
       </c>
       <c r="N47" s="11" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P47" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q47" s="1"/>
+      <c r="R47" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="S47" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="Q47" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="R47" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="S47" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="T47" s="10">
-        <v>7</v>
-      </c>
+      <c r="T47" s="10"/>
       <c r="U47" s="10"/>
-      <c r="V47" s="10">
-        <v>19540319</v>
-      </c>
+      <c r="V47" s="10"/>
       <c r="W47" s="10" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="X47" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y47" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z47" s="10">
-        <v>1</v>
-      </c>
-      <c r="AA47" s="10" t="s">
-        <v>259</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A48" s="9" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>122</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>246</v>
+        <v>88</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>221</v>
+        <v>110</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>118</v>
+        <v>191</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>13</v>
+        <v>190</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="K48" s="12" t="s">
-        <v>96</v>
+        <v>190</v>
+      </c>
+      <c r="K48" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="L48" s="10" t="s">
         <v>3</v>
       </c>
       <c r="M48" s="10">
-        <v>9472</v>
+        <v>5246</v>
       </c>
       <c r="N48" s="11" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O48" s="10" t="s">
         <v>5</v>
       </c>
       <c r="P48" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q48" s="1"/>
+      <c r="R48" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="S48" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="Q48" s="12" t="s">
+      <c r="T48" s="10"/>
+      <c r="U48" s="10"/>
+      <c r="V48" s="10"/>
+      <c r="W48" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="R48" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="S48" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="T48" s="10">
-        <v>47</v>
-      </c>
-      <c r="U48" s="10"/>
-      <c r="V48" s="10">
-        <v>7692084</v>
-      </c>
-      <c r="W48" s="10" t="s">
-        <v>12</v>
-      </c>
       <c r="X48" s="10" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Y48" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z48" s="10">
-        <v>1</v>
-      </c>
-      <c r="AA48" s="10" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A49" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B49" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D49" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="F49" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="G49" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="I49" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J49" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="K49" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="L49" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M49" s="10">
-        <v>7045</v>
-      </c>
-      <c r="N49" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="O49" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P49" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q49" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="R49" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="S49" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="T49" s="10"/>
-      <c r="U49" s="10"/>
-      <c r="V49" s="10">
-        <v>7692084</v>
-      </c>
-      <c r="W49" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="X49" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y49" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z49" s="10">
-        <v>1</v>
-      </c>
-      <c r="AA49" s="10" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A50" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B50" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="F50" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="G50" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="I50" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J50" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="K50" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="L50" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M50" s="10">
-        <v>10243</v>
-      </c>
-      <c r="N50" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="O50" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P50" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q50" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="R50" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="S50" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="T50" s="10">
-        <v>7</v>
-      </c>
-      <c r="U50" s="10"/>
-      <c r="V50" s="10">
-        <v>7692084</v>
-      </c>
-      <c r="W50" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="X50" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y50" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z50" s="10">
-        <v>1</v>
-      </c>
-      <c r="AA50" s="10" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A51" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="I51" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J51" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="K51" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="L51" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M51" s="10">
-        <v>8355</v>
-      </c>
-      <c r="N51" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="O51" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q51" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="R51" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="S51" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="T51" s="10">
-        <v>25</v>
-      </c>
-      <c r="U51" s="10"/>
-      <c r="V51" s="10">
-        <v>9934709</v>
-      </c>
-      <c r="W51" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="X51" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y51" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z51" s="10">
-        <v>1</v>
-      </c>
-      <c r="AA51" s="10" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A52" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B52" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="F52" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="G52" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="H52" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="I52" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J52" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="K52" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="L52" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="10">
-        <v>7274</v>
-      </c>
-      <c r="N52" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="O52" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P52" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q52" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="R52" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="S52" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="T52" s="10">
-        <v>10</v>
-      </c>
-      <c r="U52" s="10"/>
-      <c r="V52" s="10">
-        <v>9934709</v>
-      </c>
-      <c r="W52" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="X52" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y52" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z52" s="10">
-        <v>1</v>
-      </c>
-      <c r="AA52" s="10" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A53" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B53" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="C53" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D53" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="F53" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="G53" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="I53" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J53" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="K53" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="L53" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M53" s="10">
-        <v>8214</v>
-      </c>
-      <c r="N53" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="O53" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P53" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q53" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="R53" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="S53" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="T53" s="10">
-        <v>104</v>
-      </c>
-      <c r="U53" s="10"/>
-      <c r="V53" s="10">
-        <v>19540319</v>
-      </c>
-      <c r="W53" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="X53" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y53" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z53" s="10">
-        <v>1</v>
-      </c>
-      <c r="AA53" s="10" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A54" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="B54" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="C54" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="F54" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="G54" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="H54" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="I54" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J54" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="K54" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="L54" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="10">
-        <v>6896</v>
-      </c>
-      <c r="N54" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="O54" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P54" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q54" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="R54" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="S54" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="T54" s="10"/>
-      <c r="U54" s="10"/>
-      <c r="V54" s="10"/>
-      <c r="W54" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="X54" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y54" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z54" s="10">
-        <v>2</v>
-      </c>
-      <c r="AA54" s="10" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A55" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="F55" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="I55" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="J55" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="K55" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="L55" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M55" s="10">
-        <v>5685</v>
-      </c>
-      <c r="N55" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="O55" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P55" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q55" s="12"/>
-      <c r="R55" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="S55" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="T55" s="10"/>
-      <c r="U55" s="10"/>
-      <c r="V55" s="10"/>
-      <c r="W55" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="X55" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y55" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z55" s="10">
-        <v>4</v>
-      </c>
-      <c r="AA55" s="10" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A56" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="B56" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="D56" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="E56" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="F56" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="G56" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="H56" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="I56" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J56" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="K56" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="L56" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M56" s="13"/>
-      <c r="N56" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="O56" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P56" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q56" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="R56" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="S56" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="T56" s="13"/>
-      <c r="U56" s="13"/>
-      <c r="V56" s="13"/>
-      <c r="W56" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="X56" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y56" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z56" s="13">
-        <v>1</v>
-      </c>
-      <c r="AA56" s="10" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="C57" s="2"/>
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z55">
-    <sortCondition ref="G2:G55"/>
-    <sortCondition ref="H2:H55"/>
-    <sortCondition ref="N2:N55"/>
-    <sortCondition ref="P2:P55"/>
-    <sortCondition ref="Q2:Q55"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z48">
+    <sortCondition ref="N2:N48"/>
+    <sortCondition ref="P2:P48"/>
+    <sortCondition ref="Q2:Q48"/>
+    <sortCondition ref="C2:C48"/>
   </sortState>
-  <conditionalFormatting sqref="Z44:Z45">
-    <cfRule type="colorScale" priority="19">
+  <conditionalFormatting sqref="Z49:Z1048576 Z1:Z8">
+    <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6047,31 +5144,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z46">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z47">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z48">
+  <conditionalFormatting sqref="Z9:Z11">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -6083,7 +5156,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z49">
+  <conditionalFormatting sqref="Z12:Z23">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -6095,7 +5168,19 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z52">
+  <conditionalFormatting sqref="Z24:Z25">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z26:Z29">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -6107,7 +5192,55 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z53">
+  <conditionalFormatting sqref="Z30:Z34">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z42:Z43">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z44">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z45">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z35:Z41 Z46">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -6119,56 +5252,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z54">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z55">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z50">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z51">
+  <conditionalFormatting sqref="Z47:Z48">
     <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z56:Z1048576 Z1:Z43 AA1:AA56">
-    <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6192,6 +5277,7 @@
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="4" max="4" width="40.5" customWidth="1"/>
     <col min="5" max="5" width="21.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.2">
@@ -6199,34 +5285,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>1</v>
@@ -6235,70 +5321,70 @@
         <v>2</v>
       </c>
       <c r="N1" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="W1" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="Q1" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="U1" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="V1" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="W1" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="Z1" s="4" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -6313,10 +5399,10 @@
         <v>5</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>6</v>
@@ -6332,13 +5418,13 @@
         <v>31167914</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z2" s="2">
         <v>1</v>
@@ -6346,29 +5432,29 @@
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -6383,10 +5469,10 @@
         <v>5</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>6</v>
@@ -6402,13 +5488,13 @@
         <v>31167914</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z3" s="2">
         <v>1</v>
@@ -6416,56 +5502,56 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="7" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>7</v>
@@ -6476,13 +5562,13 @@
         <v>28397686</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z4" s="2">
         <v>1</v>
@@ -6490,56 +5576,56 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M5" s="2"/>
       <c r="N5" s="7" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="S5" s="2" t="s">
         <v>7</v>
@@ -6550,13 +5636,13 @@
         <v>28397686</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z5" s="2">
         <v>1</v>
@@ -6564,56 +5650,56 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="7" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="S6" s="2" t="s">
         <v>7</v>
@@ -6624,13 +5710,13 @@
         <v>28397686</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z6" s="2">
         <v>1</v>
@@ -6638,59 +5724,59 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="7" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
@@ -6698,13 +5784,13 @@
         <v>26952212</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z7" s="2">
         <v>3</v>
@@ -6712,59 +5798,59 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M8" s="2"/>
       <c r="N8" s="7" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
@@ -6772,13 +5858,13 @@
         <v>26952212</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z8" s="2">
         <v>3</v>
@@ -6786,7 +5872,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="Z2">
-    <cfRule type="colorScale" priority="5">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6798,7 +5884,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6810,7 +5896,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="colorScale" priority="24">
+    <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6822,7 +5908,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z4:Z5">
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6834,7 +5920,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z6:Z7">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6846,7 +5932,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z8">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/tabular/reference/herv_sublineage_data.xlsx
+++ b/tabular/reference/herv_sublineage_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17BA465D-F397-F743-8226-FFFEDD8020A0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{322FE258-50B4-1049-ADA8-5067A1D05C1F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3460" yWindow="620" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1680" yWindow="620" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sublineage" sheetId="2" r:id="rId1"/>
@@ -1245,7 +1245,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
@@ -1268,6 +1268,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2086,7 +2087,7 @@
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="14" t="s">
         <v>43</v>
       </c>
       <c r="B7" s="12" t="s">

--- a/tabular/reference/herv_sublineage_data.xlsx
+++ b/tabular/reference/herv_sublineage_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{322FE258-50B4-1049-ADA8-5067A1D05C1F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2AB2FE-734C-7841-BAD2-AA079230A84D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1680" yWindow="620" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1580" yWindow="1260" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sublineage" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="231">
   <si>
     <t>sequenceID</t>
   </si>
@@ -65,9 +65,6 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>most_intact</t>
-  </si>
-  <si>
     <t>I</t>
   </si>
   <si>
@@ -194,9 +191,6 @@
     <t>Zetaretrovirus</t>
   </si>
   <si>
-    <t>HERVHF</t>
-  </si>
-  <si>
     <t>HERV-19</t>
   </si>
   <si>
@@ -350,9 +344,6 @@
     <t>sublineage</t>
   </si>
   <si>
-    <t>ERV-1.Gamma.HARLEQUIN</t>
-  </si>
-  <si>
     <t>ERV-3.Lambda.L</t>
   </si>
   <si>
@@ -404,87 +395,24 @@
     <t>ERV-1.Theta.24.b</t>
   </si>
   <si>
-    <t>ERV-1.Theta.Lb.38</t>
-  </si>
-  <si>
-    <t>ERV-1.Theta.Lb.LOR1</t>
-  </si>
-  <si>
-    <t>ERV-1.Theta.Lb.37</t>
-  </si>
-  <si>
-    <t>ERV-1.Theta.Lb.43</t>
-  </si>
-  <si>
-    <t>ERV-1.Theta.Lb.101</t>
-  </si>
-  <si>
-    <t>ERV-1.Theta.Lb.MER4</t>
-  </si>
-  <si>
-    <t>ERV-1.Theta.Lb.MER4b</t>
-  </si>
-  <si>
-    <t>ERV-1.Theta.Lb.MER61</t>
-  </si>
-  <si>
-    <t>ERV-1.Theta.Lb.MER89</t>
-  </si>
-  <si>
     <t>ERV-1.Zeta.primax</t>
   </si>
   <si>
     <t>ERV-1.Zeta.HF.52A</t>
   </si>
   <si>
-    <t>ERV-1.Zeta.W9.G25</t>
-  </si>
-  <si>
     <t>ERV-1.Zeta.19</t>
   </si>
   <si>
     <t>ERV-1.Zeta.35</t>
   </si>
   <si>
-    <t>ERV-1.Zeta.MER41</t>
-  </si>
-  <si>
-    <t>ERV-1.Zeta.MER57</t>
-  </si>
-  <si>
-    <t>ERV-1.Zeta.MER83A</t>
-  </si>
-  <si>
-    <t>ERV-1.Zeta.MER83B</t>
-  </si>
-  <si>
-    <t>ERV-1.Zeta.MER84</t>
-  </si>
-  <si>
     <t>Standardised lineage name</t>
   </si>
   <si>
-    <t>HERV-Fc1</t>
-  </si>
-  <si>
-    <t>ERV-1.HF.Fc.1</t>
-  </si>
-  <si>
     <t>AncRecon</t>
   </si>
   <si>
-    <t>HERV-Fc2</t>
-  </si>
-  <si>
-    <t>ERV-1.HF.Fc.2</t>
-  </si>
-  <si>
-    <t>human endogenous retrovirus F(c) 2</t>
-  </si>
-  <si>
-    <t>human endogenous retrovirus F(c) 1</t>
-  </si>
-  <si>
     <t>HERV-T1</t>
   </si>
   <si>
@@ -572,15 +500,9 @@
     <t>medium reiteration frequency repeat 76</t>
   </si>
   <si>
-    <t>ERV-1.Zeta.huersP1</t>
-  </si>
-  <si>
     <t>ERV-1.Zeta.P.huersP3b</t>
   </si>
   <si>
-    <t>ERV-1.Zeta.P.huersP2</t>
-  </si>
-  <si>
     <t>entity_type</t>
   </si>
   <si>
@@ -614,24 +536,9 @@
     <t>Theta.Lb</t>
   </si>
   <si>
-    <t>ERV-1.Theta.Lb.MER65</t>
-  </si>
-  <si>
-    <t>ERV-1.Theta.Lb.MER34b</t>
-  </si>
-  <si>
-    <t>ERV-1.Theta.Lb.MER31</t>
-  </si>
-  <si>
-    <t>ERV-1.Theta.Lb.MER21</t>
-  </si>
-  <si>
     <t>ERV-1.Gamma.T</t>
   </si>
   <si>
-    <t>ERV-1.HF.Fc</t>
-  </si>
-  <si>
     <t>ERV-2.Gamma.E</t>
   </si>
   <si>
@@ -656,9 +563,6 @@
     <t>ERV-1.Zeta.P</t>
   </si>
   <si>
-    <t>ERV-1.Zeta.W9</t>
-  </si>
-  <si>
     <t>relationship</t>
   </si>
   <si>
@@ -717,13 +621,106 @@
   </si>
   <si>
     <t>ERV-1.Theta.V</t>
+  </si>
+  <si>
+    <t>HuRRS-P</t>
+  </si>
+  <si>
+    <t>ERV-1.Zeta.W9P.P.2</t>
+  </si>
+  <si>
+    <t>ERV-1.Zeta.W9P.P.1</t>
+  </si>
+  <si>
+    <t>ERV-1.Zeta.W9P.P.HuRRSp</t>
+  </si>
+  <si>
+    <t>ERV-1.Zeta.W9P.P</t>
+  </si>
+  <si>
+    <t>ERV-1.Zeta.W9P.P.G25</t>
+  </si>
+  <si>
+    <t>phylogeny_group</t>
+  </si>
+  <si>
+    <t>W9P</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>ERVR-1.Zeta.MER41</t>
+  </si>
+  <si>
+    <t>ERVR-1.Zeta.MER57</t>
+  </si>
+  <si>
+    <t>ERVR-1.Gamma.Eta.HQ</t>
+  </si>
+  <si>
+    <t>ERV-1.Unclassified.MER4</t>
+  </si>
+  <si>
+    <t>ERV-1.Unclassified.MER4b</t>
+  </si>
+  <si>
+    <t>ERV-1.Unclassified.MER65</t>
+  </si>
+  <si>
+    <t>Rhoretrovirus</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.LOR1</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.37</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.43</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.38</t>
+  </si>
+  <si>
+    <t>ERV-1.Theta.101</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.MER31</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.MER21</t>
+  </si>
+  <si>
+    <t>ERV-1.Theta.MER34b</t>
+  </si>
+  <si>
+    <t>ERV-1.Theta.MER61</t>
+  </si>
+  <si>
+    <t>ERV-1.Theta.MER89</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>ERVR-1.Zeta.MER83A</t>
+  </si>
+  <si>
+    <t>ERVR-1.Zeta.MER83B</t>
+  </si>
+  <si>
+    <t>ERVR-1.Zeta.MER84</t>
+  </si>
+  <si>
+    <t>entity_level</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -869,6 +866,14 @@
       <i/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1245,7 +1250,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
@@ -1269,6 +1274,12 @@
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1624,7 +1635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB9083D8-DE01-F14E-ACB5-AF33867092C5}">
-  <dimension ref="A1:Z48"/>
+  <dimension ref="A1:AA43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -1633,465 +1644,482 @@
     <col min="4" max="4" width="40.33203125" customWidth="1"/>
     <col min="5" max="5" width="21.6640625" customWidth="1"/>
     <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="19.6640625" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" customWidth="1"/>
-    <col min="9" max="9" width="14.5" customWidth="1"/>
-    <col min="10" max="10" width="25" customWidth="1"/>
-    <col min="11" max="11" width="19" customWidth="1"/>
-    <col min="14" max="14" width="10.83203125" style="8"/>
-    <col min="16" max="16" width="21" customWidth="1"/>
+    <col min="7" max="8" width="19.6640625" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.5" customWidth="1"/>
+    <col min="11" max="11" width="25" customWidth="1"/>
+    <col min="12" max="12" width="19" customWidth="1"/>
+    <col min="15" max="15" width="10.83203125" style="8"/>
+    <col min="17" max="17" width="21" customWidth="1"/>
+    <col min="20" max="20" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="O1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="N1" s="6" t="s">
+      <c r="Q1" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="X1" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="Z1" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
-        <v>86</v>
-      </c>
       <c r="B2" s="12" t="s">
-        <v>109</v>
+        <v>211</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>11</v>
+        <v>162</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M2" s="10">
+        <v>11</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" s="10">
         <v>6896</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="O2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P2" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="R2" s="10" t="s">
+      <c r="R2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S2" s="10" t="s">
+      <c r="T2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T2" s="10"/>
       <c r="U2" s="10"/>
       <c r="V2" s="10"/>
-      <c r="W2" s="10" t="s">
+      <c r="W2" s="10"/>
+      <c r="X2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="X2" s="10" t="s">
-        <v>11</v>
-      </c>
       <c r="Y2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z2" s="10">
+      <c r="Z2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA2" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>223</v>
+        <v>121</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>92</v>
+        <v>34</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>213</v>
+        <v>164</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>11</v>
+        <v>162</v>
       </c>
       <c r="J3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>91</v>
+      <c r="K3" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M3" s="10">
-        <v>9611</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O3" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N3" s="10">
+        <v>4936</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="R3" s="10" t="s">
+      <c r="Q3" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="R3" s="1"/>
+      <c r="S3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S3" s="10" t="s">
+      <c r="T3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="10"/>
       <c r="U3" s="10"/>
       <c r="V3" s="10"/>
-      <c r="W3" s="10" t="s">
-        <v>10</v>
-      </c>
+      <c r="W3" s="10"/>
       <c r="X3" s="10" t="s">
-        <v>11</v>
+        <v>198</v>
       </c>
       <c r="Y3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z3" s="10">
-        <v>2</v>
+      <c r="Z3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA3" s="10">
+        <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>11</v>
+        <v>162</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4" s="10">
-        <v>7613</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O4" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N4" s="10">
+        <v>9084</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P4" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="10" t="s">
+      <c r="Q4" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="R4" s="1"/>
+      <c r="S4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S4" s="10" t="s">
+      <c r="T4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T4" s="10"/>
       <c r="U4" s="10"/>
       <c r="V4" s="10"/>
-      <c r="W4" s="10" t="s">
-        <v>10</v>
-      </c>
+      <c r="W4" s="10"/>
       <c r="X4" s="10" t="s">
-        <v>11</v>
+        <v>198</v>
       </c>
       <c r="Y4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z4" s="10">
-        <v>3</v>
+      <c r="Z4" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA4" s="10">
+        <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>127</v>
+        <v>219</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="J5" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M5" s="10">
+        <v>41</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="10">
         <v>1786</v>
       </c>
-      <c r="N5" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O5" s="10" t="s">
+      <c r="O5" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P5" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="10" t="s">
+      <c r="Q5" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="R5" s="1"/>
+      <c r="S5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S5" s="10" t="s">
+      <c r="T5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="10"/>
       <c r="U5" s="10"/>
       <c r="V5" s="10"/>
-      <c r="W5" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="W5" s="10"/>
       <c r="X5" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="Y5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z5" s="10">
+      <c r="Z5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA5" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A6" s="9" t="s">
-        <v>225</v>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A6" s="14" t="s">
+        <v>42</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>225</v>
+        <v>42</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>231</v>
+        <v>42</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>175</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>213</v>
+        <v>164</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>225</v>
+        <v>12</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M6" s="13">
-        <v>2482</v>
-      </c>
-      <c r="N6" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O6" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N6" s="10">
+        <v>8120</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P6" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10" t="s">
-        <v>13</v>
-      </c>
+      <c r="Q6" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="R6" s="1"/>
       <c r="S6" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="13"/>
-      <c r="W6" s="10" t="s">
-        <v>36</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="T6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="U6" s="10"/>
+      <c r="V6" s="10"/>
+      <c r="W6" s="10"/>
       <c r="X6" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="Y6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z6" s="13">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="Z6" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA6" s="10">
+        <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A7" s="14" t="s">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A7" s="9" t="s">
         <v>43</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>128</v>
+        <v>217</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>43</v>
@@ -2100,70 +2128,73 @@
         <v>43</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L7" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="10">
-        <v>8120</v>
-      </c>
-      <c r="N7" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O7" s="10" t="s">
+      <c r="M7" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="10">
+        <v>4060</v>
+      </c>
+      <c r="O7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P7" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="10" t="s">
+      <c r="Q7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="R7" s="1"/>
+      <c r="S7" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S7" s="10" t="s">
+      <c r="T7" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T7" s="10"/>
       <c r="U7" s="10"/>
       <c r="V7" s="10"/>
-      <c r="W7" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="W7" s="10"/>
       <c r="X7" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="Y7" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z7" s="10">
+      <c r="Z7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA7" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>129</v>
+        <v>218</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>44</v>
@@ -2172,2969 +2203,2719 @@
         <v>44</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K8" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L8" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="10">
-        <v>4060</v>
-      </c>
-      <c r="N8" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O8" s="10" t="s">
+      <c r="M8" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="10">
+        <v>4798</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P8" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="10" t="s">
+      <c r="Q8" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="R8" s="1"/>
+      <c r="S8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S8" s="10" t="s">
+      <c r="T8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T8" s="10"/>
       <c r="U8" s="10"/>
       <c r="V8" s="10"/>
-      <c r="W8" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="W8" s="10"/>
       <c r="X8" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="Y8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z8" s="10">
+      <c r="Z8" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA8" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>45</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>45</v>
       </c>
       <c r="D9" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L9" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="L9" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="10">
-        <v>4798</v>
-      </c>
-      <c r="N9" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O9" s="10" t="s">
+      <c r="M9" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="10">
+        <v>6639</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P9" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="10" t="s">
+      <c r="Q9" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="R9" s="1"/>
+      <c r="S9" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S9" s="10" t="s">
+      <c r="T9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T9" s="10"/>
       <c r="U9" s="10"/>
       <c r="V9" s="10"/>
-      <c r="W9" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="W9" s="10"/>
       <c r="X9" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="Y9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z9" s="10">
+      <c r="Z9" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA9" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>131</v>
+        <v>222</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>46</v>
       </c>
       <c r="D10" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G10" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>192</v>
-      </c>
       <c r="H10" s="10" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K10" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L10" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="10">
-        <v>6639</v>
-      </c>
-      <c r="N10" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O10" s="10" t="s">
+      <c r="M10" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="10">
+        <v>933</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P10" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="10" t="s">
+      <c r="Q10" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="R10" s="1"/>
+      <c r="S10" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S10" s="10" t="s">
+      <c r="T10" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T10" s="10"/>
       <c r="U10" s="10"/>
       <c r="V10" s="10"/>
-      <c r="W10" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="W10" s="10"/>
       <c r="X10" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="Y10" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z10" s="10">
+      <c r="Z10" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA10" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>47</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="J11" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K11" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="L11" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M11" s="10">
-        <v>933</v>
-      </c>
-      <c r="N11" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O11" s="10" t="s">
+      <c r="M11" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N11" s="10">
+        <v>4936</v>
+      </c>
+      <c r="O11" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P11" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P11" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="10" t="s">
+      <c r="Q11" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="R11" s="1"/>
+      <c r="S11" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S11" s="10" t="s">
+      <c r="T11" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T11" s="10"/>
       <c r="U11" s="10"/>
       <c r="V11" s="10"/>
-      <c r="W11" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="W11" s="10"/>
       <c r="X11" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="Y11" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z11" s="10">
+      <c r="Z11" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA11" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
         <v>48</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>48</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="J12" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K12" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L12" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="L12" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M12" s="10">
-        <v>4936</v>
-      </c>
-      <c r="N12" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O12" s="10" t="s">
+      <c r="M12" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="10">
+        <v>5356</v>
+      </c>
+      <c r="O12" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P12" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P12" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="10" t="s">
+      <c r="Q12" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="R12" s="1"/>
+      <c r="S12" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S12" s="10" t="s">
+      <c r="T12" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T12" s="10"/>
       <c r="U12" s="10"/>
       <c r="V12" s="10"/>
-      <c r="W12" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="W12" s="10"/>
       <c r="X12" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="Y12" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z12" s="10">
+      <c r="Z12" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA12" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="J13" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M13" s="10">
-        <v>5356</v>
-      </c>
-      <c r="N13" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O13" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N13" s="10">
+        <v>5217</v>
+      </c>
+      <c r="O13" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P13" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P13" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="10" t="s">
+      <c r="Q13" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="R13" s="1"/>
+      <c r="S13" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S13" s="10" t="s">
+      <c r="T13" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T13" s="10"/>
       <c r="U13" s="10"/>
       <c r="V13" s="10"/>
-      <c r="W13" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="W13" s="10"/>
       <c r="X13" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="Y13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z13" s="10">
+      <c r="Z13" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA13" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>132</v>
+        <v>225</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="J14" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="10">
-        <v>6387</v>
-      </c>
-      <c r="N14" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O14" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="M14" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="10">
+        <v>7048</v>
+      </c>
+      <c r="O14" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P14" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="10" t="s">
+      <c r="Q14" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="R14" s="1"/>
+      <c r="S14" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S14" s="10" t="s">
+      <c r="T14" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T14" s="10"/>
       <c r="U14" s="10"/>
       <c r="V14" s="10"/>
-      <c r="W14" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="W14" s="10"/>
       <c r="X14" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="Y14" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z14" s="10">
+      <c r="Z14" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA14" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>51</v>
+        <v>192</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>133</v>
+        <v>194</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>51</v>
+        <v>192</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="G15" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="L15" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H15" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K15" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="L15" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M15" s="10">
-        <v>6758</v>
-      </c>
-      <c r="N15" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O15" s="10" t="s">
+      <c r="M15" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P15" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P15" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="10" t="s">
+      <c r="Q15" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="R15" s="10"/>
+      <c r="S15" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="T15" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="U15" s="13"/>
+      <c r="V15" s="13"/>
+      <c r="W15" s="13"/>
+      <c r="X15" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y15" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z15" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA15" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A16" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L16" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="M16" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N16" s="10">
+        <v>6387</v>
+      </c>
+      <c r="O16" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P16" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q16" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="R16" s="1"/>
+      <c r="S16" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S15" s="10" t="s">
+      <c r="T16" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T15" s="10"/>
-      <c r="U15" s="10"/>
-      <c r="V15" s="10"/>
-      <c r="W15" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="X15" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y15" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z15" s="10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A16" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K16" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="L16" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M16" s="10">
-        <v>5217</v>
-      </c>
-      <c r="N16" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O16" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P16" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="S16" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="T16" s="10"/>
       <c r="U16" s="10"/>
       <c r="V16" s="10"/>
-      <c r="W16" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="W16" s="10"/>
       <c r="X16" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="Y16" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z16" s="10">
+      <c r="Z16" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA16" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="J17" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="10">
-        <v>4871</v>
-      </c>
-      <c r="N17" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O17" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="10">
+        <v>6758</v>
+      </c>
+      <c r="O17" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P17" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P17" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="10" t="s">
+      <c r="Q17" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="R17" s="1"/>
+      <c r="S17" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S17" s="10" t="s">
+      <c r="T17" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T17" s="10"/>
       <c r="U17" s="10"/>
       <c r="V17" s="10"/>
-      <c r="W17" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="W17" s="10"/>
       <c r="X17" s="10" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="Y17" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z17" s="10">
+      <c r="Z17" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA17" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>135</v>
+        <v>214</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="J18" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="10">
-        <v>7048</v>
-      </c>
-      <c r="N18" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O18" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="M18" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="10">
+        <v>4871</v>
+      </c>
+      <c r="O18" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P18" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P18" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="10" t="s">
+      <c r="Q18" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="R18" s="1"/>
+      <c r="S18" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S18" s="10" t="s">
+      <c r="T18" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T18" s="10"/>
       <c r="U18" s="10"/>
       <c r="V18" s="10"/>
-      <c r="W18" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="W18" s="10"/>
       <c r="X18" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="Y18" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z18" s="10">
+        <v>10</v>
+      </c>
+      <c r="Z18" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA18" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="M19" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N19" s="10">
+        <v>4981</v>
+      </c>
+      <c r="O19" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P19" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K19" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="L19" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M19" s="10">
-        <v>4102</v>
-      </c>
-      <c r="N19" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O19" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P19" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="10" t="s">
+      <c r="R19" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="S19" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S19" s="10" t="s">
+      <c r="T19" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T19" s="10"/>
       <c r="U19" s="10"/>
       <c r="V19" s="10"/>
-      <c r="W19" s="10" t="s">
-        <v>10</v>
-      </c>
+      <c r="W19" s="10"/>
       <c r="X19" s="10" t="s">
         <v>10</v>
       </c>
       <c r="Y19" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z19" s="10">
+      <c r="Z19" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA19" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>224</v>
+        <v>59</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>228</v>
+        <v>59</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>213</v>
+        <v>164</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>108</v>
+        <v>165</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>11</v>
+        <v>164</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="13"/>
-      <c r="N20" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O20" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="M20" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="10">
+        <v>6996</v>
+      </c>
+      <c r="O20" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P20" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P20" s="10" t="s">
-        <v>227</v>
-      </c>
       <c r="Q20" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="R20" s="10" t="s">
-        <v>13</v>
+        <v>55</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="T20" s="13"/>
-      <c r="U20" s="13"/>
-      <c r="V20" s="13"/>
-      <c r="W20" s="10" t="s">
-        <v>36</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="T20" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="U20" s="10"/>
+      <c r="V20" s="10"/>
+      <c r="W20" s="10"/>
       <c r="X20" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z20" s="13">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="Z20" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA20" s="10">
+        <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>124</v>
+        <v>202</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>93</v>
+        <v>60</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>60</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="10">
-        <v>4936</v>
-      </c>
-      <c r="N21" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O21" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="M21" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="10">
+        <v>11027</v>
+      </c>
+      <c r="O21" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P21" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P21" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="10" t="s">
+      <c r="Q21" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="S21" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S21" s="10" t="s">
+      <c r="T21" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T21" s="10"/>
       <c r="U21" s="10"/>
       <c r="V21" s="10"/>
-      <c r="W21" s="10" t="s">
-        <v>230</v>
+      <c r="W21" s="10">
+        <v>2825129</v>
       </c>
       <c r="X21" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="Y21" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z21" s="10">
+      <c r="Z21" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA21" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>125</v>
+        <v>201</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>94</v>
+        <v>61</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>61</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="10">
-        <v>9084</v>
-      </c>
-      <c r="N22" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O22" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="M22" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="10">
+        <v>8987</v>
+      </c>
+      <c r="O22" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P22" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P22" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="10" t="s">
+      <c r="Q22" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="S22" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S22" s="10" t="s">
+      <c r="T22" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T22" s="10"/>
       <c r="U22" s="10"/>
       <c r="V22" s="10"/>
-      <c r="W22" s="10" t="s">
-        <v>230</v>
+      <c r="W22" s="13">
+        <v>2825129</v>
       </c>
       <c r="X22" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y22" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z22" s="10">
+      <c r="Z22" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA22" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:26" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>66</v>
+        <v>200</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>137</v>
+        <v>203</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>66</v>
+        <v>200</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="E23" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="10"/>
+      <c r="O23" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P23" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="R23" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="J23" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K23" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="L23" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="10">
-        <v>4981</v>
-      </c>
-      <c r="N23" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O23" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P23" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="R23" s="10" t="s">
-        <v>6</v>
-      </c>
       <c r="S23" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="T23" s="10"/>
+        <v>13</v>
+      </c>
+      <c r="T23" s="10" t="s">
+        <v>3</v>
+      </c>
       <c r="U23" s="10"/>
       <c r="V23" s="10"/>
-      <c r="W23" s="10" t="s">
+      <c r="W23" s="13"/>
+      <c r="X23" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="X23" s="10" t="s">
-        <v>11</v>
-      </c>
       <c r="Y23" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z23" s="10">
-        <v>3</v>
+      <c r="Z23" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA23" s="13">
+        <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>99</v>
+        <v>56</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>95</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="J24" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="10">
-        <v>6996</v>
-      </c>
-      <c r="N24" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O24" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M24" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="10">
+        <v>5586</v>
+      </c>
+      <c r="O24" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P24" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P24" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="R24" s="10" t="s">
+      <c r="Q24" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="R24" s="1"/>
+      <c r="S24" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S24" s="10" t="s">
+      <c r="T24" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T24" s="10"/>
       <c r="U24" s="10"/>
       <c r="V24" s="10"/>
-      <c r="W24" s="10" t="s">
-        <v>10</v>
-      </c>
+      <c r="W24" s="10"/>
       <c r="X24" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="Y24" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z24" s="10">
-        <v>3</v>
+      <c r="Z24" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA24" s="10">
+        <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>183</v>
+        <v>127</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>213</v>
+        <v>164</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>190</v>
+        <v>106</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M25" s="10">
-        <v>11027</v>
-      </c>
-      <c r="N25" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O25" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="M25" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N25" s="10">
+        <v>6918</v>
+      </c>
+      <c r="O25" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P25" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P25" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="R25" s="10" t="s">
+      <c r="Q25" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="R25" s="1"/>
+      <c r="S25" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S25" s="10" t="s">
+      <c r="T25" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T25" s="10"/>
       <c r="U25" s="10"/>
-      <c r="V25" s="10">
-        <v>2825129</v>
-      </c>
-      <c r="W25" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="V25" s="10"/>
+      <c r="W25" s="10"/>
       <c r="X25" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="Y25" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z25" s="10">
+      <c r="Z25" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA25" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
         <v>63</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>63</v>
       </c>
       <c r="D26" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L26" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="M26" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="10">
+        <v>3944</v>
+      </c>
+      <c r="O26" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P26" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q26" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="R26" s="1"/>
+      <c r="S26" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="T26" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="U26" s="10"/>
+      <c r="V26" s="10"/>
+      <c r="W26" s="10"/>
+      <c r="X26" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y26" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z26" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA26" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A27" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="F26" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="H26" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="K26" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="L26" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="10">
-        <v>8987</v>
-      </c>
-      <c r="N26" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O26" s="10" t="s">
+      <c r="C27" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L27" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="M27" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="10">
+        <v>7133</v>
+      </c>
+      <c r="O27" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P27" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P26" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q26" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="R26" s="10" t="s">
+      <c r="Q27" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="R27" s="1"/>
+      <c r="S27" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S26" s="10" t="s">
+      <c r="T27" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T26" s="10"/>
-      <c r="U26" s="10"/>
-      <c r="V26" s="13">
-        <v>2825129</v>
-      </c>
-      <c r="W26" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="X26" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y26" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z26" s="10">
+      <c r="U27" s="10"/>
+      <c r="V27" s="10"/>
+      <c r="W27" s="10"/>
+      <c r="X27" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y27" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z27" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA27" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A27" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="L27" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="10">
-        <v>7418</v>
-      </c>
-      <c r="N27" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O27" s="10" t="s">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A28" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K28" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L28" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="M28" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N28" s="10">
+        <v>4285</v>
+      </c>
+      <c r="O28" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P28" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P27" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="R27" s="10" t="s">
+      <c r="Q28" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="R28" s="1"/>
+      <c r="S28" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S27" s="10" t="s">
+      <c r="T28" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T27" s="10"/>
-      <c r="U27" s="10"/>
-      <c r="V27" s="13">
-        <v>2825129</v>
-      </c>
-      <c r="W27" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="X27" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y27" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z27" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A28" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="J28" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K28" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="L28" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M28" s="10">
-        <v>5586</v>
-      </c>
-      <c r="N28" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O28" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P28" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="S28" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="T28" s="10"/>
       <c r="U28" s="10"/>
       <c r="V28" s="10"/>
-      <c r="W28" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="W28" s="10"/>
       <c r="X28" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="Y28" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z28" s="10">
+      <c r="Z28" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA28" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>140</v>
+        <v>228</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>98</v>
+        <v>155</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>205</v>
+        <v>174</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="J29" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M29" s="10">
-        <v>6918</v>
-      </c>
-      <c r="N29" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O29" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="M29" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N29" s="10">
+        <v>4880</v>
+      </c>
+      <c r="O29" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P29" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P29" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="10" t="s">
+      <c r="Q29" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="R29" s="1"/>
+      <c r="S29" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S29" s="10" t="s">
+      <c r="T29" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T29" s="10"/>
       <c r="U29" s="10"/>
       <c r="V29" s="10"/>
-      <c r="W29" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="W29" s="10"/>
       <c r="X29" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="Y29" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z29" s="10">
+      <c r="Z29" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA29" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>141</v>
+        <v>229</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>205</v>
+        <v>174</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="J30" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M30" s="10">
-        <v>3944</v>
-      </c>
-      <c r="N30" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O30" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="M30" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N30" s="10">
+        <v>2880</v>
+      </c>
+      <c r="O30" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P30" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P30" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="10" t="s">
+      <c r="Q30" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="R30" s="1"/>
+      <c r="S30" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="S30" s="10" t="s">
+      <c r="T30" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T30" s="10"/>
       <c r="U30" s="10"/>
       <c r="V30" s="10"/>
-      <c r="W30" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="W30" s="10"/>
       <c r="X30" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y30" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z30" s="10">
-        <v>4</v>
+        <v>10</v>
+      </c>
+      <c r="Z30" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA30" s="10">
+        <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>142</v>
+        <v>20</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>120</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>177</v>
+        <v>20</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>205</v>
+        <v>107</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="J31" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="L31" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M31" s="10">
-        <v>7133</v>
-      </c>
-      <c r="N31" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O31" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N31" s="10">
+        <v>6070</v>
+      </c>
+      <c r="O31" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="P31" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P31" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="10" t="s">
-        <v>6</v>
+      <c r="Q31" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="R31" s="15">
+        <v>16</v>
       </c>
       <c r="S31" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="T31" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T31" s="10"/>
       <c r="U31" s="10"/>
       <c r="V31" s="10"/>
-      <c r="W31" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="W31" s="10"/>
       <c r="X31" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y31" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z31" s="10">
-        <v>4</v>
+      <c r="Z31" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA31" s="10">
+        <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>143</v>
+        <v>21</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>107</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>178</v>
+        <v>85</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>205</v>
+        <v>107</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="10">
-        <v>4285</v>
-      </c>
-      <c r="N32" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O32" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M32" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="10">
+        <v>5667</v>
+      </c>
+      <c r="O32" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="P32" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P32" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="10" t="s">
-        <v>6</v>
+      <c r="Q32" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="R32" s="15" t="s">
+        <v>226</v>
       </c>
       <c r="S32" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="T32" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T32" s="10"/>
       <c r="U32" s="10"/>
       <c r="V32" s="10"/>
-      <c r="W32" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="W32" s="10"/>
       <c r="X32" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y32" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z32" s="10">
-        <v>4</v>
+      <c r="Z32" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA32" s="10">
+        <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>144</v>
+        <v>22</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>116</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>179</v>
+        <v>22</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>205</v>
+        <v>107</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="L33" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="10">
-        <v>4880</v>
-      </c>
-      <c r="N33" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O33" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M33" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="10">
+        <v>5714</v>
+      </c>
+      <c r="O33" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="P33" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P33" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q33" s="1"/>
-      <c r="R33" s="10" t="s">
-        <v>6</v>
+      <c r="Q33" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>226</v>
       </c>
       <c r="S33" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="T33" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T33" s="10"/>
       <c r="U33" s="10"/>
       <c r="V33" s="10"/>
-      <c r="W33" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="W33" s="10"/>
       <c r="X33" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y33" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z33" s="10">
-        <v>4</v>
+      <c r="Z33" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA33" s="10">
+        <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>145</v>
+        <v>24</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>109</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>180</v>
+        <v>98</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>205</v>
+        <v>107</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>192</v>
+        <v>164</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>165</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="J34" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M34" s="10">
-        <v>2880</v>
-      </c>
-      <c r="N34" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O34" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="M34" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N34" s="10">
+        <v>4996</v>
+      </c>
+      <c r="O34" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="P34" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P34" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q34" s="1"/>
-      <c r="R34" s="10" t="s">
-        <v>6</v>
+      <c r="Q34" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="R34" s="16">
+        <v>16</v>
       </c>
       <c r="S34" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="T34" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T34" s="10"/>
       <c r="U34" s="10"/>
       <c r="V34" s="10"/>
-      <c r="W34" s="10" t="s">
-        <v>10</v>
-      </c>
+      <c r="W34" s="10"/>
       <c r="X34" s="10" t="s">
         <v>10</v>
       </c>
       <c r="Y34" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z34" s="10">
-        <v>3</v>
+      <c r="Z34" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA34" s="10">
+        <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>191</v>
+        <v>164</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>165</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>11</v>
+        <v>163</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="10">
-        <v>6070</v>
-      </c>
-      <c r="N35" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="M35" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="10">
+        <v>3556</v>
+      </c>
+      <c r="O35" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="P35" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="O35" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P35" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q35" s="1"/>
-      <c r="R35" s="10" t="s">
+      <c r="R35" s="1"/>
+      <c r="S35" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="S35" s="10" t="s">
+      <c r="T35" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T35" s="10"/>
       <c r="U35" s="10"/>
       <c r="V35" s="10"/>
-      <c r="W35" s="10" t="s">
-        <v>10</v>
-      </c>
+      <c r="W35" s="10"/>
       <c r="X35" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="Y35" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z35" s="10">
-        <v>2</v>
+      <c r="Z35" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA35" s="10">
+        <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>213</v>
+        <v>164</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>11</v>
+        <v>163</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="L36" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M36" s="10">
-        <v>5667</v>
-      </c>
-      <c r="N36" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="M36" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N36" s="10">
+        <v>5343</v>
+      </c>
+      <c r="O36" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="P36" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q36" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="O36" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P36" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q36" s="1"/>
-      <c r="R36" s="10" t="s">
+      <c r="R36" s="1"/>
+      <c r="S36" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="S36" s="10" t="s">
+      <c r="T36" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T36" s="10"/>
       <c r="U36" s="10"/>
       <c r="V36" s="10"/>
-      <c r="W36" s="10" t="s">
-        <v>10</v>
-      </c>
+      <c r="W36" s="10"/>
       <c r="X36" s="10" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="Y36" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z36" s="10">
-        <v>2</v>
+      <c r="Z36" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA36" s="10">
+        <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>90</v>
+        <v>28</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>101</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>213</v>
+        <v>164</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>11</v>
+        <v>162</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="L37" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M37" s="10">
-        <v>5714</v>
-      </c>
-      <c r="N37" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M37" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N37" s="10">
+        <v>5530</v>
+      </c>
+      <c r="O37" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="P37" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q37" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="O37" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P37" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q37" s="1"/>
-      <c r="R37" s="10" t="s">
+      <c r="R37" s="1"/>
+      <c r="S37" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="S37" s="10" t="s">
+      <c r="T37" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T37" s="10"/>
       <c r="U37" s="10"/>
       <c r="V37" s="10"/>
-      <c r="W37" s="10" t="s">
-        <v>10</v>
-      </c>
+      <c r="W37" s="10"/>
       <c r="X37" s="10" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="Y37" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z37" s="10">
-        <v>2</v>
+      <c r="Z37" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA37" s="10">
+        <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38" s="9" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>89</v>
+        <v>29</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>102</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>213</v>
+        <v>164</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>11</v>
+        <v>162</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L38" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M38" s="10">
-        <v>5667</v>
-      </c>
-      <c r="N38" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="M38" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="10">
+        <v>3329</v>
+      </c>
+      <c r="O38" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="P38" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q38" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="O38" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P38" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q38" s="1"/>
-      <c r="R38" s="10" t="s">
+      <c r="R38" s="1"/>
+      <c r="S38" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="S38" s="10" t="s">
+      <c r="T38" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T38" s="10"/>
       <c r="U38" s="10"/>
       <c r="V38" s="10"/>
-      <c r="W38" s="10" t="s">
-        <v>10</v>
-      </c>
+      <c r="W38" s="10"/>
       <c r="X38" s="10" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="Y38" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z38" s="10">
-        <v>2</v>
+      <c r="Z38" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA38" s="10">
+        <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>11</v>
+        <v>162</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="L39" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M39" s="10">
-        <v>4996</v>
-      </c>
-      <c r="N39" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="M39" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N39" s="10">
+        <v>3037</v>
+      </c>
+      <c r="O39" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="P39" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q39" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="O39" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P39" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q39" s="1"/>
-      <c r="R39" s="10" t="s">
+      <c r="R39" s="1"/>
+      <c r="S39" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="S39" s="10" t="s">
+      <c r="T39" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T39" s="10"/>
       <c r="U39" s="10"/>
       <c r="V39" s="10"/>
-      <c r="W39" s="10" t="s">
-        <v>10</v>
-      </c>
+      <c r="W39" s="10"/>
       <c r="X39" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="Y39" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z39" s="10">
-        <v>2</v>
+      <c r="Z39" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA39" s="10">
+        <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>110</v>
+        <v>173</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>106</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="K40" s="10" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="L40" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M40" s="10">
-        <v>3556</v>
-      </c>
-      <c r="N40" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="M40" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N40" s="10">
+        <v>5685</v>
+      </c>
+      <c r="O40" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="P40" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q40" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="O40" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P40" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q40" s="1"/>
-      <c r="R40" s="10" t="s">
+      <c r="R40" s="1"/>
+      <c r="S40" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="S40" s="10" t="s">
+      <c r="T40" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T40" s="10"/>
       <c r="U40" s="10"/>
       <c r="V40" s="10"/>
-      <c r="W40" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="W40" s="10"/>
       <c r="X40" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="Y40" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z40" s="10">
+      <c r="Z40" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA40" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>102</v>
+        <v>157</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>110</v>
+        <v>173</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="L41" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="10">
-        <v>5343</v>
-      </c>
-      <c r="N41" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="M41" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="10">
+        <v>5023</v>
+      </c>
+      <c r="O41" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="P41" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q41" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="O41" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P41" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q41" s="1"/>
-      <c r="R41" s="10" t="s">
+      <c r="R41" s="1"/>
+      <c r="S41" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="S41" s="10" t="s">
+      <c r="T41" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T41" s="10"/>
       <c r="U41" s="10"/>
       <c r="V41" s="10"/>
-      <c r="W41" s="10" t="s">
-        <v>28</v>
-      </c>
+      <c r="W41" s="10"/>
       <c r="X41" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y41" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z41" s="10">
-        <v>4</v>
+      <c r="Z41" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA41" s="10">
+        <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42" s="9" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>103</v>
+        <v>158</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>110</v>
+        <v>173</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="K42" s="10" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="L42" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M42" s="10">
-        <v>5530</v>
-      </c>
-      <c r="N42" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="M42" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="10">
+        <v>6189</v>
+      </c>
+      <c r="O42" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="P42" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q42" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="O42" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P42" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q42" s="1"/>
-      <c r="R42" s="10" t="s">
+      <c r="R42" s="1"/>
+      <c r="S42" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="S42" s="10" t="s">
+      <c r="T42" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T42" s="10"/>
       <c r="U42" s="10"/>
       <c r="V42" s="10"/>
-      <c r="W42" s="10" t="s">
-        <v>28</v>
-      </c>
+      <c r="W42" s="10"/>
       <c r="X42" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="Y42" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z42" s="10">
+      <c r="Z42" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA42" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43" s="9" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>165</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="K43" s="10" t="s">
-        <v>30</v>
+        <v>164</v>
       </c>
       <c r="L43" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="10">
-        <v>3329</v>
-      </c>
-      <c r="N43" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="O43" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M43" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="10">
+        <v>5246</v>
+      </c>
+      <c r="O43" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="P43" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P43" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q43" s="1"/>
-      <c r="R43" s="10" t="s">
+      <c r="Q43" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="R43" s="1"/>
+      <c r="S43" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="S43" s="10" t="s">
+      <c r="T43" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T43" s="10"/>
       <c r="U43" s="10"/>
       <c r="V43" s="10"/>
-      <c r="W43" s="10" t="s">
-        <v>28</v>
-      </c>
+      <c r="W43" s="10"/>
       <c r="X43" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y43" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z43" s="10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A44" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="F44" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="H44" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="I44" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="J44" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K44" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="L44" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M44" s="10">
-        <v>3037</v>
-      </c>
-      <c r="N44" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="O44" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P44" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q44" s="1"/>
-      <c r="R44" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="S44" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="T44" s="10"/>
-      <c r="U44" s="10"/>
-      <c r="V44" s="10"/>
-      <c r="W44" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="X44" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y44" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z44" s="10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A45" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="G45" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="I45" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="J45" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K45" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="L45" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="10">
-        <v>5685</v>
-      </c>
-      <c r="N45" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="O45" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P45" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q45" s="1"/>
-      <c r="R45" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="S45" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="T45" s="10"/>
-      <c r="U45" s="10"/>
-      <c r="V45" s="10"/>
-      <c r="W45" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="X45" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y45" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z45" s="10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A46" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="F46" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="G46" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="I46" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="J46" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K46" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="L46" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="10">
-        <v>5023</v>
-      </c>
-      <c r="N46" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="O46" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P46" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q46" s="1"/>
-      <c r="R46" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="S46" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="T46" s="10"/>
-      <c r="U46" s="10"/>
-      <c r="V46" s="10"/>
-      <c r="W46" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="X46" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y46" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z46" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A47" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="F47" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="G47" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="I47" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="J47" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K47" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="L47" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="10">
-        <v>6189</v>
-      </c>
-      <c r="N47" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="O47" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P47" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q47" s="1"/>
-      <c r="R47" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="S47" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="T47" s="10"/>
-      <c r="U47" s="10"/>
-      <c r="V47" s="10"/>
-      <c r="W47" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="X47" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y47" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z47" s="10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A48" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="F48" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="G48" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="H48" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="I48" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="J48" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="K48" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="L48" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="10">
-        <v>5246</v>
-      </c>
-      <c r="N48" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="O48" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P48" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q48" s="1"/>
-      <c r="R48" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="S48" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="T48" s="10"/>
-      <c r="U48" s="10"/>
-      <c r="V48" s="10"/>
-      <c r="W48" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="X48" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y48" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z48" s="10">
+      <c r="Z43" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA43" s="10">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z48">
-    <sortCondition ref="N2:N48"/>
-    <sortCondition ref="P2:P48"/>
-    <sortCondition ref="Q2:Q48"/>
-    <sortCondition ref="C2:C48"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA43">
+    <sortCondition ref="O2:O43"/>
+    <sortCondition ref="Q2:Q43"/>
+    <sortCondition ref="R2:R43"/>
+    <sortCondition ref="C2:C43"/>
   </sortState>
-  <conditionalFormatting sqref="Z49:Z1048576 Z1:Z8">
-    <cfRule type="colorScale" priority="36">
+  <conditionalFormatting sqref="AA44:AA1048576 AA1:AA5">
+    <cfRule type="colorScale" priority="37">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5145,7 +4926,19 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z9:Z11">
+  <conditionalFormatting sqref="AA6:AA8">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA9:AA19">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -5157,7 +4950,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z12:Z23">
+  <conditionalFormatting sqref="AA20:AA21">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -5169,7 +4962,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z24:Z25">
+  <conditionalFormatting sqref="AA24:AA25 AA22">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -5181,8 +4974,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z26:Z29">
-    <cfRule type="colorScale" priority="7">
+  <conditionalFormatting sqref="AA37:AA38">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5193,7 +4986,31 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z30:Z34">
+  <conditionalFormatting sqref="AA39">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA40">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA30:AA32 AA34:AA36 AA41">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -5205,31 +5022,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z42:Z43">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z44">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z45">
+  <conditionalFormatting sqref="AA42:AA43">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -5241,8 +5034,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z35:Z41 Z46">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="AA23">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5253,8 +5046,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z47:Z48">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="AA26:AA29 AA33">
+    <cfRule type="colorScale" priority="45">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5271,7 +5064,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E84FD6B7-DAC0-EF4A-B6E8-A6FD2C634E5A}">
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.1640625" customWidth="1"/>
@@ -5286,34 +5079,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>1</v>
@@ -5322,66 +5115,66 @@
         <v>2</v>
       </c>
       <c r="N1" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="X1" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>84</v>
-      </c>
       <c r="Z1" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
@@ -5403,7 +5196,7 @@
         <v>8</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>6</v>
@@ -5433,25 +5226,25 @@
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
@@ -5473,7 +5266,7 @@
         <v>8</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>6</v>
@@ -5503,28 +5296,28 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>201</v>
+        <v>171</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>11</v>
@@ -5533,26 +5326,26 @@
         <v>11</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>7</v>
@@ -5577,28 +5370,28 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>201</v>
+        <v>171</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>11</v>
@@ -5607,26 +5400,26 @@
         <v>11</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M5" s="2"/>
       <c r="N5" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="S5" s="2" t="s">
         <v>7</v>
@@ -5651,29 +5444,29 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>188</v>
-      </c>
       <c r="I6" s="2" t="s">
         <v>11</v>
       </c>
@@ -5681,26 +5474,26 @@
         <v>11</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="S6" s="2" t="s">
         <v>7</v>
@@ -5724,156 +5517,518 @@
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="O7" s="2" t="s">
+      <c r="A7" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="13">
+        <v>2482</v>
+      </c>
+      <c r="N7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="O7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="R7" s="2" t="s">
+      <c r="P7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
-      <c r="V7" s="2">
-        <v>26952212</v>
-      </c>
-      <c r="W7" s="2" t="s">
+      <c r="S7" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="T7" s="13"/>
+      <c r="U7" s="13"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z7" s="2">
-        <v>3</v>
+      <c r="Z7" s="13">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>150</v>
+      <c r="A8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="10">
+        <v>5667</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="O8" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="P8" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="S8" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="10"/>
+      <c r="W8" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="X8" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y8" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z8" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A9" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="10">
+        <v>7418</v>
+      </c>
+      <c r="N9" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="O9" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R9" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="S9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="13">
+        <v>2825129</v>
+      </c>
+      <c r="W9" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="X9" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y9" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z9" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="10">
+        <v>4102</v>
+      </c>
+      <c r="N10" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="O10" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="S10" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="X10" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y10" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z10" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="M11" s="10">
+        <v>9611</v>
+      </c>
+      <c r="N11" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="O11" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="P11" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="Q11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="R11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="S11" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="10"/>
+      <c r="W11" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="X11" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y11" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z11" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="10">
+        <v>7613</v>
+      </c>
+      <c r="N12" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="O12" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="P8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="R8" s="2" t="s">
+      <c r="P12" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="S12" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="10"/>
+      <c r="W12" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="X12" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y12" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z12" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A13" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="M13" s="13">
+        <v>2482</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="O13" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="P13" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="S8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2">
-        <v>26952212</v>
-      </c>
-      <c r="W8" s="2" t="s">
+      <c r="S13" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="T13" s="13"/>
+      <c r="U13" s="13"/>
+      <c r="V13" s="13"/>
+      <c r="W13" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="X13" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="X8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z8" s="2">
-        <v>3</v>
+      <c r="Z13" s="13">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="Z2">
-    <cfRule type="colorScale" priority="15">
+    <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5885,7 +6040,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="colorScale" priority="14">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5897,7 +6052,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="colorScale" priority="34">
+    <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5909,7 +6064,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z4:Z5">
-    <cfRule type="colorScale" priority="13">
+    <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5920,8 +6075,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z6:Z7">
-    <cfRule type="colorScale" priority="12">
+  <conditionalFormatting sqref="Z7">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z6">
+    <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5933,7 +6100,55 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z8">
-    <cfRule type="colorScale" priority="11">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z9">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z10">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z11:Z12">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z13">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/tabular/reference/herv_sublineage_data.xlsx
+++ b/tabular/reference/herv_sublineage_data.xlsx
@@ -8,20 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2AB2FE-734C-7841-BAD2-AA079230A84D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABDD328-B1EA-CD48-B144-ADF75E9AD73B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1580" yWindow="1260" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1680" yWindow="1120" windowWidth="27120" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sublineage" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="232">
   <si>
     <t>sequenceID</t>
   </si>
@@ -83,9 +93,6 @@
     <t>Lambdaretrovirus</t>
   </si>
   <si>
-    <t>ERV-3-16A3</t>
-  </si>
-  <si>
     <t>ERV-L</t>
   </si>
   <si>
@@ -714,6 +721,12 @@
   </si>
   <si>
     <t>entity_level</t>
+  </si>
+  <si>
+    <t>ERV3-16A3</t>
+  </si>
+  <si>
+    <t>ERV3-16A3a</t>
   </si>
 </sst>
 </file>
@@ -1250,13 +1263,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1649,7 +1661,7 @@
     <col min="10" max="10" width="14.5" customWidth="1"/>
     <col min="11" max="11" width="25" customWidth="1"/>
     <col min="12" max="12" width="19" customWidth="1"/>
-    <col min="15" max="15" width="10.83203125" style="8"/>
+    <col min="15" max="15" width="10.83203125" style="7"/>
     <col min="17" max="17" width="21" customWidth="1"/>
     <col min="20" max="20" width="16" customWidth="1"/>
   </cols>
@@ -1659,37 +1671,37 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="E1" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>161</v>
-      </c>
       <c r="J1" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="K1" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="L1" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M1" s="4" t="s">
         <v>1</v>
@@ -1697,3213 +1709,3213 @@
       <c r="N1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="Z1" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="AA1" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="10" t="s">
+      <c r="A2" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="9" t="s">
         <v>12</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N2" s="10">
+        <v>88</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" s="9">
         <v>6896</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="O2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="10" t="s">
+      <c r="Q2" s="9" t="s">
         <v>15</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="10" t="s">
+      <c r="S2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="10" t="s">
+      <c r="T2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10" t="s">
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="Y2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA2" s="10">
+      <c r="Y2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA2" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>34</v>
+      <c r="A3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="F3" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="G3" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" s="10">
+      <c r="H3" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N3" s="9">
         <v>4936</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="O3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="10" t="s">
+      <c r="P3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q3" s="10" t="s">
-        <v>215</v>
+      <c r="Q3" s="9" t="s">
+        <v>214</v>
       </c>
       <c r="R3" s="1"/>
-      <c r="S3" s="10" t="s">
+      <c r="S3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T3" s="10" t="s">
+      <c r="T3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U3" s="10"/>
-      <c r="V3" s="10"/>
-      <c r="W3" s="10"/>
-      <c r="X3" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="Y3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA3" s="10">
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="Y3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA3" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>36</v>
+      <c r="A4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="F4" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G4" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="G4" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="M4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N4" s="10">
+      <c r="H4" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N4" s="9">
         <v>9084</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P4" s="10" t="s">
+      <c r="P4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q4" s="10" t="s">
-        <v>215</v>
+      <c r="Q4" s="9" t="s">
+        <v>214</v>
       </c>
       <c r="R4" s="1"/>
-      <c r="S4" s="10" t="s">
+      <c r="S4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T4" s="10" t="s">
+      <c r="T4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="10"/>
-      <c r="V4" s="10"/>
-      <c r="W4" s="10"/>
-      <c r="X4" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="Y4" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z4" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA4" s="10">
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="Y4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA4" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A5" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>41</v>
+      <c r="A5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>40</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F5" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="G5" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="M5" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N5" s="10">
+      <c r="H5" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="9">
         <v>1786</v>
       </c>
-      <c r="O5" s="11" t="s">
+      <c r="O5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P5" s="10" t="s">
+      <c r="P5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q5" s="10" t="s">
-        <v>39</v>
+      <c r="Q5" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="R5" s="1"/>
-      <c r="S5" s="10" t="s">
+      <c r="S5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T5" s="10" t="s">
+      <c r="T5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U5" s="10"/>
-      <c r="V5" s="10"/>
-      <c r="W5" s="10"/>
-      <c r="X5" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y5" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z5" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA5" s="10">
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA5" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I6" s="10" t="s">
+      <c r="A6" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J6" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="M6" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N6" s="10">
+      <c r="G6" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N6" s="9">
         <v>8120</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="O6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P6" s="10" t="s">
+      <c r="P6" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q6" s="10" t="s">
-        <v>39</v>
+      <c r="Q6" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="R6" s="1"/>
-      <c r="S6" s="10" t="s">
+      <c r="S6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T6" s="10" t="s">
+      <c r="T6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U6" s="10"/>
-      <c r="V6" s="10"/>
-      <c r="W6" s="10"/>
-      <c r="X6" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y6" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z6" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA6" s="10">
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA6" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A7" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I7" s="10" t="s">
+      <c r="A7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J7" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M7" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="10">
+      <c r="G7" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="9">
         <v>4060</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="O7" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P7" s="10" t="s">
+      <c r="P7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q7" s="10" t="s">
-        <v>39</v>
+      <c r="Q7" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="R7" s="1"/>
-      <c r="S7" s="10" t="s">
+      <c r="S7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T7" s="10" t="s">
+      <c r="T7" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U7" s="10"/>
-      <c r="V7" s="10"/>
-      <c r="W7" s="10"/>
-      <c r="X7" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y7" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z7" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA7" s="10">
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA7" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A8" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I8" s="10" t="s">
+      <c r="A8" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J8" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L8" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="M8" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N8" s="10">
+      <c r="G8" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="9">
         <v>4798</v>
       </c>
-      <c r="O8" s="11" t="s">
+      <c r="O8" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P8" s="10" t="s">
+      <c r="P8" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q8" s="10" t="s">
-        <v>39</v>
+      <c r="Q8" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="R8" s="1"/>
-      <c r="S8" s="10" t="s">
+      <c r="S8" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T8" s="10" t="s">
+      <c r="T8" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U8" s="10"/>
-      <c r="V8" s="10"/>
-      <c r="W8" s="10"/>
-      <c r="X8" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y8" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z8" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA8" s="10">
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA8" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A9" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I9" s="10" t="s">
+      <c r="A9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J9" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L9" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M9" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N9" s="10">
+      <c r="G9" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="9">
         <v>6639</v>
       </c>
-      <c r="O9" s="11" t="s">
+      <c r="O9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P9" s="10" t="s">
+      <c r="P9" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q9" s="10" t="s">
-        <v>39</v>
+      <c r="Q9" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="R9" s="1"/>
-      <c r="S9" s="10" t="s">
+      <c r="S9" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T9" s="10" t="s">
+      <c r="T9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U9" s="10"/>
-      <c r="V9" s="10"/>
-      <c r="W9" s="10"/>
-      <c r="X9" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y9" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z9" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA9" s="10">
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA9" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A10" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I10" s="10" t="s">
+      <c r="A10" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J10" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L10" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="M10" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N10" s="10">
+      <c r="G10" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="9">
         <v>933</v>
       </c>
-      <c r="O10" s="11" t="s">
+      <c r="O10" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P10" s="10" t="s">
+      <c r="P10" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q10" s="10" t="s">
-        <v>39</v>
+      <c r="Q10" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="R10" s="1"/>
-      <c r="S10" s="10" t="s">
+      <c r="S10" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T10" s="10" t="s">
+      <c r="T10" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U10" s="10"/>
-      <c r="V10" s="10"/>
-      <c r="W10" s="10"/>
-      <c r="X10" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y10" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z10" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA10" s="10">
+      <c r="U10" s="9"/>
+      <c r="V10" s="9"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA10" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I11" s="10" t="s">
+      <c r="A11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F11" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J11" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K11" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L11" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="M11" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N11" s="10">
+      <c r="G11" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N11" s="9">
         <v>4936</v>
       </c>
-      <c r="O11" s="11" t="s">
+      <c r="O11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P11" s="10" t="s">
+      <c r="P11" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q11" s="10" t="s">
-        <v>39</v>
+      <c r="Q11" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="R11" s="1"/>
-      <c r="S11" s="10" t="s">
+      <c r="S11" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T11" s="10" t="s">
+      <c r="T11" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U11" s="10"/>
-      <c r="V11" s="10"/>
-      <c r="W11" s="10"/>
-      <c r="X11" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y11" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z11" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA11" s="10">
+      <c r="U11" s="9"/>
+      <c r="V11" s="9"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y11" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z11" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA11" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A12" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I12" s="10" t="s">
+      <c r="A12" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J12" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="M12" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N12" s="10">
+      <c r="G12" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="9">
         <v>5356</v>
       </c>
-      <c r="O12" s="11" t="s">
+      <c r="O12" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P12" s="10" t="s">
+      <c r="P12" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q12" s="10" t="s">
-        <v>39</v>
+      <c r="Q12" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="R12" s="1"/>
-      <c r="S12" s="10" t="s">
+      <c r="S12" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T12" s="10" t="s">
+      <c r="T12" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U12" s="10"/>
-      <c r="V12" s="10"/>
-      <c r="W12" s="10"/>
-      <c r="X12" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y12" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z12" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA12" s="10">
+      <c r="U12" s="9"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA12" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A13" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I13" s="10" t="s">
+      <c r="A13" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J13" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L13" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="M13" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N13" s="10">
+      <c r="G13" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N13" s="9">
         <v>5217</v>
       </c>
-      <c r="O13" s="11" t="s">
+      <c r="O13" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P13" s="10" t="s">
+      <c r="P13" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q13" s="10" t="s">
-        <v>39</v>
+      <c r="Q13" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="R13" s="1"/>
-      <c r="S13" s="10" t="s">
+      <c r="S13" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T13" s="10" t="s">
+      <c r="T13" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U13" s="10"/>
-      <c r="V13" s="10"/>
-      <c r="W13" s="10"/>
-      <c r="X13" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y13" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z13" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA13" s="10">
+      <c r="U13" s="9"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA13" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A14" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I14" s="10" t="s">
+      <c r="A14" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J14" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L14" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="M14" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="10">
+      <c r="G14" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="9">
         <v>7048</v>
       </c>
-      <c r="O14" s="11" t="s">
+      <c r="O14" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P14" s="10" t="s">
+      <c r="P14" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="10" t="s">
-        <v>39</v>
+      <c r="Q14" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="R14" s="1"/>
-      <c r="S14" s="10" t="s">
+      <c r="S14" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T14" s="10" t="s">
+      <c r="T14" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U14" s="10"/>
-      <c r="V14" s="10"/>
-      <c r="W14" s="10"/>
-      <c r="X14" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y14" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z14" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA14" s="10">
+      <c r="U14" s="9"/>
+      <c r="V14" s="9"/>
+      <c r="W14" s="9"/>
+      <c r="X14" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y14" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z14" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA14" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A15" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="B15" s="12" t="s">
+      <c r="A15" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="12"/>
+      <c r="O15" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P15" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K15" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="L15" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N15" s="13"/>
-      <c r="O15" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="P15" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q15" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10" t="s">
+      <c r="R15" s="9"/>
+      <c r="S15" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="T15" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="U15" s="13"/>
-      <c r="V15" s="13"/>
-      <c r="W15" s="13"/>
-      <c r="X15" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y15" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z15" s="10" t="s">
+      <c r="T15" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="U15" s="12"/>
+      <c r="V15" s="12"/>
+      <c r="W15" s="12"/>
+      <c r="X15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y15" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z15" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="AA15" s="13">
+      <c r="AA15" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A16" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I16" s="10" t="s">
+      <c r="A16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F16" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J16" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K16" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L16" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="M16" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N16" s="10">
+      <c r="G16" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N16" s="9">
         <v>6387</v>
       </c>
-      <c r="O16" s="11" t="s">
+      <c r="O16" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P16" s="10" t="s">
+      <c r="P16" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q16" s="10" t="s">
-        <v>195</v>
+      <c r="Q16" s="9" t="s">
+        <v>194</v>
       </c>
       <c r="R16" s="1"/>
-      <c r="S16" s="10" t="s">
+      <c r="S16" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T16" s="10" t="s">
+      <c r="T16" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U16" s="10"/>
-      <c r="V16" s="10"/>
-      <c r="W16" s="10"/>
-      <c r="X16" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y16" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z16" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA16" s="10">
+      <c r="U16" s="9"/>
+      <c r="V16" s="9"/>
+      <c r="W16" s="9"/>
+      <c r="X16" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y16" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z16" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA16" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A17" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I17" s="10" t="s">
+      <c r="A17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F17" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J17" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K17" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L17" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="M17" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N17" s="10">
+      <c r="G17" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="9">
         <v>6758</v>
       </c>
-      <c r="O17" s="11" t="s">
+      <c r="O17" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P17" s="10" t="s">
+      <c r="P17" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q17" s="10" t="s">
-        <v>195</v>
+      <c r="Q17" s="9" t="s">
+        <v>194</v>
       </c>
       <c r="R17" s="1"/>
-      <c r="S17" s="10" t="s">
+      <c r="S17" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T17" s="10" t="s">
+      <c r="T17" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U17" s="10"/>
-      <c r="V17" s="10"/>
-      <c r="W17" s="10"/>
-      <c r="X17" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y17" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z17" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA17" s="10">
+      <c r="U17" s="9"/>
+      <c r="V17" s="9"/>
+      <c r="W17" s="9"/>
+      <c r="X17" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y17" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z17" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA17" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A18" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I18" s="10" t="s">
+      <c r="A18" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F18" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J18" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K18" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L18" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M18" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="10">
+      <c r="G18" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="9">
         <v>4871</v>
       </c>
-      <c r="O18" s="11" t="s">
+      <c r="O18" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P18" s="10" t="s">
+      <c r="P18" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q18" s="10" t="s">
-        <v>195</v>
+      <c r="Q18" s="9" t="s">
+        <v>194</v>
       </c>
       <c r="R18" s="1"/>
-      <c r="S18" s="10" t="s">
+      <c r="S18" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T18" s="10" t="s">
+      <c r="T18" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U18" s="10"/>
-      <c r="V18" s="10"/>
-      <c r="W18" s="10"/>
-      <c r="X18" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y18" s="10" t="s">
+      <c r="U18" s="9"/>
+      <c r="V18" s="9"/>
+      <c r="W18" s="9"/>
+      <c r="X18" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y18" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="Z18" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA18" s="10">
+      <c r="Z18" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA18" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="F19" s="10" t="s">
+      <c r="A19" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G19" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="G19" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="K19" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L19" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="M19" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N19" s="10">
+      <c r="H19" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N19" s="9">
         <v>4981</v>
       </c>
-      <c r="O19" s="11" t="s">
+      <c r="O19" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P19" s="10" t="s">
+      <c r="P19" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q19" s="10" t="s">
-        <v>55</v>
+      <c r="Q19" s="9" t="s">
+        <v>54</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="S19" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="S19" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T19" s="10" t="s">
+      <c r="T19" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U19" s="10"/>
-      <c r="V19" s="10"/>
-      <c r="W19" s="10"/>
-      <c r="X19" s="10" t="s">
+      <c r="U19" s="9"/>
+      <c r="V19" s="9"/>
+      <c r="W19" s="9"/>
+      <c r="X19" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="Y19" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z19" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA19" s="10">
+      <c r="Y19" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z19" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA19" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A20" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>59</v>
+      <c r="A20" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>58</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="F20" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G20" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="G20" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I20" s="10" t="s">
+      <c r="H20" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J20" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J20" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="K20" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L20" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="M20" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="10">
+      <c r="K20" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="9">
         <v>6996</v>
       </c>
-      <c r="O20" s="11" t="s">
+      <c r="O20" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P20" s="10" t="s">
+      <c r="P20" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="10" t="s">
-        <v>55</v>
+      <c r="Q20" s="9" t="s">
+        <v>54</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="S20" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="S20" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T20" s="10" t="s">
+      <c r="T20" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U20" s="10"/>
-      <c r="V20" s="10"/>
-      <c r="W20" s="10"/>
-      <c r="X20" s="10" t="s">
+      <c r="U20" s="9"/>
+      <c r="V20" s="9"/>
+      <c r="W20" s="9"/>
+      <c r="X20" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="Y20" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z20" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA20" s="10">
+      <c r="Y20" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z20" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA20" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A21" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="G21" s="10" t="s">
+      <c r="A21" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="9">
+        <v>11027</v>
+      </c>
+      <c r="O21" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P21" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="R21" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="H21" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="K21" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="L21" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="M21" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="10">
-        <v>11027</v>
-      </c>
-      <c r="O21" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="P21" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q21" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="S21" s="10" t="s">
+      <c r="S21" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T21" s="10" t="s">
+      <c r="T21" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U21" s="10"/>
-      <c r="V21" s="10"/>
-      <c r="W21" s="10">
+      <c r="U21" s="9"/>
+      <c r="V21" s="9"/>
+      <c r="W21" s="9">
         <v>2825129</v>
       </c>
-      <c r="X21" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y21" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z21" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA21" s="10">
+      <c r="X21" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y21" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z21" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA21" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A22" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G22" s="10" t="s">
+      <c r="A22" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="9">
+        <v>8987</v>
+      </c>
+      <c r="O22" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P22" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="R22" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="H22" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="K22" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="L22" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="M22" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="10">
-        <v>8987</v>
-      </c>
-      <c r="O22" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="P22" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q22" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="S22" s="10" t="s">
+      <c r="S22" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T22" s="10" t="s">
+      <c r="T22" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U22" s="10"/>
-      <c r="V22" s="10"/>
-      <c r="W22" s="13">
+      <c r="U22" s="9"/>
+      <c r="V22" s="9"/>
+      <c r="W22" s="12">
         <v>2825129</v>
       </c>
-      <c r="X22" s="10" t="s">
+      <c r="X22" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="Y22" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z22" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA22" s="10">
+      <c r="Y22" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z22" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA22" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A23" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="B23" s="12" t="s">
+      <c r="A23" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="E23" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="G23" s="10" t="s">
+      <c r="F23" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="M23" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="9"/>
+      <c r="O23" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P23" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="R23" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="H23" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="J23" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="K23" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="L23" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="M23" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N23" s="10"/>
-      <c r="O23" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="P23" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q23" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="S23" s="10" t="s">
+      <c r="S23" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="T23" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="U23" s="10"/>
-      <c r="V23" s="10"/>
-      <c r="W23" s="13"/>
-      <c r="X23" s="10" t="s">
+      <c r="T23" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="U23" s="9"/>
+      <c r="V23" s="9"/>
+      <c r="W23" s="12"/>
+      <c r="X23" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="Y23" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z23" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA23" s="13">
+      <c r="Y23" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z23" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA23" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A24" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="F24" s="10" t="s">
+      <c r="A24" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G24" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="G24" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="H24" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K24" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L24" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="M24" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N24" s="10">
+      <c r="H24" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K24" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="M24" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="9">
         <v>5586</v>
       </c>
-      <c r="O24" s="11" t="s">
+      <c r="O24" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P24" s="10" t="s">
+      <c r="P24" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q24" s="10" t="s">
-        <v>55</v>
+      <c r="Q24" s="9" t="s">
+        <v>54</v>
       </c>
       <c r="R24" s="1"/>
-      <c r="S24" s="10" t="s">
+      <c r="S24" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T24" s="10" t="s">
+      <c r="T24" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U24" s="10"/>
-      <c r="V24" s="10"/>
-      <c r="W24" s="10"/>
-      <c r="X24" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y24" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z24" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA24" s="10">
+      <c r="U24" s="9"/>
+      <c r="V24" s="9"/>
+      <c r="W24" s="9"/>
+      <c r="X24" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y24" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z24" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA24" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A25" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="F25" s="10" t="s">
+      <c r="A25" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G25" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="G25" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="J25" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K25" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L25" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="M25" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N25" s="10">
+      <c r="H25" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N25" s="9">
         <v>6918</v>
       </c>
-      <c r="O25" s="11" t="s">
+      <c r="O25" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P25" s="10" t="s">
+      <c r="P25" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q25" s="10" t="s">
-        <v>55</v>
+      <c r="Q25" s="9" t="s">
+        <v>54</v>
       </c>
       <c r="R25" s="1"/>
-      <c r="S25" s="10" t="s">
+      <c r="S25" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T25" s="10" t="s">
+      <c r="T25" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U25" s="10"/>
-      <c r="V25" s="10"/>
-      <c r="W25" s="10"/>
-      <c r="X25" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y25" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z25" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA25" s="10">
+      <c r="U25" s="9"/>
+      <c r="V25" s="9"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y25" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z25" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA25" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A26" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H26" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I26" s="10" t="s">
+      <c r="A26" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F26" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J26" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K26" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L26" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="M26" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N26" s="10">
+      <c r="G26" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="9">
         <v>3944</v>
       </c>
-      <c r="O26" s="11" t="s">
+      <c r="O26" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P26" s="10" t="s">
+      <c r="P26" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q26" s="10" t="s">
-        <v>55</v>
+      <c r="Q26" s="9" t="s">
+        <v>54</v>
       </c>
       <c r="R26" s="1"/>
-      <c r="S26" s="10" t="s">
+      <c r="S26" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T26" s="10" t="s">
+      <c r="T26" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U26" s="10"/>
-      <c r="V26" s="10"/>
-      <c r="W26" s="10"/>
-      <c r="X26" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y26" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z26" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA26" s="10">
+      <c r="U26" s="9"/>
+      <c r="V26" s="9"/>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y26" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z26" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA26" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A27" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I27" s="10" t="s">
+      <c r="A27" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F27" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J27" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L27" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="M27" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N27" s="10">
+      <c r="G27" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="9">
         <v>7133</v>
       </c>
-      <c r="O27" s="11" t="s">
+      <c r="O27" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P27" s="10" t="s">
+      <c r="P27" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q27" s="10" t="s">
-        <v>55</v>
+      <c r="Q27" s="9" t="s">
+        <v>54</v>
       </c>
       <c r="R27" s="1"/>
-      <c r="S27" s="10" t="s">
+      <c r="S27" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T27" s="10" t="s">
+      <c r="T27" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U27" s="10"/>
-      <c r="V27" s="10"/>
-      <c r="W27" s="10"/>
-      <c r="X27" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y27" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z27" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA27" s="10">
+      <c r="U27" s="9"/>
+      <c r="V27" s="9"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y27" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z27" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA27" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A28" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I28" s="10" t="s">
+      <c r="A28" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F28" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J28" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K28" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L28" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="M28" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N28" s="10">
+      <c r="G28" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="M28" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N28" s="9">
         <v>4285</v>
       </c>
-      <c r="O28" s="11" t="s">
+      <c r="O28" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P28" s="10" t="s">
+      <c r="P28" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q28" s="10" t="s">
-        <v>55</v>
+      <c r="Q28" s="9" t="s">
+        <v>54</v>
       </c>
       <c r="R28" s="1"/>
-      <c r="S28" s="10" t="s">
+      <c r="S28" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T28" s="10" t="s">
+      <c r="T28" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U28" s="10"/>
-      <c r="V28" s="10"/>
-      <c r="W28" s="10"/>
-      <c r="X28" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y28" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z28" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA28" s="10">
+      <c r="U28" s="9"/>
+      <c r="V28" s="9"/>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y28" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z28" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA28" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A29" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I29" s="10" t="s">
+      <c r="A29" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F29" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J29" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K29" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L29" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="M29" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N29" s="10">
+      <c r="G29" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N29" s="9">
         <v>4880</v>
       </c>
-      <c r="O29" s="11" t="s">
+      <c r="O29" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P29" s="10" t="s">
+      <c r="P29" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q29" s="10" t="s">
-        <v>55</v>
+      <c r="Q29" s="9" t="s">
+        <v>54</v>
       </c>
       <c r="R29" s="1"/>
-      <c r="S29" s="10" t="s">
+      <c r="S29" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T29" s="10" t="s">
+      <c r="T29" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U29" s="10"/>
-      <c r="V29" s="10"/>
-      <c r="W29" s="10"/>
-      <c r="X29" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y29" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z29" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA29" s="10">
+      <c r="U29" s="9"/>
+      <c r="V29" s="9"/>
+      <c r="W29" s="9"/>
+      <c r="X29" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y29" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z29" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA29" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A30" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H30" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I30" s="10" t="s">
+      <c r="A30" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F30" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J30" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K30" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L30" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="M30" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N30" s="10">
+      <c r="G30" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M30" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N30" s="9">
         <v>2880</v>
       </c>
-      <c r="O30" s="11" t="s">
+      <c r="O30" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P30" s="10" t="s">
+      <c r="P30" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q30" s="10" t="s">
-        <v>55</v>
+      <c r="Q30" s="9" t="s">
+        <v>54</v>
       </c>
       <c r="R30" s="1"/>
-      <c r="S30" s="10" t="s">
+      <c r="S30" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T30" s="10" t="s">
+      <c r="T30" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U30" s="10"/>
-      <c r="V30" s="10"/>
-      <c r="W30" s="10"/>
-      <c r="X30" s="10" t="s">
+      <c r="U30" s="9"/>
+      <c r="V30" s="9"/>
+      <c r="W30" s="9"/>
+      <c r="X30" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="Y30" s="10" t="s">
+      <c r="Y30" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="Z30" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA30" s="10">
+      <c r="Z30" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA30" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A31" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="F31" s="10" t="s">
+      <c r="A31" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G31" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="G31" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I31" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="J31" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K31" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L31" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="M31" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N31" s="10">
+      <c r="H31" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N31" s="9">
         <v>6070</v>
       </c>
-      <c r="O31" s="11" t="s">
+      <c r="O31" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P31" s="10" t="s">
+      <c r="P31" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q31" s="10" t="s">
+      <c r="Q31" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="R31" s="15">
+      <c r="R31" s="14">
         <v>16</v>
       </c>
-      <c r="S31" s="10" t="s">
+      <c r="S31" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="T31" s="10" t="s">
+      <c r="T31" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U31" s="10"/>
-      <c r="V31" s="10"/>
-      <c r="W31" s="10"/>
-      <c r="X31" s="10" t="s">
+      <c r="U31" s="9"/>
+      <c r="V31" s="9"/>
+      <c r="W31" s="9"/>
+      <c r="X31" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="Y31" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z31" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA31" s="10">
+      <c r="Y31" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z31" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA31" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A32" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="H32" s="10" t="s">
+      <c r="A32" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="I32" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="K32" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="L32" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M32" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="10">
+      <c r="C32" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="M32" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="9">
         <v>5667</v>
       </c>
-      <c r="O32" s="11" t="s">
+      <c r="O32" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P32" s="10" t="s">
+      <c r="P32" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="10" t="s">
+      <c r="Q32" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="R32" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="S32" s="10" t="s">
+      <c r="R32" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="S32" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="T32" s="10" t="s">
+      <c r="T32" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U32" s="10"/>
-      <c r="V32" s="10"/>
-      <c r="W32" s="10"/>
-      <c r="X32" s="10" t="s">
+      <c r="U32" s="9"/>
+      <c r="V32" s="9"/>
+      <c r="W32" s="9"/>
+      <c r="X32" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="Y32" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z32" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA32" s="10">
+      <c r="Y32" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z32" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA32" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A33" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>22</v>
+      <c r="A33" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>21</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="H33" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="I33" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="K33" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L33" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="M33" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N33" s="10">
+      <c r="F33" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M33" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="9">
         <v>5714</v>
       </c>
-      <c r="O33" s="11" t="s">
+      <c r="O33" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P33" s="10" t="s">
+      <c r="P33" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q33" s="10" t="s">
+      <c r="Q33" s="9" t="s">
         <v>19</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="S33" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="S33" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="T33" s="10" t="s">
+      <c r="T33" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U33" s="10"/>
-      <c r="V33" s="10"/>
-      <c r="W33" s="10"/>
-      <c r="X33" s="10" t="s">
+      <c r="U33" s="9"/>
+      <c r="V33" s="9"/>
+      <c r="W33" s="9"/>
+      <c r="X33" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="Y33" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z33" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA33" s="10">
+      <c r="Y33" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z33" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA33" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A34" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="F34" s="10" t="s">
+      <c r="A34" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="J34" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K34" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L34" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="M34" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N34" s="10">
+      <c r="H34" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M34" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N34" s="9">
         <v>4996</v>
       </c>
-      <c r="O34" s="11" t="s">
+      <c r="O34" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P34" s="10" t="s">
+      <c r="P34" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q34" s="10" t="s">
+      <c r="Q34" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="R34" s="16">
+      <c r="R34" s="15">
         <v>16</v>
       </c>
-      <c r="S34" s="10" t="s">
+      <c r="S34" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="T34" s="10" t="s">
+      <c r="T34" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U34" s="10"/>
-      <c r="V34" s="10"/>
-      <c r="W34" s="10"/>
-      <c r="X34" s="10" t="s">
+      <c r="U34" s="9"/>
+      <c r="V34" s="9"/>
+      <c r="W34" s="9"/>
+      <c r="X34" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="Y34" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z34" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA34" s="10">
+      <c r="Y34" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z34" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA34" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A35" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="F35" s="10" t="s">
+      <c r="A35" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G35" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I35" s="10" t="s">
+      <c r="H35" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J35" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J35" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="K35" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L35" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="M35" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N35" s="10">
+      <c r="K35" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L35" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M35" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="9">
         <v>3556</v>
       </c>
-      <c r="O35" s="11" t="s">
+      <c r="O35" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P35" s="10" t="s">
+      <c r="P35" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q35" s="10" t="s">
+      <c r="Q35" s="9" t="s">
         <v>19</v>
       </c>
       <c r="R35" s="1"/>
-      <c r="S35" s="10" t="s">
+      <c r="S35" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="T35" s="10" t="s">
+      <c r="T35" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U35" s="10"/>
-      <c r="V35" s="10"/>
-      <c r="W35" s="10"/>
-      <c r="X35" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y35" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z35" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA35" s="10">
+      <c r="U35" s="9"/>
+      <c r="V35" s="9"/>
+      <c r="W35" s="9"/>
+      <c r="X35" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y35" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z35" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA35" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A36" s="9" t="s">
+      <c r="A36" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L36" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="M36" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N36" s="9">
+        <v>5343</v>
+      </c>
+      <c r="O36" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="P36" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q36" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="R36" s="1"/>
+      <c r="S36" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="T36" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U36" s="9"/>
+      <c r="V36" s="9"/>
+      <c r="W36" s="9"/>
+      <c r="X36" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="J36" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="K36" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L36" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M36" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N36" s="10">
-        <v>5343</v>
-      </c>
-      <c r="O36" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="P36" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q36" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="R36" s="1"/>
-      <c r="S36" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="T36" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="U36" s="10"/>
-      <c r="V36" s="10"/>
-      <c r="W36" s="10"/>
-      <c r="X36" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y36" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z36" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA36" s="10">
+      <c r="Y36" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z36" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA36" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A37" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="F37" s="10" t="s">
+      <c r="A37" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G37" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="G37" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="J37" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="K37" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L37" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="M37" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N37" s="10">
+      <c r="H37" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L37" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="M37" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N37" s="9">
         <v>5530</v>
       </c>
-      <c r="O37" s="11" t="s">
+      <c r="O37" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P37" s="10" t="s">
+      <c r="P37" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q37" s="10" t="s">
+      <c r="Q37" s="9" t="s">
         <v>19</v>
       </c>
       <c r="R37" s="1"/>
-      <c r="S37" s="10" t="s">
+      <c r="S37" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="T37" s="10" t="s">
+      <c r="T37" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U37" s="10"/>
-      <c r="V37" s="10"/>
-      <c r="W37" s="10"/>
-      <c r="X37" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y37" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z37" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA37" s="10">
+      <c r="U37" s="9"/>
+      <c r="V37" s="9"/>
+      <c r="W37" s="9"/>
+      <c r="X37" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y37" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z37" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA37" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A38" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="F38" s="10" t="s">
+      <c r="A38" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G38" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H38" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="J38" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="K38" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L38" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="M38" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N38" s="10">
+      <c r="H38" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="K38" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L38" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M38" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="9">
         <v>3329</v>
       </c>
-      <c r="O38" s="11" t="s">
+      <c r="O38" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P38" s="10" t="s">
+      <c r="P38" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q38" s="10" t="s">
+      <c r="Q38" s="9" t="s">
         <v>19</v>
       </c>
       <c r="R38" s="1"/>
-      <c r="S38" s="10" t="s">
+      <c r="S38" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="T38" s="10" t="s">
+      <c r="T38" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U38" s="10"/>
-      <c r="V38" s="10"/>
-      <c r="W38" s="10"/>
-      <c r="X38" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y38" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z38" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA38" s="10">
+      <c r="U38" s="9"/>
+      <c r="V38" s="9"/>
+      <c r="W38" s="9"/>
+      <c r="X38" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y38" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z38" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA38" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A39" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="F39" s="10" t="s">
+      <c r="A39" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G39" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="J39" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="K39" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L39" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M39" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N39" s="10">
+      <c r="H39" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J39" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="K39" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L39" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M39" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N39" s="9">
         <v>3037</v>
       </c>
-      <c r="O39" s="11" t="s">
+      <c r="O39" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P39" s="10" t="s">
+      <c r="P39" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q39" s="10" t="s">
+      <c r="Q39" s="9" t="s">
         <v>19</v>
       </c>
       <c r="R39" s="1"/>
-      <c r="S39" s="10" t="s">
+      <c r="S39" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="T39" s="10" t="s">
+      <c r="T39" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U39" s="10"/>
-      <c r="V39" s="10"/>
-      <c r="W39" s="10"/>
-      <c r="X39" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y39" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z39" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA39" s="10">
+      <c r="U39" s="9"/>
+      <c r="V39" s="9"/>
+      <c r="W39" s="9"/>
+      <c r="X39" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y39" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z39" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA39" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A40" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="F40" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="H40" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I40" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="J40" s="10" t="s">
+      <c r="A40" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G40" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="K40" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L40" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="M40" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N40" s="10">
+      <c r="H40" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="K40" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L40" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M40" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N40" s="9">
         <v>5685</v>
       </c>
-      <c r="O40" s="11" t="s">
+      <c r="O40" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P40" s="10" t="s">
+      <c r="P40" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q40" s="10" t="s">
+      <c r="Q40" s="9" t="s">
         <v>19</v>
       </c>
       <c r="R40" s="1"/>
-      <c r="S40" s="10" t="s">
+      <c r="S40" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="T40" s="10" t="s">
+      <c r="T40" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U40" s="10"/>
-      <c r="V40" s="10"/>
-      <c r="W40" s="10"/>
-      <c r="X40" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y40" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z40" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA40" s="10">
+      <c r="U40" s="9"/>
+      <c r="V40" s="9"/>
+      <c r="W40" s="9"/>
+      <c r="X40" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y40" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z40" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA40" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A41" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="F41" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I41" s="10" t="s">
+      <c r="A41" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F41" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J41" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="K41" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L41" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M41" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N41" s="10">
+      <c r="G41" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J41" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="K41" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L41" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M41" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="9">
         <v>5023</v>
       </c>
-      <c r="O41" s="11" t="s">
+      <c r="O41" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P41" s="10" t="s">
+      <c r="P41" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q41" s="10" t="s">
+      <c r="Q41" s="9" t="s">
         <v>19</v>
       </c>
       <c r="R41" s="1"/>
-      <c r="S41" s="10" t="s">
+      <c r="S41" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="T41" s="10" t="s">
+      <c r="T41" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U41" s="10"/>
-      <c r="V41" s="10"/>
-      <c r="W41" s="10"/>
-      <c r="X41" s="10" t="s">
+      <c r="U41" s="9"/>
+      <c r="V41" s="9"/>
+      <c r="W41" s="9"/>
+      <c r="X41" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="Y41" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z41" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA41" s="10">
+      <c r="Y41" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z41" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA41" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A42" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="F42" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G42" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I42" s="10" t="s">
+      <c r="A42" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F42" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="J42" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="K42" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L42" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="M42" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N42" s="10">
+      <c r="G42" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J42" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="K42" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L42" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="M42" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="9">
         <v>6189</v>
       </c>
-      <c r="O42" s="11" t="s">
+      <c r="O42" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P42" s="10" t="s">
+      <c r="P42" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q42" s="10" t="s">
+      <c r="Q42" s="9" t="s">
         <v>19</v>
       </c>
       <c r="R42" s="1"/>
-      <c r="S42" s="10" t="s">
+      <c r="S42" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="T42" s="10" t="s">
+      <c r="T42" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U42" s="10"/>
-      <c r="V42" s="10"/>
-      <c r="W42" s="10"/>
-      <c r="X42" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y42" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z42" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA42" s="10">
+      <c r="U42" s="9"/>
+      <c r="V42" s="9"/>
+      <c r="W42" s="9"/>
+      <c r="X42" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y42" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z42" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA42" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A43" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="F43" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="H43" s="10" t="s">
+      <c r="A43" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E43" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="I43" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="J43" s="10" t="s">
+      <c r="F43" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G43" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="K43" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="L43" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M43" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="10">
+      <c r="H43" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="K43" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="L43" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M43" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="9">
         <v>5246</v>
       </c>
-      <c r="O43" s="11" t="s">
+      <c r="O43" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P43" s="10" t="s">
+      <c r="P43" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="Q43" s="10" t="s">
-        <v>37</v>
+      <c r="Q43" s="9" t="s">
+        <v>36</v>
       </c>
       <c r="R43" s="1"/>
-      <c r="S43" s="10" t="s">
+      <c r="S43" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="T43" s="10" t="s">
+      <c r="T43" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U43" s="10"/>
-      <c r="V43" s="10"/>
-      <c r="W43" s="10"/>
-      <c r="X43" s="10" t="s">
+      <c r="U43" s="9"/>
+      <c r="V43" s="9"/>
+      <c r="W43" s="9"/>
+      <c r="X43" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="Y43" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z43" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA43" s="10">
+      <c r="Y43" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z43" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA43" s="9">
         <v>3</v>
       </c>
     </row>
@@ -5079,34 +5091,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="E1" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>161</v>
-      </c>
       <c r="I1" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="K1" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>1</v>
@@ -5114,67 +5126,67 @@
       <c r="M1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="Y1" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="Z1" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>182</v>
+      <c r="A2" s="8" t="s">
+        <v>181</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>186</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
@@ -5186,7 +5198,7 @@
       <c r="M2" s="2">
         <v>8214</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="O2" s="2" t="s">
@@ -5196,7 +5208,7 @@
         <v>8</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>6</v>
@@ -5225,26 +5237,26 @@
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
@@ -5256,7 +5268,7 @@
       <c r="M3" s="2">
         <v>8214</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="6" t="s">
         <v>4</v>
       </c>
       <c r="O3" s="2" t="s">
@@ -5266,7 +5278,7 @@
         <v>8</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>6</v>
@@ -5295,29 +5307,29 @@
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>11</v>
@@ -5326,13 +5338,13 @@
         <v>11</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M4" s="2"/>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="6" t="s">
         <v>14</v>
       </c>
       <c r="O4" s="2" t="s">
@@ -5342,10 +5354,10 @@
         <v>15</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>7</v>
@@ -5369,29 +5381,29 @@
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>11</v>
@@ -5400,13 +5412,13 @@
         <v>11</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M5" s="2"/>
-      <c r="N5" s="7" t="s">
+      <c r="N5" s="6" t="s">
         <v>14</v>
       </c>
       <c r="O5" s="2" t="s">
@@ -5416,10 +5428,10 @@
         <v>15</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="S5" s="2" t="s">
         <v>7</v>
@@ -5443,29 +5455,29 @@
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>11</v>
@@ -5474,13 +5486,13 @@
         <v>11</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M6" s="2"/>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="6" t="s">
         <v>14</v>
       </c>
       <c r="O6" s="2" t="s">
@@ -5490,10 +5502,10 @@
         <v>15</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="S6" s="2" t="s">
         <v>7</v>
@@ -5517,512 +5529,512 @@
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A7" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="13">
+      <c r="A7" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="12">
         <v>2482</v>
       </c>
-      <c r="N7" s="11" t="s">
+      <c r="N7" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="O7" s="10" t="s">
+      <c r="O7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="P7" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10" t="s">
+      <c r="P7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="S7" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="T7" s="13"/>
-      <c r="U7" s="13"/>
-      <c r="V7" s="13"/>
-      <c r="W7" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="X7" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y7" s="10" t="s">
+      <c r="S7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="T7" s="12"/>
+      <c r="U7" s="12"/>
+      <c r="V7" s="12"/>
+      <c r="W7" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="X7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y7" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="Z7" s="13">
+      <c r="Z7" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A8" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>23</v>
+      <c r="A8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>22</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>181</v>
+        <v>86</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>180</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="L8" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="10">
+        <v>164</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="9">
         <v>5667</v>
       </c>
-      <c r="N8" s="11" t="s">
+      <c r="N8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="O8" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="P8" s="10" t="s">
+      <c r="P8" s="9" t="s">
         <v>19</v>
       </c>
       <c r="Q8" s="1"/>
-      <c r="R8" s="10" t="s">
+      <c r="R8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="S8" s="10" t="s">
+      <c r="S8" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="T8" s="10"/>
-      <c r="U8" s="10"/>
-      <c r="V8" s="10"/>
-      <c r="W8" s="10" t="s">
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="X8" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y8" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z8" s="10">
+      <c r="X8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z8" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A9" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F9" s="10" t="s">
+      <c r="A9" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="G9" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="L9" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="10">
+      <c r="H9" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="9">
         <v>7418</v>
       </c>
-      <c r="N9" s="11" t="s">
+      <c r="N9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="10" t="s">
+      <c r="O9" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="10" t="s">
-        <v>55</v>
+      <c r="P9" s="9" t="s">
+        <v>54</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="R9" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="R9" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="S9" s="10" t="s">
+      <c r="S9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="T9" s="10"/>
-      <c r="U9" s="10"/>
-      <c r="V9" s="13">
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="12">
         <v>2825129</v>
       </c>
-      <c r="W9" s="10" t="s">
+      <c r="W9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="X9" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y9" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z9" s="10">
+      <c r="X9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z9" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A10" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F10" s="10" t="s">
+      <c r="A10" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G10" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="G10" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="L10" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="10">
+      <c r="H10" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="9">
         <v>4102</v>
       </c>
-      <c r="N10" s="11" t="s">
+      <c r="N10" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="O10" s="10" t="s">
+      <c r="O10" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="10" t="s">
-        <v>39</v>
+      <c r="P10" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="Q10" s="1"/>
-      <c r="R10" s="10" t="s">
+      <c r="R10" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="S10" s="10" t="s">
+      <c r="S10" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="T10" s="10"/>
-      <c r="U10" s="10"/>
-      <c r="V10" s="10"/>
-      <c r="W10" s="10" t="s">
+      <c r="T10" s="9"/>
+      <c r="U10" s="9"/>
+      <c r="V10" s="9"/>
+      <c r="W10" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="X10" s="10" t="s">
+      <c r="X10" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="Y10" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z10" s="10">
+      <c r="Y10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z10" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="C11" s="10" t="s">
+      <c r="B11" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="J11" s="10" t="s">
+      <c r="D11" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="J11" s="9" t="s">
         <v>12</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="L11" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M11" s="10">
+        <v>88</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="M11" s="9">
         <v>9611</v>
       </c>
-      <c r="N11" s="11" t="s">
+      <c r="N11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="O11" s="10" t="s">
+      <c r="O11" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="P11" s="10" t="s">
+      <c r="P11" s="9" t="s">
         <v>15</v>
       </c>
       <c r="Q11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R11" s="10" t="s">
+      <c r="R11" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="S11" s="10" t="s">
+      <c r="S11" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="T11" s="10"/>
-      <c r="U11" s="10"/>
-      <c r="V11" s="10"/>
-      <c r="W11" s="10" t="s">
+      <c r="T11" s="9"/>
+      <c r="U11" s="9"/>
+      <c r="V11" s="9"/>
+      <c r="W11" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="X11" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y11" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z11" s="10">
+      <c r="X11" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y11" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z11" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>40</v>
+      <c r="A12" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F12" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G12" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="G12" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M12" s="10">
+      <c r="H12" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="9">
         <v>7613</v>
       </c>
-      <c r="N12" s="11" t="s">
+      <c r="N12" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="O12" s="10" t="s">
+      <c r="O12" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="P12" s="10" t="s">
-        <v>39</v>
+      <c r="P12" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="Q12" s="1"/>
-      <c r="R12" s="10" t="s">
+      <c r="R12" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="S12" s="10" t="s">
+      <c r="S12" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="T12" s="10"/>
-      <c r="U12" s="10"/>
-      <c r="V12" s="10"/>
-      <c r="W12" s="10" t="s">
+      <c r="T12" s="9"/>
+      <c r="U12" s="9"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="X12" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y12" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z12" s="10">
+      <c r="X12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z12" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A13" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="L13" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M13" s="13">
+      <c r="A13" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="M13" s="12">
         <v>2482</v>
       </c>
-      <c r="N13" s="11" t="s">
+      <c r="N13" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="O13" s="10" t="s">
+      <c r="O13" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="P13" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10" t="s">
+      <c r="P13" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="S13" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="T13" s="13"/>
-      <c r="U13" s="13"/>
-      <c r="V13" s="13"/>
-      <c r="W13" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="X13" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y13" s="10" t="s">
+      <c r="S13" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="T13" s="12"/>
+      <c r="U13" s="12"/>
+      <c r="V13" s="12"/>
+      <c r="W13" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="X13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y13" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="Z13" s="13">
+      <c r="Z13" s="12">
         <v>1</v>
       </c>
     </row>

--- a/tabular/reference/herv_sublineage_data.xlsx
+++ b/tabular/reference/herv_sublineage_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABDD328-B1EA-CD48-B144-ADF75E9AD73B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E6A20B-AEFD-1243-BFBD-5F405BE46AD4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1680" yWindow="1120" windowWidth="27120" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1680" yWindow="1100" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sublineage" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="232">
   <si>
     <t>sequenceID</t>
   </si>
@@ -1657,7 +1657,7 @@
     <col min="5" max="5" width="21.6640625" customWidth="1"/>
     <col min="6" max="6" width="15.83203125" customWidth="1"/>
     <col min="7" max="8" width="19.6640625" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
     <col min="10" max="10" width="14.5" customWidth="1"/>
     <col min="11" max="11" width="25" customWidth="1"/>
     <col min="12" max="12" width="19" customWidth="1"/>
@@ -2002,7 +2002,7 @@
         <v>105</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J5" s="9" t="s">
         <v>12</v>
@@ -2077,7 +2077,7 @@
         <v>105</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J6" s="9" t="s">
         <v>12</v>
@@ -2152,7 +2152,7 @@
         <v>105</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J7" s="9" t="s">
         <v>12</v>
@@ -2227,7 +2227,7 @@
         <v>105</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J8" s="9" t="s">
         <v>12</v>
@@ -2302,7 +2302,7 @@
         <v>105</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>12</v>
@@ -2377,7 +2377,7 @@
         <v>105</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>12</v>
@@ -2452,7 +2452,7 @@
         <v>105</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>12</v>
@@ -2527,7 +2527,7 @@
         <v>105</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J12" s="9" t="s">
         <v>12</v>
@@ -2602,7 +2602,7 @@
         <v>105</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>12</v>
@@ -2677,7 +2677,7 @@
         <v>105</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>12</v>
@@ -2825,7 +2825,7 @@
         <v>105</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>12</v>
@@ -2900,7 +2900,7 @@
         <v>105</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>12</v>
@@ -2975,7 +2975,7 @@
         <v>105</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J18" s="9" t="s">
         <v>12</v>
@@ -3050,7 +3050,7 @@
         <v>105</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J19" s="9" t="s">
         <v>11</v>
@@ -3127,7 +3127,7 @@
         <v>105</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J20" s="9" t="s">
         <v>163</v>
@@ -3437,7 +3437,7 @@
         <v>105</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>12</v>
@@ -3512,7 +3512,7 @@
         <v>105</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>12</v>
@@ -3587,7 +3587,7 @@
         <v>105</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J26" s="9" t="s">
         <v>12</v>
@@ -3662,7 +3662,7 @@
         <v>105</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J27" s="9" t="s">
         <v>12</v>
@@ -3737,7 +3737,7 @@
         <v>105</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J28" s="9" t="s">
         <v>12</v>
@@ -3812,7 +3812,7 @@
         <v>105</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J29" s="9" t="s">
         <v>12</v>
@@ -3887,7 +3887,7 @@
         <v>105</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J30" s="9" t="s">
         <v>12</v>
@@ -4193,7 +4193,7 @@
         <v>105</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J34" s="9" t="s">
         <v>12</v>
@@ -4270,7 +4270,7 @@
         <v>105</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J35" s="9" t="s">
         <v>163</v>
@@ -4345,7 +4345,7 @@
         <v>105</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J36" s="9" t="s">
         <v>163</v>
@@ -4720,7 +4720,7 @@
         <v>105</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J41" s="9" t="s">
         <v>163</v>
@@ -4795,7 +4795,7 @@
         <v>105</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J42" s="9" t="s">
         <v>163</v>
@@ -4920,14 +4920,14 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA43">
-    <sortCondition ref="O2:O43"/>
-    <sortCondition ref="Q2:Q43"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AB43">
+    <sortCondition ref="P2:P43"/>
     <sortCondition ref="R2:R43"/>
+    <sortCondition ref="S2:S43"/>
     <sortCondition ref="C2:C43"/>
   </sortState>
   <conditionalFormatting sqref="AA44:AA1048576 AA1:AA5">
-    <cfRule type="colorScale" priority="37">
+    <cfRule type="colorScale" priority="47">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4939,6 +4939,114 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA6:AA8">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA9:AA19">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA20:AA21">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA24:AA25 AA22">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA37:AA38">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA39">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA40">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA30:AA32 AA34:AA36 AA41">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA42:AA43">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA23">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -4950,116 +5058,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA9:AA19">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA20:AA21">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA24:AA25 AA22">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA37:AA38">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA39">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA40">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA30:AA32 AA34:AA36 AA41">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA42:AA43">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA23">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AA26:AA29 AA33">
-    <cfRule type="colorScale" priority="45">
+    <cfRule type="colorScale" priority="55">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5076,17 +5076,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E84FD6B7-DAC0-EF4A-B6E8-A6FD2C634E5A}">
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:AA13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.1640625" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="4" max="4" width="40.5" customWidth="1"/>
     <col min="5" max="5" width="21.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.1640625" customWidth="1"/>
+    <col min="6" max="7" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -5106,67 +5106,70 @@
         <v>179</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>181</v>
       </c>
@@ -5188,43 +5191,43 @@
       <c r="G2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
-      <c r="M2" s="2">
+      <c r="M2" s="2"/>
+      <c r="N2" s="2">
         <v>8214</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="O2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="2">
+      <c r="U2" s="2">
         <v>20</v>
       </c>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2">
+      <c r="V2" s="2"/>
+      <c r="W2" s="2">
         <v>31167914</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>10</v>
@@ -5232,11 +5235,14 @@
       <c r="Y2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="Z2" s="2">
+      <c r="Z2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA2" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>182</v>
       </c>
@@ -5258,43 +5264,43 @@
       <c r="G3" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
-      <c r="M3" s="2">
+      <c r="M3" s="2"/>
+      <c r="N3" s="2">
         <v>8214</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="O3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="T3" s="2">
+      <c r="U3" s="2">
         <v>20</v>
       </c>
-      <c r="U3" s="2"/>
-      <c r="V3" s="2">
+      <c r="V3" s="2"/>
+      <c r="W3" s="2">
         <v>31167914</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="X3" s="2" t="s">
         <v>10</v>
@@ -5302,11 +5308,14 @@
       <c r="Y3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="Z3" s="2">
+      <c r="Z3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA3" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>129</v>
       </c>
@@ -5329,46 +5338,46 @@
         <v>105</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="J4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="K4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="2"/>
+      <c r="O4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="T4" s="2"/>
       <c r="U4" s="2"/>
-      <c r="V4" s="2">
+      <c r="V4" s="2"/>
+      <c r="W4" s="2">
         <v>28397686</v>
-      </c>
-      <c r="W4" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>10</v>
@@ -5376,11 +5385,14 @@
       <c r="Y4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="Z4" s="2">
+      <c r="Z4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA4" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>132</v>
       </c>
@@ -5403,46 +5415,46 @@
         <v>105</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="J5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="K5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="2"/>
+      <c r="O5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="P5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="Q5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="R5" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="S5" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="S5" s="2" t="s">
+      <c r="T5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="T5" s="2"/>
       <c r="U5" s="2"/>
-      <c r="V5" s="2">
+      <c r="V5" s="2"/>
+      <c r="W5" s="2">
         <v>28397686</v>
-      </c>
-      <c r="W5" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="X5" s="2" t="s">
         <v>10</v>
@@ -5450,11 +5462,14 @@
       <c r="Y5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="Z5" s="2">
+      <c r="Z5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA5" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>137</v>
       </c>
@@ -5477,46 +5492,46 @@
         <v>105</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="J6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="K6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="6" t="s">
+      <c r="N6" s="2"/>
+      <c r="O6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q6" s="1" t="s">
+      <c r="R6" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="S6" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="T6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="T6" s="2"/>
       <c r="U6" s="2"/>
-      <c r="V6" s="2">
+      <c r="V6" s="2"/>
+      <c r="W6" s="2">
         <v>28397686</v>
-      </c>
-      <c r="W6" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="X6" s="2" t="s">
         <v>10</v>
@@ -5524,11 +5539,14 @@
       <c r="Y6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="Z6" s="2">
+      <c r="Z6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA6" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>192</v>
       </c>
@@ -5547,60 +5565,63 @@
       <c r="F7" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="2" t="s">
         <v>105</v>
       </c>
       <c r="H7" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I7" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="I7" s="9" t="s">
-        <v>12</v>
-      </c>
       <c r="J7" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="L7" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="M7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="M7" s="12">
+      <c r="N7" s="12">
         <v>2482</v>
       </c>
-      <c r="N7" s="10" t="s">
+      <c r="O7" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="O7" s="9" t="s">
+      <c r="P7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="P7" s="9" t="s">
+      <c r="Q7" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="9" t="s">
+      <c r="R7" s="9"/>
+      <c r="S7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="S7" s="9" t="s">
+      <c r="T7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="T7" s="12"/>
       <c r="U7" s="12"/>
       <c r="V7" s="12"/>
-      <c r="W7" s="9" t="s">
+      <c r="W7" s="12"/>
+      <c r="X7" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="X7" s="9" t="s">
-        <v>11</v>
-      </c>
       <c r="Y7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z7" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="Z7" s="12">
+      <c r="AA7" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>22</v>
       </c>
@@ -5619,60 +5640,63 @@
       <c r="F8" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="I8" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="I8" s="9" t="s">
-        <v>11</v>
-      </c>
       <c r="J8" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L8" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="M8" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="9">
+      <c r="N8" s="9">
         <v>5667</v>
       </c>
-      <c r="N8" s="10" t="s">
+      <c r="O8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O8" s="9" t="s">
+      <c r="P8" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="P8" s="9" t="s">
+      <c r="Q8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="9" t="s">
+      <c r="R8" s="1"/>
+      <c r="S8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="S8" s="9" t="s">
+      <c r="T8" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="T8" s="9"/>
       <c r="U8" s="9"/>
       <c r="V8" s="9"/>
-      <c r="W8" s="9" t="s">
+      <c r="W8" s="9"/>
+      <c r="X8" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="X8" s="9" t="s">
-        <v>11</v>
-      </c>
       <c r="Y8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="Z8" s="9">
+      <c r="Z8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA8" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>61</v>
       </c>
@@ -5691,64 +5715,67 @@
       <c r="F9" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H9" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="I9" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>11</v>
-      </c>
       <c r="J9" s="9" t="s">
         <v>11</v>
       </c>
       <c r="K9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="L9" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="M9" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="9">
+      <c r="N9" s="9">
         <v>7418</v>
       </c>
-      <c r="N9" s="10" t="s">
+      <c r="O9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="9" t="s">
+      <c r="P9" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="9" t="s">
+      <c r="Q9" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="Q9" s="1" t="s">
+      <c r="R9" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="R9" s="9" t="s">
+      <c r="S9" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="S9" s="9" t="s">
+      <c r="T9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="T9" s="9"/>
       <c r="U9" s="9"/>
-      <c r="V9" s="12">
+      <c r="V9" s="9"/>
+      <c r="W9" s="12">
         <v>2825129</v>
       </c>
-      <c r="W9" s="9" t="s">
+      <c r="X9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="X9" s="9" t="s">
-        <v>11</v>
-      </c>
       <c r="Y9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="Z9" s="9">
+      <c r="Z9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA9" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>53</v>
       </c>
@@ -5767,60 +5794,63 @@
       <c r="F10" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="I10" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>12</v>
-      </c>
       <c r="J10" s="9" t="s">
         <v>12</v>
       </c>
       <c r="K10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L10" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="M10" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="9">
+      <c r="N10" s="9">
         <v>4102</v>
       </c>
-      <c r="N10" s="10" t="s">
+      <c r="O10" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="O10" s="9" t="s">
+      <c r="P10" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="9" t="s">
+      <c r="Q10" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="9" t="s">
+      <c r="R10" s="1"/>
+      <c r="S10" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="S10" s="9" t="s">
+      <c r="T10" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="T10" s="9"/>
       <c r="U10" s="9"/>
       <c r="V10" s="9"/>
-      <c r="W10" s="9" t="s">
-        <v>10</v>
-      </c>
+      <c r="W10" s="9"/>
       <c r="X10" s="9" t="s">
         <v>10</v>
       </c>
       <c r="Y10" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z10" s="9">
+        <v>10</v>
+      </c>
+      <c r="Z10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA10" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
         <v>16</v>
       </c>
@@ -5839,62 +5869,65 @@
       <c r="F11" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H11" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="I11" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="I11" s="9" t="s">
-        <v>11</v>
-      </c>
       <c r="J11" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="M11" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="M11" s="9">
+      <c r="N11" s="9">
         <v>9611</v>
       </c>
-      <c r="N11" s="10" t="s">
+      <c r="O11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="O11" s="9" t="s">
+      <c r="P11" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="P11" s="9" t="s">
+      <c r="Q11" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="Q11" s="1" t="s">
+      <c r="R11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R11" s="9" t="s">
+      <c r="S11" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="S11" s="9" t="s">
+      <c r="T11" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="T11" s="9"/>
       <c r="U11" s="9"/>
       <c r="V11" s="9"/>
-      <c r="W11" s="9" t="s">
+      <c r="W11" s="9"/>
+      <c r="X11" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="X11" s="9" t="s">
-        <v>11</v>
-      </c>
       <c r="Y11" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="Z11" s="9">
+      <c r="Z11" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA11" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>39</v>
       </c>
@@ -5913,60 +5946,63 @@
       <c r="F12" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H12" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="I12" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="I12" s="9" t="s">
-        <v>11</v>
-      </c>
       <c r="J12" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="M12" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="9">
+      <c r="N12" s="9">
         <v>7613</v>
       </c>
-      <c r="N12" s="10" t="s">
+      <c r="O12" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="O12" s="9" t="s">
+      <c r="P12" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="P12" s="9" t="s">
+      <c r="Q12" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="9" t="s">
+      <c r="R12" s="1"/>
+      <c r="S12" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="S12" s="9" t="s">
+      <c r="T12" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="T12" s="9"/>
       <c r="U12" s="9"/>
       <c r="V12" s="9"/>
-      <c r="W12" s="9" t="s">
+      <c r="W12" s="9"/>
+      <c r="X12" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="X12" s="9" t="s">
-        <v>11</v>
-      </c>
       <c r="Y12" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="Z12" s="9">
+      <c r="Z12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA12" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>192</v>
       </c>
@@ -5985,61 +6021,64 @@
       <c r="F13" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="2" t="s">
         <v>105</v>
       </c>
       <c r="H13" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I13" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="I13" s="9" t="s">
-        <v>12</v>
-      </c>
       <c r="J13" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="L13" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="M13" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="M13" s="12">
+      <c r="N13" s="12">
         <v>2482</v>
       </c>
-      <c r="N13" s="10" t="s">
+      <c r="O13" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="O13" s="9" t="s">
+      <c r="P13" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="P13" s="9" t="s">
+      <c r="Q13" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="9" t="s">
+      <c r="R13" s="9"/>
+      <c r="S13" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="S13" s="9" t="s">
+      <c r="T13" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="T13" s="12"/>
       <c r="U13" s="12"/>
       <c r="V13" s="12"/>
-      <c r="W13" s="9" t="s">
+      <c r="W13" s="12"/>
+      <c r="X13" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="X13" s="9" t="s">
-        <v>11</v>
-      </c>
       <c r="Y13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z13" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="Z13" s="12">
+      <c r="AA13" s="12">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="Z2">
+  <conditionalFormatting sqref="AA2">
     <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
@@ -6051,7 +6090,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z3">
+  <conditionalFormatting sqref="AA3">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
@@ -6063,7 +6102,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z1">
+  <conditionalFormatting sqref="AA1">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min"/>
@@ -6075,7 +6114,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z4:Z5">
+  <conditionalFormatting sqref="AA4:AA5">
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
@@ -6087,7 +6126,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z7">
+  <conditionalFormatting sqref="AA7">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -6099,7 +6138,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z6">
+  <conditionalFormatting sqref="AA6">
     <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="min"/>
@@ -6111,7 +6150,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z8">
+  <conditionalFormatting sqref="AA8">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -6123,7 +6162,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z9">
+  <conditionalFormatting sqref="AA9">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -6135,7 +6174,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z10">
+  <conditionalFormatting sqref="AA10">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -6147,7 +6186,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z11:Z12">
+  <conditionalFormatting sqref="AA11:AA12">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -6159,7 +6198,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z13">
+  <conditionalFormatting sqref="AA13">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/tabular/reference/herv_sublineage_data.xlsx
+++ b/tabular/reference/herv_sublineage_data.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E6A20B-AEFD-1243-BFBD-5F405BE46AD4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341FA787-1BF4-C64C-B0A0-9AB52AA6E50C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1680" yWindow="1100" windowWidth="27120" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1240" yWindow="500" windowWidth="23060" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sublineage" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="removed" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="233">
   <si>
     <t>sequenceID</t>
   </si>
@@ -546,9 +547,6 @@
     <t>ERV-1.Gamma.T</t>
   </si>
   <si>
-    <t>ERV-2.Gamma.E</t>
-  </si>
-  <si>
     <t>ERV-3.Lamba.L</t>
   </si>
   <si>
@@ -612,9 +610,6 @@
     <t>HERV-V</t>
   </si>
   <si>
-    <t>ERV-1.Unclassified.Pb</t>
-  </si>
-  <si>
     <t>Unclassified</t>
   </si>
   <si>
@@ -663,9 +658,6 @@
     <t>ERVR-1.Zeta.MER57</t>
   </si>
   <si>
-    <t>ERVR-1.Gamma.Eta.HQ</t>
-  </si>
-  <si>
     <t>ERV-1.Unclassified.MER4</t>
   </si>
   <si>
@@ -727,6 +719,18 @@
   </si>
   <si>
     <t>ERV3-16A3a</t>
+  </si>
+  <si>
+    <t>ERV-1.Iota.I.Pb</t>
+  </si>
+  <si>
+    <t>Iotaretrovirus</t>
+  </si>
+  <si>
+    <t>ERVR-1.Gamma.Eta.E.HQ</t>
+  </si>
+  <si>
+    <t>ERVR-1.Gamma.Eta.E</t>
   </si>
 </sst>
 </file>
@@ -1263,7 +1267,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
@@ -1285,7 +1289,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1647,7 +1650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB9083D8-DE01-F14E-ACB5-AF33867092C5}">
-  <dimension ref="A1:AA43"/>
+  <dimension ref="A1:AA33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -1671,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>68</v>
@@ -1683,13 +1686,13 @@
         <v>168</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>159</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>160</v>
@@ -1754,7 +1757,7 @@
         <v>83</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>83</v>
@@ -1763,10 +1766,10 @@
         <v>83</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>171</v>
+        <v>232</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>165</v>
@@ -1828,19 +1831,19 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>163</v>
@@ -1855,19 +1858,19 @@
         <v>161</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>12</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M3" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N3" s="9">
-        <v>4936</v>
+        <v>9084</v>
       </c>
       <c r="O3" s="10" t="s">
         <v>14</v>
@@ -1876,7 +1879,7 @@
         <v>5</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="R3" s="1"/>
       <c r="S3" s="9" t="s">
@@ -1889,7 +1892,7 @@
       <c r="V3" s="9"/>
       <c r="W3" s="9"/>
       <c r="X3" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="Y3" s="9" t="s">
         <v>11</v>
@@ -1903,25 +1906,25 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>121</v>
+        <v>212</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>91</v>
+        <v>41</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>41</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>163</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>105</v>
@@ -1930,19 +1933,19 @@
         <v>161</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>163</v>
+        <v>12</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>12</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="M4" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N4" s="9">
-        <v>9084</v>
+        <v>8120</v>
       </c>
       <c r="O4" s="10" t="s">
         <v>14</v>
@@ -1951,7 +1954,7 @@
         <v>5</v>
       </c>
       <c r="Q4" s="9" t="s">
-        <v>214</v>
+        <v>38</v>
       </c>
       <c r="R4" s="1"/>
       <c r="S4" s="9" t="s">
@@ -1964,7 +1967,7 @@
       <c r="V4" s="9"/>
       <c r="W4" s="9"/>
       <c r="X4" s="9" t="s">
-        <v>197</v>
+        <v>34</v>
       </c>
       <c r="Y4" s="9" t="s">
         <v>11</v>
@@ -1978,25 +1981,25 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>93</v>
+        <v>43</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>43</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>163</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>105</v>
@@ -2011,13 +2014,13 @@
         <v>12</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M5" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N5" s="9">
-        <v>1786</v>
+        <v>4798</v>
       </c>
       <c r="O5" s="10" t="s">
         <v>14</v>
@@ -2052,20 +2055,20 @@
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A6" s="13" t="s">
-        <v>41</v>
+      <c r="A6" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>41</v>
+        <v>141</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>163</v>
@@ -2086,13 +2089,13 @@
         <v>12</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M6" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N6" s="9">
-        <v>8120</v>
+        <v>6639</v>
       </c>
       <c r="O6" s="10" t="s">
         <v>14</v>
@@ -2128,19 +2131,19 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>42</v>
+        <v>147</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>163</v>
@@ -2161,13 +2164,13 @@
         <v>12</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="M7" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N7" s="9">
-        <v>4060</v>
+        <v>5217</v>
       </c>
       <c r="O7" s="10" t="s">
         <v>14</v>
@@ -2203,19 +2206,19 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>43</v>
+        <v>149</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>163</v>
@@ -2236,13 +2239,13 @@
         <v>12</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="M8" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N8" s="9">
-        <v>4798</v>
+        <v>7048</v>
       </c>
       <c r="O8" s="10" t="s">
         <v>14</v>
@@ -2278,25 +2281,25 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>141</v>
+        <v>193</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>174</v>
+        <v>229</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>105</v>
@@ -2308,17 +2311,15 @@
         <v>12</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="M9" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="9">
-        <v>6639</v>
-      </c>
+      <c r="N9" s="12"/>
       <c r="O9" s="10" t="s">
         <v>14</v>
       </c>
@@ -2326,18 +2327,18 @@
         <v>5</v>
       </c>
       <c r="Q9" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="R9" s="1"/>
+        <v>230</v>
+      </c>
+      <c r="R9" s="9"/>
       <c r="S9" s="9" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="U9" s="9"/>
-      <c r="V9" s="9"/>
-      <c r="W9" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="U9" s="12"/>
+      <c r="V9" s="12"/>
+      <c r="W9" s="12"/>
       <c r="X9" s="9" t="s">
         <v>34</v>
       </c>
@@ -2345,24 +2346,24 @@
         <v>11</v>
       </c>
       <c r="Z9" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA9" s="9">
-        <v>4</v>
+        <v>10</v>
+      </c>
+      <c r="AA9" s="12">
+        <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>221</v>
+        <v>124</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>174</v>
@@ -2371,7 +2372,7 @@
         <v>163</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>105</v>
@@ -2380,19 +2381,19 @@
         <v>161</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>12</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="M10" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N10" s="9">
-        <v>933</v>
+        <v>4981</v>
       </c>
       <c r="O10" s="10" t="s">
         <v>14</v>
@@ -2401,9 +2402,11 @@
         <v>5</v>
       </c>
       <c r="Q10" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="R10" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>205</v>
+      </c>
       <c r="S10" s="9" t="s">
         <v>6</v>
       </c>
@@ -2414,7 +2417,7 @@
       <c r="V10" s="9"/>
       <c r="W10" s="9"/>
       <c r="X10" s="9" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="Y10" s="9" t="s">
         <v>11</v>
@@ -2423,30 +2426,30 @@
         <v>11</v>
       </c>
       <c r="AA10" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>143</v>
+        <v>58</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>163</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>105</v>
@@ -2455,19 +2458,19 @@
         <v>161</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="K11" s="9" t="s">
         <v>12</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="M11" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N11" s="9">
-        <v>4936</v>
+        <v>6996</v>
       </c>
       <c r="O11" s="10" t="s">
         <v>14</v>
@@ -2476,9 +2479,11 @@
         <v>5</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="R11" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>204</v>
+      </c>
       <c r="S11" s="9" t="s">
         <v>6</v>
       </c>
@@ -2489,7 +2494,7 @@
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
       <c r="X11" s="9" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="Y11" s="9" t="s">
         <v>11</v>
@@ -2498,30 +2503,30 @@
         <v>11</v>
       </c>
       <c r="AA11" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>144</v>
+        <v>59</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>165</v>
+        <v>203</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>105</v>
@@ -2530,19 +2535,19 @@
         <v>161</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="M12" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N12" s="9">
-        <v>5356</v>
+        <v>11027</v>
       </c>
       <c r="O12" s="10" t="s">
         <v>14</v>
@@ -2551,9 +2556,11 @@
         <v>5</v>
       </c>
       <c r="Q12" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="R12" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>204</v>
+      </c>
       <c r="S12" s="9" t="s">
         <v>6</v>
       </c>
@@ -2562,7 +2569,9 @@
       </c>
       <c r="U12" s="9"/>
       <c r="V12" s="9"/>
-      <c r="W12" s="9"/>
+      <c r="W12" s="9">
+        <v>2825129</v>
+      </c>
       <c r="X12" s="9" t="s">
         <v>34</v>
       </c>
@@ -2578,25 +2587,25 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>163</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>165</v>
+        <v>203</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>105</v>
@@ -2605,19 +2614,19 @@
         <v>161</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="M13" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N13" s="9">
-        <v>5217</v>
+        <v>8987</v>
       </c>
       <c r="O13" s="10" t="s">
         <v>14</v>
@@ -2626,9 +2635,11 @@
         <v>5</v>
       </c>
       <c r="Q13" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="R13" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>204</v>
+      </c>
       <c r="S13" s="9" t="s">
         <v>6</v>
       </c>
@@ -2637,9 +2648,11 @@
       </c>
       <c r="U13" s="9"/>
       <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
+      <c r="W13" s="12">
+        <v>2825129</v>
+      </c>
       <c r="X13" s="9" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="Y13" s="9" t="s">
         <v>11</v>
@@ -2653,25 +2666,25 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>52</v>
+        <v>197</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>52</v>
+        <v>197</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>149</v>
+        <v>197</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>165</v>
+        <v>203</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>105</v>
@@ -2680,20 +2693,18 @@
         <v>161</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>52</v>
+        <v>197</v>
       </c>
       <c r="M14" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="9">
-        <v>7048</v>
-      </c>
+      <c r="N14" s="9"/>
       <c r="O14" s="10" t="s">
         <v>14</v>
       </c>
@@ -2701,20 +2712,22 @@
         <v>5</v>
       </c>
       <c r="Q14" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="R14" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>204</v>
+      </c>
       <c r="S14" s="9" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U14" s="9"/>
       <c r="V14" s="9"/>
-      <c r="W14" s="9"/>
+      <c r="W14" s="12"/>
       <c r="X14" s="9" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="Y14" s="9" t="s">
         <v>11</v>
@@ -2722,28 +2735,28 @@
       <c r="Z14" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="AA14" s="9">
-        <v>4</v>
+      <c r="AA14" s="12">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>191</v>
+        <v>55</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>193</v>
+        <v>125</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>191</v>
+        <v>55</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>195</v>
+        <v>94</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>164</v>
@@ -2758,15 +2771,17 @@
         <v>12</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>191</v>
+        <v>55</v>
       </c>
       <c r="M15" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="N15" s="12"/>
+      <c r="N15" s="9">
+        <v>5586</v>
+      </c>
       <c r="O15" s="10" t="s">
         <v>14</v>
       </c>
@@ -2774,18 +2789,18 @@
         <v>5</v>
       </c>
       <c r="Q15" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="R15" s="9"/>
+        <v>54</v>
+      </c>
+      <c r="R15" s="1"/>
       <c r="S15" s="9" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T15" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="U15" s="12"/>
-      <c r="V15" s="12"/>
-      <c r="W15" s="12"/>
+        <v>9</v>
+      </c>
+      <c r="U15" s="9"/>
+      <c r="V15" s="9"/>
+      <c r="W15" s="9"/>
       <c r="X15" s="9" t="s">
         <v>34</v>
       </c>
@@ -2793,33 +2808,33 @@
         <v>11</v>
       </c>
       <c r="Z15" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA15" s="12">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="AA15" s="9">
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>211</v>
+        <v>126</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>163</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>105</v>
@@ -2834,13 +2849,13 @@
         <v>12</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="M16" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N16" s="9">
-        <v>6387</v>
+        <v>6918</v>
       </c>
       <c r="O16" s="10" t="s">
         <v>14</v>
@@ -2849,7 +2864,7 @@
         <v>5</v>
       </c>
       <c r="Q16" s="9" t="s">
-        <v>194</v>
+        <v>54</v>
       </c>
       <c r="R16" s="1"/>
       <c r="S16" s="9" t="s">
@@ -2876,19 +2891,19 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>163</v>
@@ -2909,13 +2924,13 @@
         <v>12</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="M17" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N17" s="9">
-        <v>6758</v>
+        <v>3944</v>
       </c>
       <c r="O17" s="10" t="s">
         <v>14</v>
@@ -2924,7 +2939,7 @@
         <v>5</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>194</v>
+        <v>54</v>
       </c>
       <c r="R17" s="1"/>
       <c r="S17" s="9" t="s">
@@ -2951,19 +2966,19 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>163</v>
@@ -2984,13 +2999,13 @@
         <v>12</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="M18" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N18" s="9">
-        <v>4871</v>
+        <v>7133</v>
       </c>
       <c r="O18" s="10" t="s">
         <v>14</v>
@@ -2999,7 +3014,7 @@
         <v>5</v>
       </c>
       <c r="Q18" s="9" t="s">
-        <v>194</v>
+        <v>54</v>
       </c>
       <c r="R18" s="1"/>
       <c r="S18" s="9" t="s">
@@ -3015,7 +3030,7 @@
         <v>34</v>
       </c>
       <c r="Y18" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z18" s="9" t="s">
         <v>11</v>
@@ -3024,27 +3039,27 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>124</v>
+        <v>223</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>163</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H19" s="9" t="s">
         <v>105</v>
@@ -3053,19 +3068,19 @@
         <v>161</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>12</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M19" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N19" s="9">
-        <v>4981</v>
+        <v>4285</v>
       </c>
       <c r="O19" s="10" t="s">
         <v>14</v>
@@ -3076,9 +3091,7 @@
       <c r="Q19" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="R19" s="1" t="s">
-        <v>207</v>
-      </c>
+      <c r="R19" s="1"/>
       <c r="S19" s="9" t="s">
         <v>6</v>
       </c>
@@ -3089,7 +3102,7 @@
       <c r="V19" s="9"/>
       <c r="W19" s="9"/>
       <c r="X19" s="9" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="Y19" s="9" t="s">
         <v>11</v>
@@ -3098,30 +3111,30 @@
         <v>11</v>
       </c>
       <c r="AA19" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>96</v>
+        <v>66</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>154</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>163</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>105</v>
@@ -3130,19 +3143,19 @@
         <v>161</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>163</v>
+        <v>12</v>
       </c>
       <c r="K20" s="9" t="s">
         <v>12</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="M20" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N20" s="9">
-        <v>6996</v>
+        <v>4880</v>
       </c>
       <c r="O20" s="10" t="s">
         <v>14</v>
@@ -3153,9 +3166,7 @@
       <c r="Q20" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="R20" s="1" t="s">
-        <v>206</v>
-      </c>
+      <c r="R20" s="1"/>
       <c r="S20" s="9" t="s">
         <v>6</v>
       </c>
@@ -3166,7 +3177,7 @@
       <c r="V20" s="9"/>
       <c r="W20" s="9"/>
       <c r="X20" s="9" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="Y20" s="9" t="s">
         <v>11</v>
@@ -3175,30 +3186,30 @@
         <v>11</v>
       </c>
       <c r="AA20" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>59</v>
+        <v>155</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>105</v>
@@ -3207,19 +3218,19 @@
         <v>161</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>163</v>
+        <v>12</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="M21" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N21" s="9">
-        <v>11027</v>
+        <v>2880</v>
       </c>
       <c r="O21" s="10" t="s">
         <v>14</v>
@@ -3230,9 +3241,7 @@
       <c r="Q21" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="R21" s="1" t="s">
-        <v>206</v>
-      </c>
+      <c r="R21" s="1"/>
       <c r="S21" s="9" t="s">
         <v>6</v>
       </c>
@@ -3241,43 +3250,41 @@
       </c>
       <c r="U21" s="9"/>
       <c r="V21" s="9"/>
-      <c r="W21" s="9">
-        <v>2825129</v>
-      </c>
+      <c r="W21" s="9"/>
       <c r="X21" s="9" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="Y21" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z21" s="9" t="s">
         <v>11</v>
       </c>
       <c r="AA21" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>200</v>
+        <v>227</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>119</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>60</v>
+        <v>227</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>60</v>
+        <v>227</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>203</v>
+        <v>106</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>163</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>205</v>
+        <v>164</v>
       </c>
       <c r="H22" s="9" t="s">
         <v>105</v>
@@ -3286,43 +3293,41 @@
         <v>161</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>60</v>
+        <v>228</v>
       </c>
       <c r="M22" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N22" s="9">
-        <v>8987</v>
+        <v>6070</v>
       </c>
       <c r="O22" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P22" s="9" t="s">
         <v>5</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>206</v>
+        <v>19</v>
+      </c>
+      <c r="R22" s="13">
+        <v>16</v>
       </c>
       <c r="S22" s="9" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T22" s="9" t="s">
         <v>9</v>
       </c>
       <c r="U22" s="9"/>
       <c r="V22" s="9"/>
-      <c r="W22" s="12">
-        <v>2825129</v>
-      </c>
+      <c r="W22" s="9"/>
       <c r="X22" s="9" t="s">
         <v>10</v>
       </c>
@@ -3333,30 +3338,30 @@
         <v>11</v>
       </c>
       <c r="AA22" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>202</v>
+        <v>20</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>106</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="E23" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="G23" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>205</v>
       </c>
       <c r="H23" s="9" t="s">
         <v>105</v>
@@ -3368,36 +3373,38 @@
         <v>11</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>11</v>
+        <v>163</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="M23" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="N23" s="9"/>
+      <c r="N23" s="9">
+        <v>5667</v>
+      </c>
       <c r="O23" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P23" s="9" t="s">
         <v>5</v>
       </c>
       <c r="Q23" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>206</v>
+        <v>19</v>
+      </c>
+      <c r="R23" s="13" t="s">
+        <v>222</v>
       </c>
       <c r="S23" s="9" t="s">
         <v>13</v>
       </c>
       <c r="T23" s="9" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U23" s="9"/>
       <c r="V23" s="9"/>
-      <c r="W23" s="12"/>
+      <c r="W23" s="9"/>
       <c r="X23" s="9" t="s">
         <v>10</v>
       </c>
@@ -3407,31 +3414,31 @@
       <c r="Z23" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="AA23" s="12">
-        <v>1</v>
+      <c r="AA23" s="9">
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>125</v>
+        <v>21</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>115</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>94</v>
+        <v>21</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>87</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="H24" s="9" t="s">
         <v>105</v>
@@ -3440,32 +3447,34 @@
         <v>161</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K24" s="9" t="s">
         <v>12</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="M24" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N24" s="9">
-        <v>5586</v>
+        <v>5714</v>
       </c>
       <c r="O24" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P24" s="9" t="s">
         <v>5</v>
       </c>
       <c r="Q24" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="R24" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>222</v>
+      </c>
       <c r="S24" s="9" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T24" s="9" t="s">
         <v>9</v>
@@ -3474,7 +3483,7 @@
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
       <c r="X24" s="9" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="Y24" s="9" t="s">
         <v>11</v>
@@ -3483,29 +3492,29 @@
         <v>11</v>
       </c>
       <c r="AA24" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>126</v>
+        <v>23</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>108</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="3" t="s">
         <v>164</v>
       </c>
       <c r="H25" s="9" t="s">
@@ -3521,26 +3530,28 @@
         <v>12</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="M25" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N25" s="9">
-        <v>6918</v>
+        <v>4996</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>5</v>
       </c>
       <c r="Q25" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="R25" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="R25" s="14">
+        <v>16</v>
+      </c>
       <c r="S25" s="9" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T25" s="9" t="s">
         <v>9</v>
@@ -3549,7 +3560,7 @@
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
       <c r="X25" s="9" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="Y25" s="9" t="s">
         <v>11</v>
@@ -3558,30 +3569,30 @@
         <v>11</v>
       </c>
       <c r="AA25" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>208</v>
+        <v>24</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>109</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="G26" s="9" t="s">
-        <v>165</v>
+      <c r="G26" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>105</v>
@@ -3590,32 +3601,32 @@
         <v>161</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>12</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="M26" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N26" s="9">
-        <v>3944</v>
+        <v>3556</v>
       </c>
       <c r="O26" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P26" s="9" t="s">
         <v>5</v>
       </c>
       <c r="Q26" s="9" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="R26" s="1"/>
       <c r="S26" s="9" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T26" s="9" t="s">
         <v>9</v>
@@ -3638,25 +3649,25 @@
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>209</v>
+        <v>25</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>110</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>152</v>
+        <v>99</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>163</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H27" s="9" t="s">
         <v>105</v>
@@ -3665,32 +3676,32 @@
         <v>161</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>12</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="M27" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N27" s="9">
-        <v>7133</v>
+        <v>5343</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P27" s="9" t="s">
         <v>5</v>
       </c>
       <c r="Q27" s="9" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="R27" s="1"/>
       <c r="S27" s="9" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T27" s="9" t="s">
         <v>9</v>
@@ -3699,7 +3710,7 @@
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
       <c r="X27" s="9" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="Y27" s="9" t="s">
         <v>11</v>
@@ -3713,25 +3724,25 @@
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>226</v>
+        <v>27</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>111</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>153</v>
+        <v>100</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>163</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H28" s="9" t="s">
         <v>105</v>
@@ -3740,32 +3751,32 @@
         <v>161</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="K28" s="9" t="s">
         <v>12</v>
       </c>
       <c r="L28" s="9" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="M28" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N28" s="9">
-        <v>4285</v>
+        <v>5530</v>
       </c>
       <c r="O28" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P28" s="9" t="s">
         <v>5</v>
       </c>
       <c r="Q28" s="9" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="R28" s="1"/>
       <c r="S28" s="9" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T28" s="9" t="s">
         <v>9</v>
@@ -3774,7 +3785,7 @@
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
       <c r="X28" s="9" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="Y28" s="9" t="s">
         <v>11</v>
@@ -3788,25 +3799,25 @@
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>227</v>
+        <v>28</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>112</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>154</v>
+        <v>101</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="G29" s="9" t="s">
-        <v>165</v>
+      <c r="G29" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="H29" s="9" t="s">
         <v>105</v>
@@ -3815,32 +3826,32 @@
         <v>161</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="K29" s="9" t="s">
         <v>12</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="M29" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N29" s="9">
-        <v>4880</v>
+        <v>3329</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>5</v>
       </c>
       <c r="Q29" s="9" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="R29" s="1"/>
       <c r="S29" s="9" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T29" s="9" t="s">
         <v>9</v>
@@ -3849,7 +3860,7 @@
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
       <c r="X29" s="9" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="Y29" s="9" t="s">
         <v>11</v>
@@ -3863,25 +3874,25 @@
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>228</v>
+        <v>30</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>114</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H30" s="9" t="s">
         <v>105</v>
@@ -3890,32 +3901,32 @@
         <v>161</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="K30" s="9" t="s">
         <v>12</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="M30" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N30" s="9">
-        <v>2880</v>
+        <v>5685</v>
       </c>
       <c r="O30" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P30" s="9" t="s">
         <v>5</v>
       </c>
       <c r="Q30" s="9" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="R30" s="1"/>
       <c r="S30" s="9" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T30" s="9" t="s">
         <v>9</v>
@@ -3924,39 +3935,39 @@
       <c r="V30" s="9"/>
       <c r="W30" s="9"/>
       <c r="X30" s="9" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="Y30" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z30" s="9" t="s">
         <v>11</v>
       </c>
       <c r="AA30" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
-        <v>230</v>
+        <v>31</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>230</v>
+        <v>31</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>230</v>
+        <v>156</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>106</v>
+        <v>171</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>163</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H31" s="9" t="s">
         <v>105</v>
@@ -3965,19 +3976,19 @@
         <v>161</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>12</v>
       </c>
       <c r="L31" s="9" t="s">
-        <v>231</v>
+        <v>31</v>
       </c>
       <c r="M31" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N31" s="9">
-        <v>6070</v>
+        <v>5023</v>
       </c>
       <c r="O31" s="10" t="s">
         <v>18</v>
@@ -3988,9 +3999,7 @@
       <c r="Q31" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="R31" s="14">
-        <v>16</v>
-      </c>
+      <c r="R31" s="1"/>
       <c r="S31" s="9" t="s">
         <v>13</v>
       </c>
@@ -4010,30 +4019,30 @@
         <v>11</v>
       </c>
       <c r="AA31" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>106</v>
+        <v>171</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="H32" s="9" t="s">
         <v>105</v>
@@ -4042,19 +4051,19 @@
         <v>161</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>11</v>
+        <v>163</v>
       </c>
       <c r="K32" s="9" t="s">
-        <v>163</v>
+        <v>12</v>
       </c>
       <c r="L32" s="9" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="M32" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N32" s="9">
-        <v>5667</v>
+        <v>6189</v>
       </c>
       <c r="O32" s="10" t="s">
         <v>18</v>
@@ -4065,9 +4074,7 @@
       <c r="Q32" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="R32" s="14" t="s">
-        <v>225</v>
-      </c>
+      <c r="R32" s="1"/>
       <c r="S32" s="9" t="s">
         <v>13</v>
       </c>
@@ -4078,7 +4085,7 @@
       <c r="V32" s="9"/>
       <c r="W32" s="9"/>
       <c r="X32" s="9" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="Y32" s="9" t="s">
         <v>11</v>
@@ -4087,30 +4094,30 @@
         <v>11</v>
       </c>
       <c r="AA32" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>87</v>
+        <v>37</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>85</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>106</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>205</v>
+        <v>164</v>
       </c>
       <c r="H33" s="9" t="s">
         <v>105</v>
@@ -4119,19 +4126,19 @@
         <v>161</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>11</v>
+        <v>163</v>
       </c>
       <c r="K33" s="9" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="M33" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N33" s="9">
-        <v>5714</v>
+        <v>5246</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>18</v>
@@ -4140,11 +4147,9 @@
         <v>5</v>
       </c>
       <c r="Q33" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="R33" s="1" t="s">
-        <v>225</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="R33" s="1"/>
       <c r="S33" s="9" t="s">
         <v>13</v>
       </c>
@@ -4164,769 +4169,17 @@
         <v>11</v>
       </c>
       <c r="AA33" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A34" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J34" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K34" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="L34" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="M34" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N34" s="9">
-        <v>4996</v>
-      </c>
-      <c r="O34" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="P34" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q34" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="R34" s="15">
-        <v>16</v>
-      </c>
-      <c r="S34" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="T34" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="U34" s="9"/>
-      <c r="V34" s="9"/>
-      <c r="W34" s="9"/>
-      <c r="X34" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y34" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z34" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA34" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A35" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J35" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="L35" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="M35" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N35" s="9">
-        <v>3556</v>
-      </c>
-      <c r="O35" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="P35" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q35" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="R35" s="1"/>
-      <c r="S35" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="T35" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="U35" s="9"/>
-      <c r="V35" s="9"/>
-      <c r="W35" s="9"/>
-      <c r="X35" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y35" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z35" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA35" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A36" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J36" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="L36" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="M36" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N36" s="9">
-        <v>5343</v>
-      </c>
-      <c r="O36" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="P36" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q36" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="R36" s="1"/>
-      <c r="S36" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="T36" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y36" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z36" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA36" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A37" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J37" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="K37" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="L37" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="M37" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N37" s="9">
-        <v>5530</v>
-      </c>
-      <c r="O37" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="P37" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q37" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="R37" s="1"/>
-      <c r="S37" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="T37" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="U37" s="9"/>
-      <c r="V37" s="9"/>
-      <c r="W37" s="9"/>
-      <c r="X37" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y37" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z37" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA37" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A38" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I38" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J38" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="K38" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="L38" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M38" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N38" s="9">
-        <v>3329</v>
-      </c>
-      <c r="O38" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="P38" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q38" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="R38" s="1"/>
-      <c r="S38" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="T38" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="U38" s="9"/>
-      <c r="V38" s="9"/>
-      <c r="W38" s="9"/>
-      <c r="X38" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y38" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z38" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA38" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A39" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J39" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="K39" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="L39" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="M39" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N39" s="9">
-        <v>3037</v>
-      </c>
-      <c r="O39" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="P39" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q39" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="R39" s="1"/>
-      <c r="S39" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="T39" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="U39" s="9"/>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
-      <c r="X39" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y39" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z39" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA39" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A40" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="H40" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J40" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="K40" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="L40" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="M40" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N40" s="9">
-        <v>5685</v>
-      </c>
-      <c r="O40" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="P40" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q40" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="R40" s="1"/>
-      <c r="S40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="T40" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="U40" s="9"/>
-      <c r="V40" s="9"/>
-      <c r="W40" s="9"/>
-      <c r="X40" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y40" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z40" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA40" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A41" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I41" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J41" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="K41" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="L41" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="M41" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N41" s="9">
-        <v>5023</v>
-      </c>
-      <c r="O41" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="P41" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q41" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="R41" s="1"/>
-      <c r="S41" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="T41" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="U41" s="9"/>
-      <c r="V41" s="9"/>
-      <c r="W41" s="9"/>
-      <c r="X41" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y41" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z41" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA41" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A42" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J42" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="K42" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="L42" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="M42" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N42" s="9">
-        <v>6189</v>
-      </c>
-      <c r="O42" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="P42" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q42" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="R42" s="1"/>
-      <c r="S42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="T42" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y42" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z42" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA42" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A43" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J43" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="K43" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="L43" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="M43" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="9">
-        <v>5246</v>
-      </c>
-      <c r="O43" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="P43" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q43" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="R43" s="1"/>
-      <c r="S43" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="T43" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="U43" s="9"/>
-      <c r="V43" s="9"/>
-      <c r="W43" s="9"/>
-      <c r="X43" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y43" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z43" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA43" s="9">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AB43">
-    <sortCondition ref="P2:P43"/>
-    <sortCondition ref="R2:R43"/>
-    <sortCondition ref="S2:S43"/>
-    <sortCondition ref="C2:C43"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AB33">
+    <sortCondition ref="P2:P33"/>
+    <sortCondition ref="R2:R33"/>
+    <sortCondition ref="S2:S33"/>
+    <sortCondition ref="C2:C33"/>
   </sortState>
-  <conditionalFormatting sqref="AA44:AA1048576 AA1:AA5">
+  <conditionalFormatting sqref="AA34:AA1048576 AA1:AA3">
     <cfRule type="colorScale" priority="47">
       <colorScale>
         <cfvo type="min"/>
@@ -4938,19 +4191,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA6:AA8">
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA9:AA19">
+  <conditionalFormatting sqref="AA6:AA10">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
@@ -4962,7 +4203,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA20:AA21">
+  <conditionalFormatting sqref="AA11:AA12">
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
@@ -4974,7 +4215,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA24:AA25 AA22">
+  <conditionalFormatting sqref="AA15:AA16 AA13">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
@@ -4986,7 +4227,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA37:AA38">
+  <conditionalFormatting sqref="AA28:AA29">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -4998,19 +4239,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA39">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA40">
+  <conditionalFormatting sqref="AA30">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -5022,7 +4251,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA30:AA32 AA34:AA36 AA41">
+  <conditionalFormatting sqref="AA21:AA23 AA31 AA25:AA27">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -5034,7 +4263,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA42:AA43">
+  <conditionalFormatting sqref="AA32:AA33">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -5046,7 +4275,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA23">
+  <conditionalFormatting sqref="AA14">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -5058,8 +4287,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA26:AA29 AA33">
+  <conditionalFormatting sqref="AA17:AA20 AA24">
     <cfRule type="colorScale" priority="55">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA4:AA5">
+    <cfRule type="colorScale" priority="59">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5103,10 +4344,10 @@
         <v>168</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>159</v>
@@ -5171,22 +4412,22 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>105</v>
@@ -5214,7 +4455,7 @@
         <v>8</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S2" s="2" t="s">
         <v>6</v>
@@ -5244,22 +4485,22 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>183</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>105</v>
@@ -5287,7 +4528,7 @@
         <v>8</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>6</v>
@@ -5332,7 +4573,7 @@
         <v>170</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>105</v>
@@ -5409,7 +4650,7 @@
         <v>170</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>105</v>
@@ -5486,7 +4727,7 @@
         <v>170</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>105</v>
@@ -5548,22 +4789,22 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D7" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="E7" s="12" t="s">
-        <v>198</v>
-      </c>
       <c r="F7" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>105</v>
@@ -5581,7 +4822,7 @@
         <v>11</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M7" s="9" t="s">
         <v>3</v>
@@ -5638,7 +4879,7 @@
         <v>106</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>105</v>
@@ -5710,7 +4951,7 @@
         <v>61</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>163</v>
@@ -5855,7 +5096,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>16</v>
@@ -5864,10 +5105,10 @@
         <v>89</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>105</v>
@@ -6004,22 +5245,22 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E13" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="E13" s="12" t="s">
-        <v>198</v>
-      </c>
       <c r="F13" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>105</v>
@@ -6037,7 +5278,7 @@
         <v>11</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M13" s="9" t="s">
         <v>3</v>
@@ -6212,4 +5453,955 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E81A549-F927-B644-A7B0-3BB907DA27E4}">
+  <dimension ref="A1:AA11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" s="9">
+        <v>4060</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R2" s="1"/>
+      <c r="S2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="T2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA2" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N3" s="9">
+        <v>6387</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="R3" s="1"/>
+      <c r="S3" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA3" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N4" s="9">
+        <v>4936</v>
+      </c>
+      <c r="O4" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="R4" s="1"/>
+      <c r="S4" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="Y4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA4" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="9">
+        <v>933</v>
+      </c>
+      <c r="O5" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q5" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R5" s="1"/>
+      <c r="S5" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA5" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N6" s="9">
+        <v>4936</v>
+      </c>
+      <c r="O6" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P6" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R6" s="1"/>
+      <c r="S6" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="T6" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="9">
+        <v>5356</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R7" s="1"/>
+      <c r="S7" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA7" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="9">
+        <v>1786</v>
+      </c>
+      <c r="O8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R8" s="1"/>
+      <c r="S8" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="T8" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA8" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="9">
+        <v>3037</v>
+      </c>
+      <c r="O9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="R9" s="1"/>
+      <c r="S9" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="T9" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA9" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A10" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="9">
+        <v>6758</v>
+      </c>
+      <c r="O10" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P10" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="R10" s="1"/>
+      <c r="S10" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="T10" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U10" s="9"/>
+      <c r="V10" s="9"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA10" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A11" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N11" s="9">
+        <v>4871</v>
+      </c>
+      <c r="O11" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P11" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="R11" s="1"/>
+      <c r="S11" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="T11" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U11" s="9"/>
+      <c r="V11" s="9"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y11" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z11" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA11" s="9">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="AA1">
+    <cfRule type="colorScale" priority="63">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2">
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA3">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA4">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA5:AA6">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA7">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA8">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA9">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA10:AA11">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/tabular/reference/herv_sublineage_data.xlsx
+++ b/tabular/reference/herv_sublineage_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341FA787-1BF4-C64C-B0A0-9AB52AA6E50C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13FD4EE0-82A6-4C4E-9627-0011D59E8EE4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1240" yWindow="500" windowWidth="23060" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1650,7 +1650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB9083D8-DE01-F14E-ACB5-AF33867092C5}">
-  <dimension ref="A1:AA33"/>
+  <dimension ref="A1:AA32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -2279,24 +2279,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>190</v>
+        <v>63</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>229</v>
+        <v>124</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>190</v>
+        <v>63</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>229</v>
+        <v>174</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>164</v>
@@ -2308,18 +2308,20 @@
         <v>161</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>190</v>
+        <v>63</v>
       </c>
       <c r="M9" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="12"/>
+      <c r="N9" s="9">
+        <v>4981</v>
+      </c>
       <c r="O9" s="10" t="s">
         <v>14</v>
       </c>
@@ -2327,46 +2329,48 @@
         <v>5</v>
       </c>
       <c r="Q9" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="R9" s="9"/>
+        <v>54</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>205</v>
+      </c>
       <c r="S9" s="9" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T9" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA9" s="9">
         <v>3</v>
       </c>
-      <c r="U9" s="12"/>
-      <c r="V9" s="12"/>
-      <c r="W9" s="12"/>
-      <c r="X9" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y9" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z9" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA9" s="12">
-        <v>1</v>
-      </c>
     </row>
-    <row r="10" spans="1:27" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>124</v>
+        <v>202</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>150</v>
+        <v>58</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>163</v>
@@ -2381,19 +2385,19 @@
         <v>161</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>11</v>
+        <v>163</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>12</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M10" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N10" s="9">
-        <v>4981</v>
+        <v>6996</v>
       </c>
       <c r="O10" s="10" t="s">
         <v>14</v>
@@ -2405,7 +2409,7 @@
         <v>54</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S10" s="9" t="s">
         <v>6</v>
@@ -2431,25 +2435,25 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>96</v>
+        <v>59</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>59</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>201</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>105</v>
@@ -2461,16 +2465,16 @@
         <v>163</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M11" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N11" s="9">
-        <v>6996</v>
+        <v>11027</v>
       </c>
       <c r="O11" s="10" t="s">
         <v>14</v>
@@ -2492,9 +2496,11 @@
       </c>
       <c r="U11" s="9"/>
       <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
+      <c r="W11" s="9">
+        <v>2825129</v>
+      </c>
       <c r="X11" s="9" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="Y11" s="9" t="s">
         <v>11</v>
@@ -2503,27 +2509,27 @@
         <v>11</v>
       </c>
       <c r="AA11" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>201</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>203</v>
@@ -2535,19 +2541,19 @@
         <v>161</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>163</v>
+        <v>11</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M12" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N12" s="9">
-        <v>11027</v>
+        <v>8987</v>
       </c>
       <c r="O12" s="10" t="s">
         <v>14</v>
@@ -2569,11 +2575,11 @@
       </c>
       <c r="U12" s="9"/>
       <c r="V12" s="9"/>
-      <c r="W12" s="9">
+      <c r="W12" s="12">
         <v>2825129</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="Y12" s="9" t="s">
         <v>11</v>
@@ -2587,22 +2593,22 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>60</v>
+        <v>197</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>60</v>
+        <v>197</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>60</v>
+        <v>197</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>201</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>203</v>
@@ -2620,14 +2626,12 @@
         <v>11</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>60</v>
+        <v>197</v>
       </c>
       <c r="M13" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="N13" s="9">
-        <v>8987</v>
-      </c>
+      <c r="N13" s="9"/>
       <c r="O13" s="10" t="s">
         <v>14</v>
       </c>
@@ -2641,16 +2645,14 @@
         <v>204</v>
       </c>
       <c r="S13" s="9" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U13" s="9"/>
       <c r="V13" s="9"/>
-      <c r="W13" s="12">
-        <v>2825129</v>
-      </c>
+      <c r="W13" s="12"/>
       <c r="X13" s="9" t="s">
         <v>10</v>
       </c>
@@ -2660,31 +2662,31 @@
       <c r="Z13" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="AA13" s="9">
-        <v>4</v>
+      <c r="AA13" s="12">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>197</v>
+        <v>55</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>197</v>
+        <v>55</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>197</v>
+        <v>94</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>105</v>
@@ -2693,18 +2695,20 @@
         <v>161</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>197</v>
+        <v>55</v>
       </c>
       <c r="M14" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="9"/>
+      <c r="N14" s="9">
+        <v>5586</v>
+      </c>
       <c r="O14" s="10" t="s">
         <v>14</v>
       </c>
@@ -2714,20 +2718,18 @@
       <c r="Q14" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="R14" s="1" t="s">
-        <v>204</v>
-      </c>
+      <c r="R14" s="1"/>
       <c r="S14" s="9" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U14" s="9"/>
       <c r="V14" s="9"/>
-      <c r="W14" s="12"/>
+      <c r="W14" s="9"/>
       <c r="X14" s="9" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="Y14" s="9" t="s">
         <v>11</v>
@@ -2735,22 +2737,22 @@
       <c r="Z14" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="AA14" s="12">
-        <v>1</v>
+      <c r="AA14" s="9">
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>172</v>
@@ -2774,13 +2776,13 @@
         <v>12</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M15" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N15" s="9">
-        <v>5586</v>
+        <v>6918</v>
       </c>
       <c r="O15" s="10" t="s">
         <v>14</v>
@@ -2816,16 +2818,16 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>126</v>
+        <v>206</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>172</v>
@@ -2834,7 +2836,7 @@
         <v>163</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>105</v>
@@ -2849,13 +2851,13 @@
         <v>12</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="M16" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N16" s="9">
-        <v>6918</v>
+        <v>3944</v>
       </c>
       <c r="O16" s="10" t="s">
         <v>14</v>
@@ -2891,16 +2893,16 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>172</v>
@@ -2924,13 +2926,13 @@
         <v>12</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M17" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N17" s="9">
-        <v>3944</v>
+        <v>7133</v>
       </c>
       <c r="O17" s="10" t="s">
         <v>14</v>
@@ -2966,16 +2968,16 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>172</v>
@@ -2999,13 +3001,13 @@
         <v>12</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M18" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N18" s="9">
-        <v>7133</v>
+        <v>4285</v>
       </c>
       <c r="O18" s="10" t="s">
         <v>14</v>
@@ -3041,16 +3043,16 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>172</v>
@@ -3074,13 +3076,13 @@
         <v>12</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M19" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N19" s="9">
-        <v>4285</v>
+        <v>4880</v>
       </c>
       <c r="O19" s="10" t="s">
         <v>14</v>
@@ -3116,16 +3118,16 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>172</v>
@@ -3149,13 +3151,13 @@
         <v>12</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M20" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N20" s="9">
-        <v>4880</v>
+        <v>2880</v>
       </c>
       <c r="O20" s="10" t="s">
         <v>14</v>
@@ -3177,39 +3179,39 @@
       <c r="V20" s="9"/>
       <c r="W20" s="9"/>
       <c r="X20" s="9" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="Y20" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z20" s="9" t="s">
         <v>11</v>
       </c>
       <c r="AA20" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>225</v>
+        <v>227</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>119</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>67</v>
+        <v>227</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>155</v>
+        <v>227</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>172</v>
+        <v>106</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>163</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>105</v>
@@ -3224,26 +3226,28 @@
         <v>12</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>67</v>
+        <v>228</v>
       </c>
       <c r="M21" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N21" s="9">
-        <v>2880</v>
+        <v>6070</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P21" s="9" t="s">
         <v>5</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="R21" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="R21" s="13">
+        <v>16</v>
+      </c>
       <c r="S21" s="9" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T21" s="9" t="s">
         <v>9</v>
@@ -3255,36 +3259,36 @@
         <v>10</v>
       </c>
       <c r="Y21" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z21" s="9" t="s">
         <v>11</v>
       </c>
       <c r="AA21" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>227</v>
+        <v>84</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>106</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="H22" s="9" t="s">
         <v>105</v>
@@ -3293,19 +3297,19 @@
         <v>161</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>228</v>
+        <v>20</v>
       </c>
       <c r="M22" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N22" s="9">
-        <v>6070</v>
+        <v>5667</v>
       </c>
       <c r="O22" s="10" t="s">
         <v>18</v>
@@ -3316,8 +3320,8 @@
       <c r="Q22" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="R22" s="13">
-        <v>16</v>
+      <c r="R22" s="13" t="s">
+        <v>222</v>
       </c>
       <c r="S22" s="9" t="s">
         <v>13</v>
@@ -3343,16 +3347,16 @@
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>84</v>
+        <v>21</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>87</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>106</v>
@@ -3373,16 +3377,16 @@
         <v>11</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>163</v>
+        <v>12</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M23" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N23" s="9">
-        <v>5667</v>
+        <v>5714</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>18</v>
@@ -3393,7 +3397,7 @@
       <c r="Q23" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="R23" s="13" t="s">
+      <c r="R23" s="1" t="s">
         <v>222</v>
       </c>
       <c r="S23" s="9" t="s">
@@ -3420,25 +3424,25 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>87</v>
+        <v>23</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>97</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>106</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>203</v>
+        <v>163</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="H24" s="9" t="s">
         <v>105</v>
@@ -3447,19 +3451,19 @@
         <v>161</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K24" s="9" t="s">
         <v>12</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M24" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N24" s="9">
-        <v>5714</v>
+        <v>4996</v>
       </c>
       <c r="O24" s="10" t="s">
         <v>18</v>
@@ -3470,8 +3474,8 @@
       <c r="Q24" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="R24" s="1" t="s">
-        <v>222</v>
+      <c r="R24" s="14">
+        <v>16</v>
       </c>
       <c r="S24" s="9" t="s">
         <v>13</v>
@@ -3497,16 +3501,16 @@
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>106</v>
@@ -3524,19 +3528,19 @@
         <v>161</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="K25" s="9" t="s">
         <v>12</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M25" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N25" s="9">
-        <v>4996</v>
+        <v>3556</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>18</v>
@@ -3547,9 +3551,7 @@
       <c r="Q25" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="R25" s="14">
-        <v>16</v>
-      </c>
+      <c r="R25" s="1"/>
       <c r="S25" s="9" t="s">
         <v>13</v>
       </c>
@@ -3560,7 +3562,7 @@
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
       <c r="X25" s="9" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="Y25" s="9" t="s">
         <v>11</v>
@@ -3569,21 +3571,21 @@
         <v>11</v>
       </c>
       <c r="AA25" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>106</v>
@@ -3591,7 +3593,7 @@
       <c r="F26" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="9" t="s">
         <v>164</v>
       </c>
       <c r="H26" s="9" t="s">
@@ -3607,13 +3609,13 @@
         <v>12</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M26" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N26" s="9">
-        <v>3556</v>
+        <v>5343</v>
       </c>
       <c r="O26" s="10" t="s">
         <v>18</v>
@@ -3635,7 +3637,7 @@
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
       <c r="X26" s="9" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="Y26" s="9" t="s">
         <v>11</v>
@@ -3649,16 +3651,16 @@
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>106</v>
@@ -3682,13 +3684,13 @@
         <v>12</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M27" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N27" s="9">
-        <v>5343</v>
+        <v>5530</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>18</v>
@@ -3724,16 +3726,16 @@
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>106</v>
@@ -3741,7 +3743,7 @@
       <c r="F28" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="3" t="s">
         <v>164</v>
       </c>
       <c r="H28" s="9" t="s">
@@ -3757,13 +3759,13 @@
         <v>12</v>
       </c>
       <c r="L28" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M28" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N28" s="9">
-        <v>5530</v>
+        <v>3329</v>
       </c>
       <c r="O28" s="10" t="s">
         <v>18</v>
@@ -3799,24 +3801,24 @@
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>106</v>
+        <v>171</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G29" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G29" s="9" t="s">
         <v>164</v>
       </c>
       <c r="H29" s="9" t="s">
@@ -3832,13 +3834,13 @@
         <v>12</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M29" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N29" s="9">
-        <v>3329</v>
+        <v>5685</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>18</v>
@@ -3860,7 +3862,7 @@
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
       <c r="X29" s="9" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="Y29" s="9" t="s">
         <v>11</v>
@@ -3874,25 +3876,25 @@
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>171</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H30" s="9" t="s">
         <v>105</v>
@@ -3907,13 +3909,13 @@
         <v>12</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M30" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N30" s="9">
-        <v>5685</v>
+        <v>5023</v>
       </c>
       <c r="O30" s="10" t="s">
         <v>18</v>
@@ -3935,7 +3937,7 @@
       <c r="V30" s="9"/>
       <c r="W30" s="9"/>
       <c r="X30" s="9" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="Y30" s="9" t="s">
         <v>11</v>
@@ -3944,21 +3946,21 @@
         <v>11</v>
       </c>
       <c r="AA30" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>171</v>
@@ -3982,13 +3984,13 @@
         <v>12</v>
       </c>
       <c r="L31" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M31" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N31" s="9">
-        <v>5023</v>
+        <v>6189</v>
       </c>
       <c r="O31" s="10" t="s">
         <v>18</v>
@@ -4010,7 +4012,7 @@
       <c r="V31" s="9"/>
       <c r="W31" s="9"/>
       <c r="X31" s="9" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="Y31" s="9" t="s">
         <v>11</v>
@@ -4019,30 +4021,30 @@
         <v>11</v>
       </c>
       <c r="AA31" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>157</v>
+        <v>85</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>171</v>
+        <v>106</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H32" s="9" t="s">
         <v>105</v>
@@ -4054,16 +4056,16 @@
         <v>163</v>
       </c>
       <c r="K32" s="9" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="L32" s="9" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="M32" s="9" t="s">
         <v>3</v>
       </c>
       <c r="N32" s="9">
-        <v>6189</v>
+        <v>5246</v>
       </c>
       <c r="O32" s="10" t="s">
         <v>18</v>
@@ -4072,7 +4074,7 @@
         <v>5</v>
       </c>
       <c r="Q32" s="9" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="R32" s="1"/>
       <c r="S32" s="9" t="s">
@@ -4085,7 +4087,7 @@
       <c r="V32" s="9"/>
       <c r="W32" s="9"/>
       <c r="X32" s="9" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="Y32" s="9" t="s">
         <v>11</v>
@@ -4094,92 +4096,17 @@
         <v>11</v>
       </c>
       <c r="AA32" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A33" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="L33" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="M33" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N33" s="9">
-        <v>5246</v>
-      </c>
-      <c r="O33" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="P33" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="R33" s="1"/>
-      <c r="S33" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="T33" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="U33" s="9"/>
-      <c r="V33" s="9"/>
-      <c r="W33" s="9"/>
-      <c r="X33" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y33" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z33" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA33" s="9">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AB33">
-    <sortCondition ref="P2:P33"/>
-    <sortCondition ref="R2:R33"/>
-    <sortCondition ref="S2:S33"/>
-    <sortCondition ref="C2:C33"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AB32">
+    <sortCondition ref="P2:P32"/>
+    <sortCondition ref="R2:R32"/>
+    <sortCondition ref="S2:S32"/>
+    <sortCondition ref="C2:C32"/>
   </sortState>
-  <conditionalFormatting sqref="AA34:AA1048576 AA1:AA3">
+  <conditionalFormatting sqref="AA33:AA1048576 AA1:AA3">
     <cfRule type="colorScale" priority="47">
       <colorScale>
         <cfvo type="min"/>
@@ -4191,7 +4118,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA6:AA10">
+  <conditionalFormatting sqref="AA6:AA9">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
@@ -4203,7 +4130,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA11:AA12">
+  <conditionalFormatting sqref="AA10:AA11">
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
@@ -4215,7 +4142,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA15:AA16 AA13">
+  <conditionalFormatting sqref="AA14:AA15 AA12">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
@@ -4227,7 +4154,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA28:AA29">
+  <conditionalFormatting sqref="AA27:AA28">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -4239,7 +4166,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA30">
+  <conditionalFormatting sqref="AA29">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -4251,7 +4178,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA21:AA23 AA31 AA25:AA27">
+  <conditionalFormatting sqref="AA20:AA22 AA30 AA24:AA26">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -4263,7 +4190,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA32:AA33">
+  <conditionalFormatting sqref="AA31:AA32">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -4275,7 +4202,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA14">
+  <conditionalFormatting sqref="AA13">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -4287,7 +4214,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA17:AA20 AA24">
+  <conditionalFormatting sqref="AA16:AA19 AA23">
     <cfRule type="colorScale" priority="55">
       <colorScale>
         <cfvo type="min"/>
@@ -5457,7 +5384,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E81A549-F927-B644-A7B0-3BB907DA27E4}">
-  <dimension ref="A1:AA11"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.2">
@@ -6293,9 +6220,82 @@
         <v>4</v>
       </c>
     </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A12" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="12"/>
+      <c r="O12" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P12" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="R12" s="9"/>
+      <c r="S12" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="T12" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12" s="12"/>
+      <c r="V12" s="12"/>
+      <c r="W12" s="12"/>
+      <c r="X12" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA12" s="12">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="AA1">
-    <cfRule type="colorScale" priority="63">
+    <cfRule type="colorScale" priority="64">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6307,7 +6307,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="colorScale" priority="64">
+    <cfRule type="colorScale" priority="65">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6319,6 +6319,18 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA3">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA4">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -6330,7 +6342,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA4">
+  <conditionalFormatting sqref="AA5:AA6">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -6342,7 +6354,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA5:AA6">
+  <conditionalFormatting sqref="AA7">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -6354,7 +6366,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA7">
+  <conditionalFormatting sqref="AA8">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -6366,7 +6378,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA8">
+  <conditionalFormatting sqref="AA9">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -6378,7 +6390,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA9">
+  <conditionalFormatting sqref="AA10:AA11">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -6390,7 +6402,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA10:AA11">
+  <conditionalFormatting sqref="AA12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/tabular/reference/herv_sublineage_data.xlsx
+++ b/tabular/reference/herv_sublineage_data.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13FD4EE0-82A6-4C4E-9627-0011D59E8EE4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6375B60-369C-BD47-A204-730520869A84}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1240" yWindow="500" windowWidth="23060" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sublineage" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
-    <sheet name="removed" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="233">
   <si>
     <t>sequenceID</t>
   </si>
@@ -1650,7 +1649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB9083D8-DE01-F14E-ACB5-AF33867092C5}">
-  <dimension ref="A1:AA32"/>
+  <dimension ref="A1:AA43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -4099,6 +4098,829 @@
         <v>3</v>
       </c>
     </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A33" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M33" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="9">
+        <v>4060</v>
+      </c>
+      <c r="O33" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P33" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R33" s="1"/>
+      <c r="S33" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="T33" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U33" s="9"/>
+      <c r="V33" s="9"/>
+      <c r="W33" s="9"/>
+      <c r="X33" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y33" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z33" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA33" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A34" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="M34" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N34" s="9">
+        <v>6387</v>
+      </c>
+      <c r="O34" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P34" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q34" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="R34" s="1"/>
+      <c r="S34" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="T34" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U34" s="9"/>
+      <c r="V34" s="9"/>
+      <c r="W34" s="9"/>
+      <c r="X34" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y34" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z34" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA34" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A35" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L35" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M35" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="9">
+        <v>4936</v>
+      </c>
+      <c r="O35" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P35" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="R35" s="1"/>
+      <c r="S35" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="T35" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U35" s="9"/>
+      <c r="V35" s="9"/>
+      <c r="W35" s="9"/>
+      <c r="X35" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="Y35" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z35" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA35" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A36" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L36" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="M36" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N36" s="9">
+        <v>933</v>
+      </c>
+      <c r="O36" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P36" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q36" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R36" s="1"/>
+      <c r="S36" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="T36" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U36" s="9"/>
+      <c r="V36" s="9"/>
+      <c r="W36" s="9"/>
+      <c r="X36" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y36" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z36" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A37" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L37" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M37" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N37" s="9">
+        <v>4936</v>
+      </c>
+      <c r="O37" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P37" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q37" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R37" s="1"/>
+      <c r="S37" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="T37" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U37" s="9"/>
+      <c r="V37" s="9"/>
+      <c r="W37" s="9"/>
+      <c r="X37" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y37" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z37" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA37" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A38" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K38" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L38" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="M38" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="9">
+        <v>5356</v>
+      </c>
+      <c r="O38" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P38" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q38" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R38" s="1"/>
+      <c r="S38" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="T38" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U38" s="9"/>
+      <c r="V38" s="9"/>
+      <c r="W38" s="9"/>
+      <c r="X38" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y38" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z38" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA38" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A39" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J39" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K39" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L39" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="M39" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N39" s="9">
+        <v>1786</v>
+      </c>
+      <c r="O39" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P39" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q39" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R39" s="1"/>
+      <c r="S39" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="T39" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U39" s="9"/>
+      <c r="V39" s="9"/>
+      <c r="W39" s="9"/>
+      <c r="X39" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y39" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z39" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA39" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A40" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="K40" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L40" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M40" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N40" s="9">
+        <v>3037</v>
+      </c>
+      <c r="O40" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="P40" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q40" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="R40" s="1"/>
+      <c r="S40" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="T40" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U40" s="9"/>
+      <c r="V40" s="9"/>
+      <c r="W40" s="9"/>
+      <c r="X40" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y40" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z40" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA40" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A41" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J41" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K41" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L41" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="M41" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="9">
+        <v>6758</v>
+      </c>
+      <c r="O41" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P41" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q41" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="R41" s="1"/>
+      <c r="S41" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="T41" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U41" s="9"/>
+      <c r="V41" s="9"/>
+      <c r="W41" s="9"/>
+      <c r="X41" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y41" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z41" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA41" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A42" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J42" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K42" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L42" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="M42" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="9">
+        <v>4871</v>
+      </c>
+      <c r="O42" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P42" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q42" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="R42" s="1"/>
+      <c r="S42" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="T42" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U42" s="9"/>
+      <c r="V42" s="9"/>
+      <c r="W42" s="9"/>
+      <c r="X42" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y42" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z42" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A43" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K43" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="L43" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="M43" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="12"/>
+      <c r="O43" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P43" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q43" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="R43" s="9"/>
+      <c r="S43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="T43" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="U43" s="12"/>
+      <c r="V43" s="12"/>
+      <c r="W43" s="12"/>
+      <c r="X43" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y43" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z43" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA43" s="12">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AB32">
     <sortCondition ref="P2:P32"/>
@@ -4106,8 +4928,8 @@
     <sortCondition ref="S2:S32"/>
     <sortCondition ref="C2:C32"/>
   </sortState>
-  <conditionalFormatting sqref="AA33:AA1048576 AA1:AA3">
-    <cfRule type="colorScale" priority="47">
+  <conditionalFormatting sqref="AA44:AA1048576 AA1:AA3">
+    <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4119,6 +4941,90 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA6:AA9">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA10:AA11">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA14:AA15 AA12">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA27:AA28">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA29">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA20:AA22 AA30 AA24:AA26">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA31:AA32">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA13">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
@@ -4130,92 +5036,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA10:AA11">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA14:AA15 AA12">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA27:AA28">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA29">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA20:AA22 AA30 AA24:AA26">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA31:AA32">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA13">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AA16:AA19 AA23">
-    <cfRule type="colorScale" priority="55">
+    <cfRule type="colorScale" priority="64">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4227,7 +5049,115 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA4:AA5">
-    <cfRule type="colorScale" priority="59">
+    <cfRule type="colorScale" priority="68">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA33">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA34">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA35">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA36:AA37">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA38">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA39">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA40">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA41:AA42">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA43">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4244,7 +5174,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E84FD6B7-DAC0-EF4A-B6E8-A6FD2C634E5A}">
-  <dimension ref="A1:AA13"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.1640625" customWidth="1"/>
@@ -5168,81 +6098,6 @@
       </c>
       <c r="AA12" s="9">
         <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N13" s="12">
-        <v>2482</v>
-      </c>
-      <c r="O13" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q13" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="R13" s="9"/>
-      <c r="S13" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="T13" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="U13" s="12"/>
-      <c r="V13" s="12"/>
-      <c r="W13" s="12"/>
-      <c r="X13" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y13" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z13" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA13" s="12">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5366,1054 +6221,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA13">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E81A549-F927-B644-A7B0-3BB907DA27E4}">
-  <dimension ref="A1:AA12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="U1" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="V1" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="W1" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N2" s="9">
-        <v>4060</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q2" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="R2" s="1"/>
-      <c r="S2" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="T2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y2" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z2" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA2" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" s="9">
-        <v>6387</v>
-      </c>
-      <c r="O3" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="P3" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q3" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="R3" s="1"/>
-      <c r="S3" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="T3" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-      <c r="X3" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA3" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N4" s="9">
-        <v>4936</v>
-      </c>
-      <c r="O4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="P4" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="R4" s="1"/>
-      <c r="S4" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="T4" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
-      <c r="W4" s="9"/>
-      <c r="X4" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="Y4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA4" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N5" s="9">
-        <v>933</v>
-      </c>
-      <c r="O5" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q5" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="R5" s="1"/>
-      <c r="S5" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="T5" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y5" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z5" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA5" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="M6" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N6" s="9">
-        <v>4936</v>
-      </c>
-      <c r="O6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="P6" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q6" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="R6" s="1"/>
-      <c r="S6" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="T6" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y6" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z6" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA6" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="9">
-        <v>5356</v>
-      </c>
-      <c r="O7" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q7" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="R7" s="1"/>
-      <c r="S7" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="T7" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y7" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z7" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA7" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N8" s="9">
-        <v>1786</v>
-      </c>
-      <c r="O8" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="P8" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q8" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="R8" s="1"/>
-      <c r="S8" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="T8" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="U8" s="9"/>
-      <c r="V8" s="9"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y8" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z8" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA8" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A9" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N9" s="9">
-        <v>3037</v>
-      </c>
-      <c r="O9" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="R9" s="1"/>
-      <c r="S9" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="T9" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="U9" s="9"/>
-      <c r="V9" s="9"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y9" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z9" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA9" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="M10" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N10" s="9">
-        <v>6758</v>
-      </c>
-      <c r="O10" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="P10" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q10" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="R10" s="1"/>
-      <c r="S10" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="T10" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="U10" s="9"/>
-      <c r="V10" s="9"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y10" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z10" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA10" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A11" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N11" s="9">
-        <v>4871</v>
-      </c>
-      <c r="O11" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q11" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="R11" s="1"/>
-      <c r="S11" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="T11" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y11" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z11" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA11" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A12" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N12" s="12"/>
-      <c r="O12" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q12" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="R12" s="9"/>
-      <c r="S12" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="T12" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="U12" s="12"/>
-      <c r="V12" s="12"/>
-      <c r="W12" s="12"/>
-      <c r="X12" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y12" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z12" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA12" s="12">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="AA1">
-    <cfRule type="colorScale" priority="64">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2">
-    <cfRule type="colorScale" priority="65">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA3">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA4">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA5:AA6">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA7">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA8">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA9">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA10:AA11">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA12">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>